--- a/results/intersections.xlsx
+++ b/results/intersections.xlsx
@@ -13145,7 +13145,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>N5.HOG0049214</t>
+          <t>N5.HOG0051228</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
@@ -13155,24 +13155,24 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>129227566</t>
+          <t>129229946</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>GO:0003684 [Name: damaged DNA binding]; GO:0005634 [Name: nucleus]; GO:0000012 [Name: single strand break repair]; GO:0006303 [Name: double-strand break repair via nonhomologous end joining]; GO:0006284 [Name: base-excision repair]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>DNA repair protein XRCC1</t>
+          <t>Family with sequence similarity 21</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>N5.HOG0051228</t>
+          <t>N5.HOG0051445</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -13180,26 +13180,14 @@
           <t>intensified, busted_ph_rev</t>
         </is>
       </c>
-      <c r="C496" t="inlineStr">
-        <is>
-          <t>129229946</t>
-        </is>
-      </c>
-      <c r="D496" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E496" t="inlineStr">
-        <is>
-          <t>Family with sequence similarity 21</t>
-        </is>
-      </c>
+      <c r="C496" t="inlineStr"/>
+      <c r="D496" t="inlineStr"/>
+      <c r="E496" t="inlineStr"/>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>N5.HOG0051445</t>
+          <t>N5.HOG0053205</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -13207,14 +13195,26 @@
           <t>intensified, busted_ph_rev</t>
         </is>
       </c>
-      <c r="C497" t="inlineStr"/>
-      <c r="D497" t="inlineStr"/>
-      <c r="E497" t="inlineStr"/>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>129220707</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>GO:0008270 [Name: zinc ion binding]; GO:0043130 [Name: ubiquitin binding]; GO:0000407 [Name: pre-autophagosomal structure]; GO:0016236 [Name: macroautophagy]</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>next to BRCA1 gene 1 protein-like</t>
+        </is>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>N5.HOG0053205</t>
+          <t>N5.HOG0055205</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -13224,24 +13224,24 @@
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>129220707</t>
+          <t>129224310</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>GO:0008270 [Name: zinc ion binding]; GO:0043130 [Name: ubiquitin binding]; GO:0000407 [Name: pre-autophagosomal structure]; GO:0016236 [Name: macroautophagy]</t>
+          <t>GO:0000012 [Name: single strand break repair]; GO:0017005 [Name: 3'-tyrosyl-DNA phosphodiesterase activity]; GO:0005509 [Name: calcium ion binding]; GO:0003697 [Name: single-stranded DNA binding]; GO:0005634 [Name: nucleus]; GO:0003690 [Name: double-stranded DNA binding]; GO:0006302 [Name: double-strand break repair]</t>
         </is>
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>next to BRCA1 gene 1 protein-like</t>
+          <t>tyrosyl-DNA phosphodiesterase glaikit</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>N5.HOG0055205</t>
+          <t>N5.HOG0055571</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -13251,24 +13251,24 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>129224310</t>
+          <t>129230726</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>GO:0000012 [Name: single strand break repair]; GO:0017005 [Name: 3'-tyrosyl-DNA phosphodiesterase activity]; GO:0005509 [Name: calcium ion binding]; GO:0003697 [Name: single-stranded DNA binding]; GO:0005634 [Name: nucleus]; GO:0003690 [Name: double-stranded DNA binding]; GO:0006302 [Name: double-strand break repair]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>tyrosyl-DNA phosphodiesterase glaikit</t>
+          <t>dnaJ homolog subfamily C member 10-like</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>N5.HOG0055571</t>
+          <t>N5.HOG0060290</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -13276,21 +13276,9 @@
           <t>intensified, busted_ph_rev</t>
         </is>
       </c>
-      <c r="C500" t="inlineStr">
-        <is>
-          <t>129230726</t>
-        </is>
-      </c>
-      <c r="D500" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E500" t="inlineStr">
-        <is>
-          <t>dnaJ homolog subfamily C member 10-like</t>
-        </is>
-      </c>
+      <c r="C500" t="inlineStr"/>
+      <c r="D500" t="inlineStr"/>
+      <c r="E500" t="inlineStr"/>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -13303,14 +13291,26 @@
           <t>intensified, busted_ph_rev</t>
         </is>
       </c>
-      <c r="C501" t="inlineStr"/>
-      <c r="D501" t="inlineStr"/>
-      <c r="E501" t="inlineStr"/>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>129218569</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>uncharacterized LOC129218569</t>
+        </is>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>N5.HOG0060290</t>
+          <t>N5.HOG0060455</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -13320,24 +13320,24 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>129218569</t>
+          <t>129226311</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GO:0035252 [Name: UDP-xylosyltransferase activity]</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>uncharacterized LOC129218569</t>
+          <t>xyloside xylosyltransferase 1-like</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>N5.HOG0060455</t>
+          <t>N5.HOG0060880</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -13347,24 +13347,24 @@
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>129226311</t>
+          <t>129221671</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>GO:0035252 [Name: UDP-xylosyltransferase activity]</t>
+          <t>GO:0006974 [Name: cellular response to DNA damage stimulus]; GO:0005634 [Name: nucleus]; GO:0016791 [Name: phosphatase activity]; GO:0005737 [Name: cytoplasm]</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>xyloside xylosyltransferase 1-like</t>
+          <t>damage-control phosphatase ARMT1-like</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>N5.HOG0060880</t>
+          <t>N5.HOG0062411</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -13374,24 +13374,24 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>129221671</t>
+          <t>129216252</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>GO:0006974 [Name: cellular response to DNA damage stimulus]; GO:0005634 [Name: nucleus]; GO:0016791 [Name: phosphatase activity]; GO:0005737 [Name: cytoplasm]</t>
+          <t>GO:0000209 [Name: protein polyubiquitination]; GO:0005515 [Name: protein binding]</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>damage-control phosphatase ARMT1-like</t>
+          <t>F-box only protein 28-like</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>N5.HOG0062411</t>
+          <t>N5.HOG0063012</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
@@ -13401,24 +13401,24 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>129216252</t>
+          <t>129227980</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>GO:0000209 [Name: protein polyubiquitination]; GO:0005515 [Name: protein binding]</t>
+          <t>GO:0005634 [Name: nucleus]; GO:0005664 [Name: nuclear origin of replication recognition complex]; GO:0006260 [Name: DNA replication]; GO:0003688 [Name: DNA replication origin binding]</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>F-box only protein 28-like</t>
+          <t>origin recognition complex subunit 2</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>N5.HOG0063012</t>
+          <t>N5.HOG0064288</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
@@ -13428,24 +13428,24 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>129227980</t>
+          <t>129229580</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>GO:0005634 [Name: nucleus]; GO:0005664 [Name: nuclear origin of replication recognition complex]; GO:0006260 [Name: DNA replication]; GO:0003688 [Name: DNA replication origin binding]</t>
+          <t>GO:0000978 [Name: RNA polymerase II core promoter proximal region sequence-specific DNA binding]; GO:0006357 [Name: regulation of transcription from RNA polymerase II promoter]; GO:0000981 [Name: RNA polymerase II transcription factor activity, sequence-specific DNA binding]</t>
         </is>
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>origin recognition complex subunit 2</t>
+          <t>Krueppel-like factor 13</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>N5.HOG0064288</t>
+          <t>N5.HOG0065831</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -13455,24 +13455,24 @@
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>129229580</t>
+          <t>129224328</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>GO:0000978 [Name: RNA polymerase II core promoter proximal region sequence-specific DNA binding]; GO:0006357 [Name: regulation of transcription from RNA polymerase II promoter]; GO:0000981 [Name: RNA polymerase II transcription factor activity, sequence-specific DNA binding]</t>
+          <t>GO:0008180 [Name: COP9 signalosome]; GO:0000338 [Name: protein deneddylation]; GO:0005515 [Name: protein binding]</t>
         </is>
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>Krueppel-like factor 13</t>
+          <t>COP9 signalosome complex subunit 2 alien</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>N5.HOG0065831</t>
+          <t>N5.HOG0066290</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -13480,26 +13480,14 @@
           <t>intensified, busted_ph_rev</t>
         </is>
       </c>
-      <c r="C508" t="inlineStr">
-        <is>
-          <t>129224328</t>
-        </is>
-      </c>
-      <c r="D508" t="inlineStr">
-        <is>
-          <t>GO:0008180 [Name: COP9 signalosome]; GO:0000338 [Name: protein deneddylation]; GO:0005515 [Name: protein binding]</t>
-        </is>
-      </c>
-      <c r="E508" t="inlineStr">
-        <is>
-          <t>COP9 signalosome complex subunit 2 alien</t>
-        </is>
-      </c>
+      <c r="C508" t="inlineStr"/>
+      <c r="D508" t="inlineStr"/>
+      <c r="E508" t="inlineStr"/>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>N5.HOG0066290</t>
+          <t>N5.HOG0066413</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -13507,14 +13495,26 @@
           <t>intensified, busted_ph_rev</t>
         </is>
       </c>
-      <c r="C509" t="inlineStr"/>
-      <c r="D509" t="inlineStr"/>
-      <c r="E509" t="inlineStr"/>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>129231286</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>GO:0005524 [Name: ATP binding]; GO:0009408 [Name: response to heat]; GO:0043066 [Name: negative regulation of apoptotic process]; GO:0005739 [Name: mitochondrion]; GO:0007005 [Name: mitochondrion organization]; GO:0051082 [Name: unfolded protein binding]; GO:0031072 [Name: heat shock protein binding]; GO:0006457 [Name: protein folding]</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>protein tumorous imaginal discs, mitochondrial-like</t>
+        </is>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>N5.HOG0066413</t>
+          <t>N5.HOG0067033</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -13524,24 +13524,24 @@
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>129231286</t>
+          <t>129225838</t>
         </is>
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>GO:0005524 [Name: ATP binding]; GO:0009408 [Name: response to heat]; GO:0043066 [Name: negative regulation of apoptotic process]; GO:0005739 [Name: mitochondrion]; GO:0007005 [Name: mitochondrion organization]; GO:0051082 [Name: unfolded protein binding]; GO:0031072 [Name: heat shock protein binding]; GO:0006457 [Name: protein folding]</t>
+          <t>GO:0042273 [Name: ribosomal large subunit biogenesis]; GO:0005654 [Name: nucleoplasm]; GO:0005730 [Name: nucleolus]; GO:0000122 [Name: negative regulation of transcription from RNA polymerase II promoter]; GO:0003714 [Name: transcription corepressor activity]; GO:0042393 [Name: histone binding]; GO:0030690 [Name: Noc1p-Noc2p complex]; GO:0030691 [Name: Noc2p-Noc3p complex]</t>
         </is>
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>protein tumorous imaginal discs, mitochondrial-like</t>
+          <t>nucleolar complex protein 2 homolog</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>N5.HOG0067033</t>
+          <t>N5.HOG0067848</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -13551,24 +13551,24 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>129225838</t>
+          <t>129217527</t>
         </is>
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>GO:0042273 [Name: ribosomal large subunit biogenesis]; GO:0005654 [Name: nucleoplasm]; GO:0005730 [Name: nucleolus]; GO:0000122 [Name: negative regulation of transcription from RNA polymerase II promoter]; GO:0003714 [Name: transcription corepressor activity]; GO:0042393 [Name: histone binding]; GO:0030690 [Name: Noc1p-Noc2p complex]; GO:0030691 [Name: Noc2p-Noc3p complex]</t>
+          <t>GO:0006511 [Name: ubiquitin-dependent protein catabolic process]; GO:0016567 [Name: protein ubiquitination]; GO:0061630 [Name: ubiquitin protein ligase activity]</t>
         </is>
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>nucleolar complex protein 2 homolog</t>
+          <t>E3 ubiquitin-protein ligase MYLIP-like</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>N5.HOG0067848</t>
+          <t>N5.HOG0068583</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
@@ -13578,51 +13578,51 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>129217527</t>
+          <t>129224736</t>
         </is>
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>GO:0006511 [Name: ubiquitin-dependent protein catabolic process]; GO:0016567 [Name: protein ubiquitination]; GO:0061630 [Name: ubiquitin protein ligase activity]</t>
+          <t>GO:0005615 [Name: extracellular space]; GO:0031012 [Name: extracellular matrix]; GO:0005515 [Name: protein binding]</t>
         </is>
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>E3 ubiquitin-protein ligase MYLIP-like</t>
+          <t>leucine-rich repeat transmembrane protein FLRT3-like</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>N5.HOG0068583</t>
+          <t>N5.HOG0001232</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>intensified, busted_ph_rev</t>
+          <t>silk_genes, spidroins</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>129224736</t>
+          <t>129224650</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>GO:0005615 [Name: extracellular space]; GO:0031012 [Name: extracellular matrix]; GO:0005515 [Name: protein binding]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>leucine-rich repeat transmembrane protein FLRT3-like</t>
+          <t>fibroin heavy chain-like</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>N5.HOG0001232</t>
+          <t>N5.HOG0007699</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
@@ -13630,21 +13630,9 @@
           <t>silk_genes, spidroins</t>
         </is>
       </c>
-      <c r="C514" t="inlineStr">
-        <is>
-          <t>129224650</t>
-        </is>
-      </c>
-      <c r="D514" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E514" t="inlineStr">
-        <is>
-          <t>fibroin heavy chain-like</t>
-        </is>
-      </c>
+      <c r="C514" t="inlineStr"/>
+      <c r="D514" t="inlineStr"/>
+      <c r="E514" t="inlineStr"/>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -13657,14 +13645,26 @@
           <t>silk_genes, spidroins</t>
         </is>
       </c>
-      <c r="C515" t="inlineStr"/>
-      <c r="D515" t="inlineStr"/>
-      <c r="E515" t="inlineStr"/>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>129227027</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>serine-rich adhesin for platelets-like</t>
+        </is>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>N5.HOG0007699</t>
+          <t>N5.HOG0007709</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
@@ -13674,7 +13674,7 @@
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>129227027</t>
+          <t>129223990</t>
         </is>
       </c>
       <c r="D516" t="inlineStr">
@@ -13684,7 +13684,7 @@
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>serine-rich adhesin for platelets-like</t>
+          <t>fibroin heavy chain-like</t>
         </is>
       </c>
     </row>
@@ -13701,7 +13701,7 @@
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>129223990</t>
+          <t>129224649</t>
         </is>
       </c>
       <c r="D517" t="inlineStr">
@@ -13711,7 +13711,7 @@
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>fibroin heavy chain-like</t>
+          <t>collagen alpha-1(II) chain-like</t>
         </is>
       </c>
     </row>
@@ -13728,7 +13728,7 @@
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>129224649</t>
+          <t>129224650</t>
         </is>
       </c>
       <c r="D518" t="inlineStr">
@@ -13738,14 +13738,14 @@
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>collagen alpha-1(II) chain-like</t>
+          <t>fibroin heavy chain-like</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>N5.HOG0007709</t>
+          <t>N5.HOG0012624</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
@@ -13772,7 +13772,7 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>N5.HOG0012624</t>
+          <t>N5.HOG0012625</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
@@ -13782,7 +13782,7 @@
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>129224650</t>
+          <t>129223990</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
@@ -13799,7 +13799,7 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>N5.HOG0012625</t>
+          <t>N5.HOG0025397</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
@@ -13809,7 +13809,7 @@
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>129223990</t>
+          <t>129231602</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">
@@ -13819,14 +13819,14 @@
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>fibroin heavy chain-like</t>
+          <t>serine-rich adhesin for platelets-like</t>
         </is>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>N5.HOG0025397</t>
+          <t>N5.HOG0030755</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
@@ -13836,7 +13836,7 @@
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>129231602</t>
+          <t>129235324</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
@@ -13846,14 +13846,14 @@
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>serine-rich adhesin for platelets-like</t>
+          <t>pneumococcal serine-rich repeat protein-like</t>
         </is>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>N5.HOG0030755</t>
+          <t>N5.HOG0030756</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
@@ -13880,7 +13880,7 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>N5.HOG0030756</t>
+          <t>N5.HOG0038480</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
@@ -13890,7 +13890,7 @@
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>129235324</t>
+          <t>129223990</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">
@@ -13900,14 +13900,14 @@
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>pneumococcal serine-rich repeat protein-like</t>
+          <t>fibroin heavy chain-like</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>N5.HOG0038480</t>
+          <t>N5.HOG0049756</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -13944,24 +13944,24 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>129223990</t>
+          <t>129231571</t>
         </is>
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GO:0016627 [Name: oxidoreductase activity, acting on the CH-CH group of donors]</t>
         </is>
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>fibroin heavy chain-like</t>
+          <t>acyl-CoA dehydrogenase family member 11-like</t>
         </is>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>N5.HOG0049756</t>
+          <t>N5.HOG0068505</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
@@ -13971,24 +13971,24 @@
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>129231571</t>
+          <t>129231602</t>
         </is>
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>GO:0016627 [Name: oxidoreductase activity, acting on the CH-CH group of donors]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>acyl-CoA dehydrogenase family member 11-like</t>
+          <t>serine-rich adhesin for platelets-like</t>
         </is>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>N5.HOG0068505</t>
+          <t>N5.HOG0077698</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -13998,7 +13998,7 @@
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>129231602</t>
+          <t>129226140</t>
         </is>
       </c>
       <c r="D528" t="inlineStr">
@@ -14008,14 +14008,14 @@
       </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>serine-rich adhesin for platelets-like</t>
+          <t>hornerin-like</t>
         </is>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>N5.HOG0077698</t>
+          <t>N5.HOG0078248</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
@@ -14025,7 +14025,7 @@
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>129226140</t>
+          <t>129223990</t>
         </is>
       </c>
       <c r="D529" t="inlineStr">
@@ -14035,14 +14035,14 @@
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>hornerin-like</t>
+          <t>fibroin heavy chain-like</t>
         </is>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>N5.HOG0078248</t>
+          <t>N5.HOG0078800</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
@@ -14052,24 +14052,24 @@
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>129223990</t>
+          <t>129231303</t>
         </is>
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GO:0006364 [Name: rRNA processing]; GO:0005634 [Name: nucleus]</t>
         </is>
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>fibroin heavy chain-like</t>
+          <t>uncharacterized LOC129231303</t>
         </is>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>N5.HOG0078800</t>
+          <t>N5.HOG0080637</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
@@ -14079,24 +14079,24 @@
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>129231303</t>
+          <t>129226140</t>
         </is>
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>GO:0006364 [Name: rRNA processing]; GO:0005634 [Name: nucleus]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>uncharacterized LOC129231303</t>
+          <t>hornerin-like</t>
         </is>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>N5.HOG0080637</t>
+          <t>N5.HOG0081795</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
@@ -14106,7 +14106,7 @@
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>129226140</t>
+          <t>129223990</t>
         </is>
       </c>
       <c r="D532" t="inlineStr">
@@ -14116,14 +14116,14 @@
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>hornerin-like</t>
+          <t>fibroin heavy chain-like</t>
         </is>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>N5.HOG0081795</t>
+          <t>N5.HOG0082627</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
@@ -14133,24 +14133,24 @@
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>129223990</t>
+          <t>129231303</t>
         </is>
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GO:0006364 [Name: rRNA processing]; GO:0005634 [Name: nucleus]</t>
         </is>
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>fibroin heavy chain-like</t>
+          <t>uncharacterized LOC129231303</t>
         </is>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>N5.HOG0082627</t>
+          <t>N5.HOG0088797</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
@@ -14160,17 +14160,17 @@
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>129231303</t>
+          <t>129224649</t>
         </is>
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>GO:0006364 [Name: rRNA processing]; GO:0005634 [Name: nucleus]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E534" t="inlineStr">
         <is>
-          <t>uncharacterized LOC129231303</t>
+          <t>collagen alpha-1(II) chain-like</t>
         </is>
       </c>
     </row>
@@ -14187,7 +14187,7 @@
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>129224649</t>
+          <t>129224650</t>
         </is>
       </c>
       <c r="D535" t="inlineStr">
@@ -14197,14 +14197,14 @@
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>collagen alpha-1(II) chain-like</t>
+          <t>fibroin heavy chain-like</t>
         </is>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>N5.HOG0088797</t>
+          <t>N5.HOG0107271</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
@@ -14231,7 +14231,7 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>N5.HOG0107271</t>
+          <t>N5.HOG0107302</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
@@ -14241,7 +14241,7 @@
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>129224650</t>
+          <t>129223990</t>
         </is>
       </c>
       <c r="D537" t="inlineStr">
@@ -14258,7 +14258,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>N5.HOG0107302</t>
+          <t>N5.HOG0107306</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -14285,7 +14285,7 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>N5.HOG0107306</t>
+          <t>N5.HOG0107320</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
@@ -14295,7 +14295,7 @@
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>129223990</t>
+          <t>129224650</t>
         </is>
       </c>
       <c r="D539" t="inlineStr">
@@ -14312,7 +14312,7 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>N5.HOG0107320</t>
+          <t>N5.HOG0107399</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
@@ -14339,7 +14339,7 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>N5.HOG0107399</t>
+          <t>N5.HOG0107440</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
@@ -14366,34 +14366,34 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>N5.HOG0107440</t>
+          <t>N5.HOG0023120</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>silk_genes, spidroins</t>
+          <t>relaxed, loss_50_orb</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>129224650</t>
+          <t>129228628</t>
         </is>
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GO:0016020 [Name: membrane]</t>
         </is>
       </c>
       <c r="E542" t="inlineStr">
         <is>
-          <t>fibroin heavy chain-like</t>
+          <t>solute carrier family 35 member G1-like</t>
         </is>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>N5.HOG0023120</t>
+          <t>N5.HOG0030279</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
@@ -14403,24 +14403,24 @@
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>129228628</t>
+          <t>129228677</t>
         </is>
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>GO:0016020 [Name: membrane]</t>
+          <t>GO:0005765 [Name: lysosomal membrane]; GO:0005886 [Name: plasma membrane]; GO:0072345 [Name: NAADP-sensitive calcium-release channel activity]</t>
         </is>
       </c>
       <c r="E543" t="inlineStr">
         <is>
-          <t>solute carrier family 35 member G1-like</t>
+          <t>mucolipin-3-like</t>
         </is>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>N5.HOG0030279</t>
+          <t>N5.HOG0030390</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
@@ -14430,24 +14430,24 @@
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>129228677</t>
+          <t>129233289</t>
         </is>
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>GO:0005765 [Name: lysosomal membrane]; GO:0005886 [Name: plasma membrane]; GO:0072345 [Name: NAADP-sensitive calcium-release channel activity]</t>
+          <t>GO:0036424 [Name: L-phosphoserine phosphatase activity]; GO:0006564 [Name: L-serine biosynthetic process]; GO:0005737 [Name: cytoplasm]; GO:0016311 [Name: dephosphorylation]; GO:0000287 [Name: magnesium ion binding]</t>
         </is>
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>mucolipin-3-like</t>
+          <t>phosphoserine phosphatase-like</t>
         </is>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>N5.HOG0030390</t>
+          <t>N5.HOG0034442</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
@@ -14457,24 +14457,24 @@
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>129233289</t>
+          <t>129225554</t>
         </is>
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>GO:0036424 [Name: L-phosphoserine phosphatase activity]; GO:0006564 [Name: L-serine biosynthetic process]; GO:0005737 [Name: cytoplasm]; GO:0016311 [Name: dephosphorylation]; GO:0000287 [Name: magnesium ion binding]</t>
+          <t>GO:0005634 [Name: nucleus]; GO:0003677 [Name: DNA binding]</t>
         </is>
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>phosphoserine phosphatase-like</t>
+          <t>BUB3-interacting and GLEBS motif-containing protein ZNF207-like</t>
         </is>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>N5.HOG0034442</t>
+          <t>N5.HOG0035277</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
@@ -14484,24 +14484,24 @@
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>129225554</t>
+          <t>129227642</t>
         </is>
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>GO:0005634 [Name: nucleus]; GO:0003677 [Name: DNA binding]</t>
+          <t>GO:0006486 [Name: protein glycosylation]; GO:0016020 [Name: membrane]; GO:0016758 [Name: transferase activity, transferring hexosyl groups]</t>
         </is>
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>BUB3-interacting and GLEBS motif-containing protein ZNF207-like</t>
+          <t>beta-1,3-galactosyltransferase 1-like</t>
         </is>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>N5.HOG0035277</t>
+          <t>N5.HOG0038921</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
@@ -14511,24 +14511,24 @@
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>129227642</t>
+          <t>129218598</t>
         </is>
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>GO:0006486 [Name: protein glycosylation]; GO:0016020 [Name: membrane]; GO:0016758 [Name: transferase activity, transferring hexosyl groups]</t>
+          <t>GO:0005509 [Name: calcium ion binding]</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>beta-1,3-galactosyltransferase 1-like</t>
+          <t>fibulin-1-like</t>
         </is>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>N5.HOG0038921</t>
+          <t>N5.HOG0040254</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
@@ -14538,24 +14538,24 @@
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>129218598</t>
+          <t>129235158</t>
         </is>
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>GO:0005509 [Name: calcium ion binding]</t>
+          <t>GO:0000785 [Name: chromatin]; GO:0008270 [Name: zinc ion binding]; GO:0004842 [Name: ubiquitin-protein transferase activity]; GO:0005654 [Name: nucleoplasm]; GO:0045893 [Name: positive regulation of transcription, DNA-templated]</t>
         </is>
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>fibulin-1-like</t>
+          <t>E3 ubiquitin-protein ligase TRIM33-like</t>
         </is>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>N5.HOG0040254</t>
+          <t>N5.HOG0041512</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
@@ -14565,24 +14565,24 @@
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>129235158</t>
+          <t>129226015</t>
         </is>
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>GO:0000785 [Name: chromatin]; GO:0008270 [Name: zinc ion binding]; GO:0004842 [Name: ubiquitin-protein transferase activity]; GO:0005654 [Name: nucleoplasm]; GO:0045893 [Name: positive regulation of transcription, DNA-templated]</t>
+          <t>GO:0009755 [Name: hormone-mediated signaling pathway]; GO:0051424 [Name: corticotropin-releasing hormone binding]; GO:0005615 [Name: extracellular space]; GO:0051460 [Name: negative regulation of corticotropin secretion]; GO:1900011 [Name: negative regulation of corticotropin-releasing hormone receptor activity]</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>E3 ubiquitin-protein ligase TRIM33-like</t>
+          <t>corticotropin-releasing factor-binding protein-like</t>
         </is>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>N5.HOG0041512</t>
+          <t>N5.HOG0041908</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
@@ -14592,24 +14592,24 @@
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>129226015</t>
+          <t>129217648</t>
         </is>
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>GO:0009755 [Name: hormone-mediated signaling pathway]; GO:0051424 [Name: corticotropin-releasing hormone binding]; GO:0005615 [Name: extracellular space]; GO:0051460 [Name: negative regulation of corticotropin secretion]; GO:1900011 [Name: negative regulation of corticotropin-releasing hormone receptor activity]</t>
+          <t>GO:0030431 [Name: sleep]; GO:1903818 [Name: positive regulation of voltage-gated potassium channel activity]; GO:0032222 [Name: regulation of synaptic transmission, cholinergic]</t>
         </is>
       </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>corticotropin-releasing factor-binding protein-like</t>
+          <t>glycosylphosphatidylinositol anchored membrane protein boudin</t>
         </is>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>N5.HOG0041908</t>
+          <t>N5.HOG0042922</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
@@ -14619,24 +14619,24 @@
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>129217648</t>
+          <t>129226563</t>
         </is>
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>GO:0030431 [Name: sleep]; GO:1903818 [Name: positive regulation of voltage-gated potassium channel activity]; GO:0032222 [Name: regulation of synaptic transmission, cholinergic]</t>
+          <t>GO:0003729 [Name: mRNA binding]; GO:0005737 [Name: cytoplasm]; GO:0005634 [Name: nucleus]</t>
         </is>
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>glycosylphosphatidylinositol anchored membrane protein boudin</t>
+          <t>myelin expression factor 2-like</t>
         </is>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>N5.HOG0042922</t>
+          <t>N5.HOG0045324</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
@@ -14646,24 +14646,24 @@
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>129226563</t>
+          <t>129217616</t>
         </is>
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>GO:0003729 [Name: mRNA binding]; GO:0005737 [Name: cytoplasm]; GO:0005634 [Name: nucleus]</t>
+          <t>GO:0004402 [Name: histone acetyltransferase activity]; GO:0006355 [Name: regulation of transcription, DNA-templated]</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>myelin expression factor 2-like</t>
+          <t>males absent on the first</t>
         </is>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>N5.HOG0045324</t>
+          <t>N5.HOG0049543</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
@@ -14673,24 +14673,24 @@
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>129217616</t>
+          <t>129229274</t>
         </is>
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>GO:0004402 [Name: histone acetyltransferase activity]; GO:0006355 [Name: regulation of transcription, DNA-templated]</t>
+          <t>GO:0005634 [Name: nucleus]; GO:0030154 [Name: cell differentiation]; GO:0000977 [Name: RNA polymerase II regulatory region sequence-specific DNA binding]; GO:0000785 [Name: chromatin]; GO:0006357 [Name: regulation of transcription from RNA polymerase II promoter]; GO:2000134 [Name: negative regulation of G1/S transition of mitotic cell cycle]; GO:0005667 [Name: transcription factor complex]</t>
         </is>
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>males absent on the first</t>
+          <t>retinoblastoma-like protein 1</t>
         </is>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>N5.HOG0049543</t>
+          <t>N5.HOG0054505</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
@@ -14700,24 +14700,24 @@
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>129229274</t>
+          <t>129229697</t>
         </is>
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>GO:0005634 [Name: nucleus]; GO:0030154 [Name: cell differentiation]; GO:0000977 [Name: RNA polymerase II regulatory region sequence-specific DNA binding]; GO:0000785 [Name: chromatin]; GO:0006357 [Name: regulation of transcription from RNA polymerase II promoter]; GO:2000134 [Name: negative regulation of G1/S transition of mitotic cell cycle]; GO:0005667 [Name: transcription factor complex]</t>
+          <t>GO:0072487 [Name: MSL complex]</t>
         </is>
       </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>retinoblastoma-like protein 1</t>
+          <t>male-specific lethal 1</t>
         </is>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>N5.HOG0054505</t>
+          <t>N5.HOG0057479</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
@@ -14727,24 +14727,24 @@
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>129229697</t>
+          <t>129227846</t>
         </is>
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>GO:0072487 [Name: MSL complex]</t>
+          <t>GO:0055085 [Name: transmembrane transport]; GO:0016020 [Name: membrane]; GO:0022857 [Name: transmembrane transporter activity]</t>
         </is>
       </c>
       <c r="E555" t="inlineStr">
         <is>
-          <t>male-specific lethal 1</t>
+          <t>organic cation transporter protein-like</t>
         </is>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>N5.HOG0057479</t>
+          <t>N5.HOG0057707</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
@@ -14754,24 +14754,24 @@
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>129227846</t>
+          <t>129218136</t>
         </is>
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>GO:0055085 [Name: transmembrane transport]; GO:0016020 [Name: membrane]; GO:0022857 [Name: transmembrane transporter activity]</t>
+          <t>GO:0032040 [Name: small-subunit processome]; GO:0005730 [Name: nucleolus]; GO:0003723 [Name: RNA binding]; GO:0006364 [Name: rRNA processing]</t>
         </is>
       </c>
       <c r="E556" t="inlineStr">
         <is>
-          <t>organic cation transporter protein-like</t>
+          <t>uncharacterized LOC129218136</t>
         </is>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>N5.HOG0057707</t>
+          <t>N5.HOG0058815</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
@@ -14781,24 +14781,24 @@
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>129218136</t>
+          <t>129224719</t>
         </is>
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>GO:0032040 [Name: small-subunit processome]; GO:0005730 [Name: nucleolus]; GO:0003723 [Name: RNA binding]; GO:0006364 [Name: rRNA processing]</t>
+          <t>GO:0004421 [Name: hydroxymethylglutaryl-CoA synthase activity]; GO:0010142 [Name: farnesyl diphosphate biosynthetic process, mevalonate pathway]; GO:0006084 [Name: acetyl-CoA metabolic process]</t>
         </is>
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>uncharacterized LOC129218136</t>
+          <t>hydroxymethylglutaryl-CoA synthase 1-like</t>
         </is>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>N5.HOG0058815</t>
+          <t>N5.HOG0059999</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
@@ -14808,24 +14808,24 @@
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>129224719</t>
+          <t>129218407</t>
         </is>
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>GO:0004421 [Name: hydroxymethylglutaryl-CoA synthase activity]; GO:0010142 [Name: farnesyl diphosphate biosynthetic process, mevalonate pathway]; GO:0006084 [Name: acetyl-CoA metabolic process]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>hydroxymethylglutaryl-CoA synthase 1-like</t>
+          <t>uncharacterized LOC129218407</t>
         </is>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>N5.HOG0059999</t>
+          <t>N5.HOG0062116</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
@@ -14835,24 +14835,24 @@
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>129218407</t>
+          <t>129223940</t>
         </is>
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GO:0005737 [Name: cytoplasm]; GO:0005739 [Name: mitochondrion]; GO:0016407 [Name: acetyltransferase activity]; GO:0031405 [Name: lipoic acid binding]</t>
         </is>
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>uncharacterized LOC129218407</t>
+          <t>lipoamide acyltransferase component of branched-chain alpha-keto acid dehydrogenase complex, mitochondrial-like</t>
         </is>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>N5.HOG0062116</t>
+          <t>N5.HOG0066090</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
@@ -14862,24 +14862,24 @@
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>129223940</t>
+          <t>129218525</t>
         </is>
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>GO:0005737 [Name: cytoplasm]; GO:0005739 [Name: mitochondrion]; GO:0016407 [Name: acetyltransferase activity]; GO:0031405 [Name: lipoic acid binding]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>lipoamide acyltransferase component of branched-chain alpha-keto acid dehydrogenase complex, mitochondrial-like</t>
+          <t>putative uncharacterized protein DDB_G0271982</t>
         </is>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>N5.HOG0066090</t>
+          <t>N5.HOG0066491</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
@@ -14889,7 +14889,7 @@
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>129218525</t>
+          <t>129216083</t>
         </is>
       </c>
       <c r="D561" t="inlineStr">
@@ -14899,14 +14899,14 @@
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>putative uncharacterized protein DDB_G0271982</t>
+          <t>uncharacterized LOC129216083</t>
         </is>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>N5.HOG0066491</t>
+          <t>N5.HOG0067752</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
@@ -14914,26 +14914,14 @@
           <t>relaxed, loss_50_orb</t>
         </is>
       </c>
-      <c r="C562" t="inlineStr">
-        <is>
-          <t>129216083</t>
-        </is>
-      </c>
-      <c r="D562" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E562" t="inlineStr">
-        <is>
-          <t>uncharacterized LOC129216083</t>
-        </is>
-      </c>
+      <c r="C562" t="inlineStr"/>
+      <c r="D562" t="inlineStr"/>
+      <c r="E562" t="inlineStr"/>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>N5.HOG0067752</t>
+          <t>N5.HOG0068495</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
@@ -14941,34 +14929,46 @@
           <t>relaxed, loss_50_orb</t>
         </is>
       </c>
-      <c r="C563" t="inlineStr"/>
-      <c r="D563" t="inlineStr"/>
-      <c r="E563" t="inlineStr"/>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>129217242</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>uncharacterized LOC129217242</t>
+        </is>
+      </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>N5.HOG0068495</t>
+          <t>N5.HOG0002076</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>relaxed, loss_50_orb</t>
+          <t>silk_genes, loss_50_nonorb</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>129217242</t>
+          <t>129217825</t>
         </is>
       </c>
       <c r="D564" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GO:0008010 [Name: structural constituent of chitin-based larval cuticle]</t>
         </is>
       </c>
       <c r="E564" t="inlineStr">
         <is>
-          <t>uncharacterized LOC129217242</t>
+          <t>cuticle protein-like</t>
         </is>
       </c>
     </row>
@@ -14983,21 +14983,9 @@
           <t>silk_genes, loss_50_nonorb</t>
         </is>
       </c>
-      <c r="C565" t="inlineStr">
-        <is>
-          <t>129217825</t>
-        </is>
-      </c>
-      <c r="D565" t="inlineStr">
-        <is>
-          <t>GO:0008010 [Name: structural constituent of chitin-based larval cuticle]</t>
-        </is>
-      </c>
-      <c r="E565" t="inlineStr">
-        <is>
-          <t>cuticle protein-like</t>
-        </is>
-      </c>
+      <c r="C565" t="inlineStr"/>
+      <c r="D565" t="inlineStr"/>
+      <c r="E565" t="inlineStr"/>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
@@ -15010,14 +14998,26 @@
           <t>silk_genes, loss_50_nonorb</t>
         </is>
       </c>
-      <c r="C566" t="inlineStr"/>
-      <c r="D566" t="inlineStr"/>
-      <c r="E566" t="inlineStr"/>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>129221291</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>GO:0008010 [Name: structural constituent of chitin-based larval cuticle]</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>cuticle protein 10.9-like</t>
+        </is>
+      </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>N5.HOG0002076</t>
+          <t>N5.HOG0006071</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
@@ -15027,24 +15027,24 @@
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>129221291</t>
+          <t>129231370</t>
         </is>
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>GO:0008010 [Name: structural constituent of chitin-based larval cuticle]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E567" t="inlineStr">
         <is>
-          <t>cuticle protein 10.9-like</t>
+          <t>arylsulfatase B-like</t>
         </is>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>N5.HOG0006071</t>
+          <t>N5.HOG0007085</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
@@ -15052,21 +15052,9 @@
           <t>silk_genes, loss_50_nonorb</t>
         </is>
       </c>
-      <c r="C568" t="inlineStr">
-        <is>
-          <t>129231370</t>
-        </is>
-      </c>
-      <c r="D568" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E568" t="inlineStr">
-        <is>
-          <t>arylsulfatase B-like</t>
-        </is>
-      </c>
+      <c r="C568" t="inlineStr"/>
+      <c r="D568" t="inlineStr"/>
+      <c r="E568" t="inlineStr"/>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
@@ -15079,14 +15067,26 @@
           <t>silk_genes, loss_50_nonorb</t>
         </is>
       </c>
-      <c r="C569" t="inlineStr"/>
-      <c r="D569" t="inlineStr"/>
-      <c r="E569" t="inlineStr"/>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>129229398</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>GO:0005764 [Name: lysosome]; GO:0051603 [Name: proteolysis involved in cellular protein catabolic process]; GO:0004197 [Name: cysteine-type endopeptidase activity]; GO:0005615 [Name: extracellular space]</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>procathepsin L-like</t>
+        </is>
+      </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>N5.HOG0007085</t>
+          <t>N5.HOG0009320</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
@@ -15096,17 +15096,17 @@
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>129229398</t>
+          <t>129232232</t>
         </is>
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>GO:0005764 [Name: lysosome]; GO:0051603 [Name: proteolysis involved in cellular protein catabolic process]; GO:0004197 [Name: cysteine-type endopeptidase activity]; GO:0005615 [Name: extracellular space]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E570" t="inlineStr">
         <is>
-          <t>procathepsin L-like</t>
+          <t>uncharacterized LOC129232232</t>
         </is>
       </c>
     </row>
@@ -15123,7 +15123,7 @@
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>129232232</t>
+          <t>129232236</t>
         </is>
       </c>
       <c r="D571" t="inlineStr">
@@ -15133,7 +15133,7 @@
       </c>
       <c r="E571" t="inlineStr">
         <is>
-          <t>uncharacterized LOC129232232</t>
+          <t>protein ABHD11-like</t>
         </is>
       </c>
     </row>
@@ -15150,12 +15150,12 @@
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>129232236</t>
+          <t>129223140</t>
         </is>
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GO:0003824 [Name: catalytic activity]</t>
         </is>
       </c>
       <c r="E572" t="inlineStr">
@@ -15177,12 +15177,12 @@
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>129223140</t>
+          <t>129217280</t>
         </is>
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>GO:0003824 [Name: catalytic activity]</t>
+          <t>GO:0005739 [Name: mitochondrion]; GO:0003824 [Name: catalytic activity]</t>
         </is>
       </c>
       <c r="E573" t="inlineStr">
@@ -15204,12 +15204,12 @@
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>129217280</t>
+          <t>129223149</t>
         </is>
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>GO:0005739 [Name: mitochondrion]; GO:0003824 [Name: catalytic activity]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E574" t="inlineStr">
@@ -15221,7 +15221,7 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>N5.HOG0009320</t>
+          <t>N5.HOG0009968</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
@@ -15231,17 +15231,17 @@
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>129223149</t>
+          <t>129227814</t>
         </is>
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GO:0055085 [Name: transmembrane transport]; GO:0022857 [Name: transmembrane transporter activity]</t>
         </is>
       </c>
       <c r="E575" t="inlineStr">
         <is>
-          <t>protein ABHD11-like</t>
+          <t>protein unc-93 homolog A-like</t>
         </is>
       </c>
     </row>
@@ -15258,12 +15258,12 @@
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>129227814</t>
+          <t>129227550</t>
         </is>
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>GO:0055085 [Name: transmembrane transport]; GO:0022857 [Name: transmembrane transporter activity]</t>
+          <t>GO:0005886 [Name: plasma membrane]; GO:0043266 [Name: regulation of potassium ion transport]; GO:0055120 [Name: striated muscle dense body]; GO:0006937 [Name: regulation of muscle contraction]; GO:0015459 [Name: potassium channel regulator activity]</t>
         </is>
       </c>
       <c r="E576" t="inlineStr">
@@ -15275,7 +15275,7 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>N5.HOG0009968</t>
+          <t>N5.HOG0013780</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
@@ -15285,24 +15285,24 @@
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>129227550</t>
+          <t>129218447</t>
         </is>
       </c>
       <c r="D577" t="inlineStr">
         <is>
-          <t>GO:0005886 [Name: plasma membrane]; GO:0043266 [Name: regulation of potassium ion transport]; GO:0055120 [Name: striated muscle dense body]; GO:0006937 [Name: regulation of muscle contraction]; GO:0015459 [Name: potassium channel regulator activity]</t>
+          <t>GO:0080019 [Name: fatty-acyl-CoA reductase (alcohol-forming) activity]; GO:0035336 [Name: long-chain fatty-acyl-CoA metabolic process]; GO:0005777 [Name: peroxisome]</t>
         </is>
       </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t>protein unc-93 homolog A-like</t>
+          <t>putative fatty acyl-CoA reductase CG5065</t>
         </is>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>N5.HOG0013780</t>
+          <t>N5.HOG0030774</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
@@ -15312,24 +15312,24 @@
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>129218447</t>
+          <t>129216762</t>
         </is>
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>GO:0080019 [Name: fatty-acyl-CoA reductase (alcohol-forming) activity]; GO:0035336 [Name: long-chain fatty-acyl-CoA metabolic process]; GO:0005777 [Name: peroxisome]</t>
+          <t>GO:0007165 [Name: signal transduction]; GO:0046839 [Name: phospholipid dephosphorylation]; GO:0008195 [Name: phosphatidate phosphatase activity]; GO:0006644 [Name: phospholipid metabolic process]</t>
         </is>
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>putative fatty acyl-CoA reductase CG5065</t>
+          <t>putative phosphatidate phosphatase</t>
         </is>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>N5.HOG0030774</t>
+          <t>N5.HOG0031117</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
@@ -15339,24 +15339,24 @@
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>129216762</t>
+          <t>129218435</t>
         </is>
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>GO:0007165 [Name: signal transduction]; GO:0046839 [Name: phospholipid dephosphorylation]; GO:0008195 [Name: phosphatidate phosphatase activity]; GO:0006644 [Name: phospholipid metabolic process]</t>
+          <t>GO:0003924 [Name: GTPase activity]; GO:0005525 [Name: GTP binding]; GO:0007029 [Name: endoplasmic reticulum organization]; GO:0051260 [Name: protein homooligomerization]</t>
         </is>
       </c>
       <c r="E579" t="inlineStr">
         <is>
-          <t>putative phosphatidate phosphatase</t>
+          <t>atlastin-2-like</t>
         </is>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>N5.HOG0031117</t>
+          <t>N5.HOG0031505</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
@@ -15366,24 +15366,24 @@
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>129218435</t>
+          <t>129232340</t>
         </is>
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>GO:0003924 [Name: GTPase activity]; GO:0005525 [Name: GTP binding]; GO:0007029 [Name: endoplasmic reticulum organization]; GO:0051260 [Name: protein homooligomerization]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E580" t="inlineStr">
         <is>
-          <t>atlastin-2-like</t>
+          <t>uncharacterized LOC129232340</t>
         </is>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>N5.HOG0031505</t>
+          <t>N5.HOG0031662</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
@@ -15393,24 +15393,24 @@
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>129232340</t>
+          <t>129219856</t>
         </is>
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GO:0005515 [Name: protein binding]; GO:0005615 [Name: extracellular space]; GO:0006979 [Name: response to oxidative stress]; GO:0004601 [Name: peroxidase activity]; GO:0020037 [Name: heme binding]</t>
         </is>
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>uncharacterized LOC129232340</t>
+          <t>peroxidasin-like</t>
         </is>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>N5.HOG0031662</t>
+          <t>N5.HOG0034469</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
@@ -15420,24 +15420,24 @@
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>129219856</t>
+          <t>129219926</t>
         </is>
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>GO:0005515 [Name: protein binding]; GO:0005615 [Name: extracellular space]; GO:0006979 [Name: response to oxidative stress]; GO:0004601 [Name: peroxidase activity]; GO:0020037 [Name: heme binding]</t>
+          <t>GO:0004586 [Name: ornithine decarboxylase activity]; GO:0005737 [Name: cytoplasm]; GO:0033387 [Name: putrescine biosynthetic process from ornithine]</t>
         </is>
       </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>peroxidasin-like</t>
+          <t>antizyme inhibitor 2-like</t>
         </is>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>N5.HOG0034469</t>
+          <t>N5.HOG0037868</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
@@ -15447,17 +15447,17 @@
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>129219926</t>
+          <t>129220240</t>
         </is>
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>GO:0004586 [Name: ornithine decarboxylase activity]; GO:0005737 [Name: cytoplasm]; GO:0033387 [Name: putrescine biosynthetic process from ornithine]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E583" t="inlineStr">
         <is>
-          <t>antizyme inhibitor 2-like</t>
+          <t>uncharacterized LOC129220240</t>
         </is>
       </c>
     </row>
@@ -15474,24 +15474,24 @@
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>129220240</t>
+          <t>129220023</t>
         </is>
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GO:0016020 [Name: membrane]; GO:0071805 [Name: potassium ion transmembrane transport]; GO:0030322 [Name: stabilization of membrane potential]; GO:0022841 [Name: potassium ion leak channel activity]</t>
         </is>
       </c>
       <c r="E584" t="inlineStr">
         <is>
-          <t>uncharacterized LOC129220240</t>
+          <t>TWiK family of potassium channels protein 7-like</t>
         </is>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>N5.HOG0037868</t>
+          <t>N5.HOG0039801</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
@@ -15501,24 +15501,24 @@
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>129220023</t>
+          <t>129224594</t>
         </is>
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>GO:0016020 [Name: membrane]; GO:0071805 [Name: potassium ion transmembrane transport]; GO:0030322 [Name: stabilization of membrane potential]; GO:0022841 [Name: potassium ion leak channel activity]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E585" t="inlineStr">
         <is>
-          <t>TWiK family of potassium channels protein 7-like</t>
+          <t>uncharacterized LOC129224594</t>
         </is>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>N5.HOG0039801</t>
+          <t>N5.HOG0044352</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
@@ -15528,24 +15528,24 @@
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>129224594</t>
+          <t>129231844</t>
         </is>
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GO:0000978 [Name: RNA polymerase II core promoter proximal region sequence-specific DNA binding]; GO:0000981 [Name: RNA polymerase II transcription factor activity, sequence-specific DNA binding]; GO:0005634 [Name: nucleus]; GO:0006357 [Name: regulation of transcription from RNA polymerase II promoter]</t>
         </is>
       </c>
       <c r="E586" t="inlineStr">
         <is>
-          <t>uncharacterized LOC129224594</t>
+          <t>homeobox protein abdominal-B-like</t>
         </is>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>N5.HOG0044352</t>
+          <t>N5.HOG0055488</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
@@ -15555,24 +15555,24 @@
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>129231844</t>
+          <t>129229319</t>
         </is>
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>GO:0000978 [Name: RNA polymerase II core promoter proximal region sequence-specific DNA binding]; GO:0000981 [Name: RNA polymerase II transcription factor activity, sequence-specific DNA binding]; GO:0005634 [Name: nucleus]; GO:0006357 [Name: regulation of transcription from RNA polymerase II promoter]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>homeobox protein abdominal-B-like</t>
+          <t>uncharacterized LOC129229319</t>
         </is>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>N5.HOG0055488</t>
+          <t>N5.HOG0062576</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
@@ -15582,24 +15582,24 @@
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>129229319</t>
+          <t>129220095</t>
         </is>
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GO:0014059 [Name: regulation of dopamine secretion]; GO:0005509 [Name: calcium ion binding]; GO:0017156 [Name: calcium ion regulated exocytosis]; GO:0005544 [Name: calcium-dependent phospholipid binding]; GO:0000149 [Name: SNARE binding]; GO:0001786 [Name: phosphatidylserine binding]; GO:0030276 [Name: clathrin binding]; GO:0071277 [Name: cellular response to calcium ion]; GO:0017158 [Name: regulation of calcium ion-dependent exocytosis]</t>
         </is>
       </c>
       <c r="E588" t="inlineStr">
         <is>
-          <t>uncharacterized LOC129229319</t>
+          <t>synaptotagmin-7-like</t>
         </is>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>N5.HOG0062576</t>
+          <t>N5.HOG0062761</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
@@ -15609,24 +15609,24 @@
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>129220095</t>
+          <t>129230333</t>
         </is>
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>GO:0014059 [Name: regulation of dopamine secretion]; GO:0005509 [Name: calcium ion binding]; GO:0017156 [Name: calcium ion regulated exocytosis]; GO:0005544 [Name: calcium-dependent phospholipid binding]; GO:0000149 [Name: SNARE binding]; GO:0001786 [Name: phosphatidylserine binding]; GO:0030276 [Name: clathrin binding]; GO:0071277 [Name: cellular response to calcium ion]; GO:0017158 [Name: regulation of calcium ion-dependent exocytosis]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E589" t="inlineStr">
         <is>
-          <t>synaptotagmin-7-like</t>
+          <t>titin-like</t>
         </is>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>N5.HOG0062761</t>
+          <t>N5.HOG0068491</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
@@ -15636,17 +15636,17 @@
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>129230333</t>
+          <t>129232599</t>
         </is>
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GO:0016791 [Name: phosphatase activity]; GO:0016311 [Name: dephosphorylation]</t>
         </is>
       </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t>titin-like</t>
+          <t>prostatic acid phosphatase-like</t>
         </is>
       </c>
     </row>
@@ -15663,24 +15663,24 @@
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>129232599</t>
+          <t>129233247</t>
         </is>
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>GO:0016791 [Name: phosphatase activity]; GO:0016311 [Name: dephosphorylation]</t>
+          <t>GO:0016311 [Name: dephosphorylation]; GO:0016791 [Name: phosphatase activity]</t>
         </is>
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>prostatic acid phosphatase-like</t>
+          <t>testicular acid phosphatase homolog</t>
         </is>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>N5.HOG0068491</t>
+          <t>N5.HOG0069111</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
@@ -15690,24 +15690,24 @@
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>129233247</t>
+          <t>129225146</t>
         </is>
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>GO:0016311 [Name: dephosphorylation]; GO:0016791 [Name: phosphatase activity]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E592" t="inlineStr">
         <is>
-          <t>testicular acid phosphatase homolog</t>
+          <t>uncharacterized LOC129225146</t>
         </is>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>N5.HOG0069111</t>
+          <t>N5.HOG0069490</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
@@ -15717,7 +15717,7 @@
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>129225146</t>
+          <t>129217276</t>
         </is>
       </c>
       <c r="D593" t="inlineStr">
@@ -15727,14 +15727,14 @@
       </c>
       <c r="E593" t="inlineStr">
         <is>
-          <t>uncharacterized LOC129225146</t>
+          <t>RNA-binding protein 33-like</t>
         </is>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>N5.HOG0069490</t>
+          <t>N5.HOG0070495</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
@@ -15744,7 +15744,7 @@
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>129217276</t>
+          <t>129224616</t>
         </is>
       </c>
       <c r="D594" t="inlineStr">
@@ -15754,41 +15754,41 @@
       </c>
       <c r="E594" t="inlineStr">
         <is>
-          <t>RNA-binding protein 33-like</t>
+          <t>uncharacterized LOC129224616</t>
         </is>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>N5.HOG0070495</t>
+          <t>N5.HOG0028630</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>silk_genes, loss_50_nonorb</t>
+          <t>relaxed, dup_50_nonorb</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>129224616</t>
+          <t>129219697</t>
         </is>
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GO:0005509 [Name: calcium ion binding]; GO:0047498 [Name: calcium-dependent phospholipase A2 activity]; GO:0006644 [Name: phospholipid metabolic process]; GO:0005543 [Name: phospholipid binding]; GO:0016042 [Name: lipid catabolic process]; GO:0050482 [Name: arachidonic acid secretion]</t>
         </is>
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>uncharacterized LOC129224616</t>
+          <t>neutral phospholipase A2 3-like</t>
         </is>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>N5.HOG0028630</t>
+          <t>N5.HOG0035751</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
@@ -15798,24 +15798,24 @@
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>129219697</t>
+          <t>129227580</t>
         </is>
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>GO:0005509 [Name: calcium ion binding]; GO:0047498 [Name: calcium-dependent phospholipase A2 activity]; GO:0006644 [Name: phospholipid metabolic process]; GO:0005543 [Name: phospholipid binding]; GO:0016042 [Name: lipid catabolic process]; GO:0050482 [Name: arachidonic acid secretion]</t>
+          <t>GO:0003729 [Name: mRNA binding]; GO:0006397 [Name: mRNA processing]; GO:0043484 [Name: regulation of RNA splicing]; GO:0005634 [Name: nucleus]</t>
         </is>
       </c>
       <c r="E596" t="inlineStr">
         <is>
-          <t>neutral phospholipase A2 3-like</t>
+          <t>heterogeneous nuclear ribonucleoprotein L</t>
         </is>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>N5.HOG0035751</t>
+          <t>N5.HOG0037691</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
@@ -15825,24 +15825,24 @@
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>129227580</t>
+          <t>129219015</t>
         </is>
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>GO:0003729 [Name: mRNA binding]; GO:0006397 [Name: mRNA processing]; GO:0043484 [Name: regulation of RNA splicing]; GO:0005634 [Name: nucleus]</t>
+          <t>GO:0003333 [Name: amino acid transmembrane transport]; GO:0016020 [Name: membrane]; GO:0015179 [Name: L-amino acid transmembrane transporter activity]</t>
         </is>
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>heterogeneous nuclear ribonucleoprotein L</t>
+          <t>large neutral amino acids transporter small subunit 2-like</t>
         </is>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>N5.HOG0037691</t>
+          <t>N5.HOG0041902</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
@@ -15852,24 +15852,24 @@
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>129219015</t>
+          <t>129221955</t>
         </is>
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>GO:0003333 [Name: amino acid transmembrane transport]; GO:0016020 [Name: membrane]; GO:0015179 [Name: L-amino acid transmembrane transporter activity]</t>
+          <t>GO:0006357 [Name: regulation of transcription from RNA polymerase II promoter]; GO:0035102 [Name: PRC1 complex]</t>
         </is>
       </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>large neutral amino acids transporter small subunit 2-like</t>
+          <t>polycomb group RING finger protein 3-like</t>
         </is>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>N5.HOG0041902</t>
+          <t>N5.HOG0041972</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
@@ -15879,24 +15879,24 @@
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>129221955</t>
+          <t>129218389</t>
         </is>
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>GO:0006357 [Name: regulation of transcription from RNA polymerase II promoter]; GO:0035102 [Name: PRC1 complex]</t>
+          <t>GO:0005515 [Name: protein binding]</t>
         </is>
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>polycomb group RING finger protein 3-like</t>
+          <t>IDLSRF-like peptide</t>
         </is>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>N5.HOG0041972</t>
+          <t>N5.HOG0046571</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
@@ -15906,24 +15906,24 @@
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>129218389</t>
+          <t>129230982</t>
         </is>
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>GO:0005515 [Name: protein binding]</t>
+          <t>GO:0000209 [Name: protein polyubiquitination]; GO:0008592 [Name: regulation of Toll signaling pathway]; GO:0061630 [Name: ubiquitin protein ligase activity]; GO:0005515 [Name: protein binding]</t>
         </is>
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>IDLSRF-like peptide</t>
+          <t>E3 ubiquitin-protein ligase pellino</t>
         </is>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>N5.HOG0046571</t>
+          <t>N5.HOG0050702</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
@@ -15933,24 +15933,24 @@
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>129230982</t>
+          <t>129224238</t>
         </is>
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>GO:0000209 [Name: protein polyubiquitination]; GO:0008592 [Name: regulation of Toll signaling pathway]; GO:0061630 [Name: ubiquitin protein ligase activity]; GO:0005515 [Name: protein binding]</t>
+          <t>GO:0043491 [Name: protein kinase B signaling]; GO:0005942 [Name: phosphatidylinositol 3-kinase complex]; GO:0035005 [Name: 1-phosphatidylinositol-4-phosphate 3-kinase activity]; GO:0005886 [Name: plasma membrane]; GO:0048015 [Name: phosphatidylinositol-mediated signaling]; GO:0005737 [Name: cytoplasm]; GO:0016303 [Name: 1-phosphatidylinositol-3-kinase activity]; GO:0016477 [Name: cell migration]; GO:0036092 [Name: phosphatidylinositol-3-phosphate biosynthetic process]</t>
         </is>
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>E3 ubiquitin-protein ligase pellino</t>
+          <t>phosphatidylinositol 3-kinase 92E</t>
         </is>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>N5.HOG0050702</t>
+          <t>N5.HOG0054177</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
@@ -15960,24 +15960,24 @@
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>129224238</t>
+          <t>129234625</t>
         </is>
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>GO:0043491 [Name: protein kinase B signaling]; GO:0005942 [Name: phosphatidylinositol 3-kinase complex]; GO:0035005 [Name: 1-phosphatidylinositol-4-phosphate 3-kinase activity]; GO:0005886 [Name: plasma membrane]; GO:0048015 [Name: phosphatidylinositol-mediated signaling]; GO:0005737 [Name: cytoplasm]; GO:0016303 [Name: 1-phosphatidylinositol-3-kinase activity]; GO:0016477 [Name: cell migration]; GO:0036092 [Name: phosphatidylinositol-3-phosphate biosynthetic process]</t>
+          <t>GO:0006508 [Name: proteolysis]; GO:0004185 [Name: serine-type carboxypeptidase activity]</t>
         </is>
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>phosphatidylinositol 3-kinase 92E</t>
+          <t>retinoid-inducible serine carboxypeptidase-like</t>
         </is>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>N5.HOG0054177</t>
+          <t>N5.HOG0054642</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
@@ -15985,26 +15985,14 @@
           <t>relaxed, dup_50_nonorb</t>
         </is>
       </c>
-      <c r="C603" t="inlineStr">
-        <is>
-          <t>129234625</t>
-        </is>
-      </c>
-      <c r="D603" t="inlineStr">
-        <is>
-          <t>GO:0006508 [Name: proteolysis]; GO:0004185 [Name: serine-type carboxypeptidase activity]</t>
-        </is>
-      </c>
-      <c r="E603" t="inlineStr">
-        <is>
-          <t>retinoid-inducible serine carboxypeptidase-like</t>
-        </is>
-      </c>
+      <c r="C603" t="inlineStr"/>
+      <c r="D603" t="inlineStr"/>
+      <c r="E603" t="inlineStr"/>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>N5.HOG0054642</t>
+          <t>N5.HOG0055615</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
@@ -16012,9 +16000,21 @@
           <t>relaxed, dup_50_nonorb</t>
         </is>
       </c>
-      <c r="C604" t="inlineStr"/>
-      <c r="D604" t="inlineStr"/>
-      <c r="E604" t="inlineStr"/>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>129224434</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>GO:0005615 [Name: extracellular space]; GO:0005783 [Name: endoplasmic reticulum]; GO:0071542 [Name: dopaminergic neuron differentiation]; GO:0031175 [Name: neuron projection development]</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>mesencephalic astrocyte-derived neurotrophic factor homolog</t>
+        </is>
+      </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
@@ -16029,12 +16029,12 @@
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>129224434</t>
+          <t>129231328</t>
         </is>
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>GO:0005615 [Name: extracellular space]; GO:0005783 [Name: endoplasmic reticulum]; GO:0071542 [Name: dopaminergic neuron differentiation]; GO:0031175 [Name: neuron projection development]</t>
+          <t>GO:0005783 [Name: endoplasmic reticulum]; GO:0005615 [Name: extracellular space]; GO:0031175 [Name: neuron projection development]; GO:0071542 [Name: dopaminergic neuron differentiation]</t>
         </is>
       </c>
       <c r="E605" t="inlineStr">
@@ -16046,7 +16046,7 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>N5.HOG0055615</t>
+          <t>N5.HOG0056864</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
@@ -16056,24 +16056,24 @@
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>129231328</t>
+          <t>129231311</t>
         </is>
       </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>GO:0005783 [Name: endoplasmic reticulum]; GO:0005615 [Name: extracellular space]; GO:0031175 [Name: neuron projection development]; GO:0071542 [Name: dopaminergic neuron differentiation]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E606" t="inlineStr">
         <is>
-          <t>mesencephalic astrocyte-derived neurotrophic factor homolog</t>
+          <t>uncharacterized LOC129231311</t>
         </is>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>N5.HOG0056864</t>
+          <t>N5.HOG0058669</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
@@ -16083,24 +16083,24 @@
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>129231311</t>
+          <t>129229653</t>
         </is>
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GO:0000309 [Name: nicotinamide-nucleotide adenylyltransferase activity]; GO:0004515 [Name: nicotinate-nucleotide adenylyltransferase activity]; GO:0009435 [Name: NAD biosynthetic process]</t>
         </is>
       </c>
       <c r="E607" t="inlineStr">
         <is>
-          <t>uncharacterized LOC129231311</t>
+          <t>nicotinamide mononucleotide adenylyltransferase</t>
         </is>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>N5.HOG0058669</t>
+          <t>N5.HOG0062953</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
@@ -16110,24 +16110,24 @@
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>129229653</t>
+          <t>129232431</t>
         </is>
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>GO:0000309 [Name: nicotinamide-nucleotide adenylyltransferase activity]; GO:0004515 [Name: nicotinate-nucleotide adenylyltransferase activity]; GO:0009435 [Name: NAD biosynthetic process]</t>
+          <t>GO:0005634 [Name: nucleus]; GO:0000151 [Name: ubiquitin ligase complex]; GO:0000209 [Name: protein polyubiquitination]; GO:0005737 [Name: cytoplasm]; GO:0034450 [Name: ubiquitin-ubiquitin ligase activity]</t>
         </is>
       </c>
       <c r="E608" t="inlineStr">
         <is>
-          <t>nicotinamide mononucleotide adenylyltransferase</t>
+          <t>Ubiquitination factor E4A</t>
         </is>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>N5.HOG0062953</t>
+          <t>N5.HOG0066295</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
@@ -16137,24 +16137,24 @@
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>129232431</t>
+          <t>129222847</t>
         </is>
       </c>
       <c r="D609" t="inlineStr">
         <is>
-          <t>GO:0005634 [Name: nucleus]; GO:0000151 [Name: ubiquitin ligase complex]; GO:0000209 [Name: protein polyubiquitination]; GO:0005737 [Name: cytoplasm]; GO:0034450 [Name: ubiquitin-ubiquitin ligase activity]</t>
+          <t>GO:0008017 [Name: microtubule binding]; GO:0003777 [Name: microtubule motor activity]; GO:0007018 [Name: microtubule-based movement]; GO:0005524 [Name: ATP binding]</t>
         </is>
       </c>
       <c r="E609" t="inlineStr">
         <is>
-          <t>Ubiquitination factor E4A</t>
+          <t>kinesin-like protein 64D</t>
         </is>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>N5.HOG0066295</t>
+          <t>N5.HOG0066695</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
@@ -16164,24 +16164,24 @@
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>129222847</t>
+          <t>129229387</t>
         </is>
       </c>
       <c r="D610" t="inlineStr">
         <is>
-          <t>GO:0008017 [Name: microtubule binding]; GO:0003777 [Name: microtubule motor activity]; GO:0007018 [Name: microtubule-based movement]; GO:0005524 [Name: ATP binding]</t>
+          <t>GO:0005762 [Name: mitochondrial large ribosomal subunit]; GO:0005739 [Name: mitochondrion]</t>
         </is>
       </c>
       <c r="E610" t="inlineStr">
         <is>
-          <t>kinesin-like protein 64D</t>
+          <t>mitochondrial ribosomal protein L50</t>
         </is>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>N5.HOG0066695</t>
+          <t>N5.HOG0067719</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
@@ -16191,24 +16191,24 @@
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>129229387</t>
+          <t>129224429</t>
         </is>
       </c>
       <c r="D611" t="inlineStr">
         <is>
-          <t>GO:0005762 [Name: mitochondrial large ribosomal subunit]; GO:0005739 [Name: mitochondrion]</t>
+          <t>GO:0000785 [Name: chromatin]; GO:0016592 [Name: mediator complex]; GO:0003712 [Name: transcription cofactor activity]; GO:0045944 [Name: positive regulation of transcription from RNA polymerase II promoter]</t>
         </is>
       </c>
       <c r="E611" t="inlineStr">
         <is>
-          <t>mitochondrial ribosomal protein L50</t>
+          <t>mediator complex subunit 10</t>
         </is>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>N5.HOG0067719</t>
+          <t>N5.HOG0067771</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
@@ -16218,17 +16218,17 @@
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>129224429</t>
+          <t>129216246</t>
         </is>
       </c>
       <c r="D612" t="inlineStr">
         <is>
-          <t>GO:0000785 [Name: chromatin]; GO:0016592 [Name: mediator complex]; GO:0003712 [Name: transcription cofactor activity]; GO:0045944 [Name: positive regulation of transcription from RNA polymerase II promoter]</t>
+          <t>GO:0006406 [Name: mRNA export from nucleus]; GO:0005515 [Name: protein binding]; GO:0000445 [Name: THO complex part of transcription export complex]</t>
         </is>
       </c>
       <c r="E612" t="inlineStr">
         <is>
-          <t>mediator complex subunit 10</t>
+          <t>THO complex 3 homolog tex</t>
         </is>
       </c>
     </row>
@@ -16245,24 +16245,24 @@
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>129216246</t>
+          <t>129216247</t>
         </is>
       </c>
       <c r="D613" t="inlineStr">
         <is>
-          <t>GO:0006406 [Name: mRNA export from nucleus]; GO:0005515 [Name: protein binding]; GO:0000445 [Name: THO complex part of transcription export complex]</t>
+          <t>GO:0006633 [Name: fatty acid biosynthetic process]; GO:0000035 [Name: acyl binding]; GO:0005739 [Name: mitochondrion]; GO:0000036 [Name: ACP phosphopantetheine attachment site binding involved in fatty acid biosynthetic process]</t>
         </is>
       </c>
       <c r="E613" t="inlineStr">
         <is>
-          <t>THO complex 3 homolog tex</t>
+          <t>NADH dehydrogenase (ubiquinone) acyl carrier protein</t>
         </is>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>N5.HOG0067771</t>
+          <t>N5.HOG0068405</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
@@ -16272,24 +16272,24 @@
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>129216247</t>
+          <t>129217662</t>
         </is>
       </c>
       <c r="D614" t="inlineStr">
         <is>
-          <t>GO:0006633 [Name: fatty acid biosynthetic process]; GO:0000035 [Name: acyl binding]; GO:0005739 [Name: mitochondrion]; GO:0000036 [Name: ACP phosphopantetheine attachment site binding involved in fatty acid biosynthetic process]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E614" t="inlineStr">
         <is>
-          <t>NADH dehydrogenase (ubiquinone) acyl carrier protein</t>
+          <t>uncharacterized LOC129217662</t>
         </is>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>N5.HOG0068405</t>
+          <t>N5.HOG0069098</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
@@ -16297,26 +16297,14 @@
           <t>relaxed, dup_50_nonorb</t>
         </is>
       </c>
-      <c r="C615" t="inlineStr">
-        <is>
-          <t>129217662</t>
-        </is>
-      </c>
-      <c r="D615" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E615" t="inlineStr">
-        <is>
-          <t>uncharacterized LOC129217662</t>
-        </is>
-      </c>
+      <c r="C615" t="inlineStr"/>
+      <c r="D615" t="inlineStr"/>
+      <c r="E615" t="inlineStr"/>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>N5.HOG0069098</t>
+          <t>N5.HOG0069309</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
@@ -16324,41 +16312,53 @@
           <t>relaxed, dup_50_nonorb</t>
         </is>
       </c>
-      <c r="C616" t="inlineStr"/>
-      <c r="D616" t="inlineStr"/>
-      <c r="E616" t="inlineStr"/>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>129223070</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>GO:0046872 [Name: metal ion binding]</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>zinc finger CCCH domain-containing protein 10-like</t>
+        </is>
+      </c>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>N5.HOG0069309</t>
+          <t>N5.HOG0026858</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>relaxed, dup_50_nonorb</t>
+          <t>busted_ph_rev, loss_50_nonorb</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>129223070</t>
+          <t>129223269</t>
         </is>
       </c>
       <c r="D617" t="inlineStr">
         <is>
-          <t>GO:0046872 [Name: metal ion binding]</t>
+          <t>GO:0033540 [Name: fatty acid beta-oxidation using acyl-CoA oxidase]; GO:0005777 [Name: peroxisome]; GO:0005504 [Name: fatty acid binding]; GO:0071949 [Name: FAD binding]; GO:0055088 [Name: lipid homeostasis]; GO:0016402 [Name: pristanoyl-CoA oxidase activity]</t>
         </is>
       </c>
       <c r="E617" t="inlineStr">
         <is>
-          <t>zinc finger CCCH domain-containing protein 10-like</t>
+          <t>peroxisomal acyl-coenzyme A oxidase 3-like</t>
         </is>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>N5.HOG0026858</t>
+          <t>N5.HOG0030671</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
@@ -16368,24 +16368,24 @@
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>129223269</t>
+          <t>129228696</t>
         </is>
       </c>
       <c r="D618" t="inlineStr">
         <is>
-          <t>GO:0033540 [Name: fatty acid beta-oxidation using acyl-CoA oxidase]; GO:0005777 [Name: peroxisome]; GO:0005504 [Name: fatty acid binding]; GO:0071949 [Name: FAD binding]; GO:0055088 [Name: lipid homeostasis]; GO:0016402 [Name: pristanoyl-CoA oxidase activity]</t>
+          <t>GO:0005515 [Name: protein binding]; GO:0015347 [Name: sodium-independent organic anion transmembrane transporter activity]; GO:0043252 [Name: sodium-independent organic anion transport]; GO:0016020 [Name: membrane]; GO:0055085 [Name: transmembrane transport]</t>
         </is>
       </c>
       <c r="E618" t="inlineStr">
         <is>
-          <t>peroxisomal acyl-coenzyme A oxidase 3-like</t>
+          <t>solute carrier organic anion transporter family member 4A1-like</t>
         </is>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>N5.HOG0030671</t>
+          <t>N5.HOG0034845</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
@@ -16395,24 +16395,24 @@
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>129228696</t>
+          <t>129218819</t>
         </is>
       </c>
       <c r="D619" t="inlineStr">
         <is>
-          <t>GO:0005515 [Name: protein binding]; GO:0015347 [Name: sodium-independent organic anion transmembrane transporter activity]; GO:0043252 [Name: sodium-independent organic anion transport]; GO:0016020 [Name: membrane]; GO:0055085 [Name: transmembrane transport]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E619" t="inlineStr">
         <is>
-          <t>solute carrier organic anion transporter family member 4A1-like</t>
+          <t>uncharacterized LOC129218819</t>
         </is>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>N5.HOG0034845</t>
+          <t>N5.HOG0037747</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
@@ -16422,24 +16422,24 @@
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>129218819</t>
+          <t>129218101</t>
         </is>
       </c>
       <c r="D620" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GO:0019901 [Name: protein kinase binding]; GO:0005634 [Name: nucleus]; GO:0007165 [Name: signal transduction]; GO:0005737 [Name: cytoplasm]; GO:0031588 [Name: nucleotide-activated protein kinase complex]</t>
         </is>
       </c>
       <c r="E620" t="inlineStr">
         <is>
-          <t>uncharacterized LOC129218819</t>
+          <t>5'-AMP-activated protein kinase subunit beta-1-like</t>
         </is>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>N5.HOG0037747</t>
+          <t>N5.HOG0038057</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
@@ -16449,24 +16449,24 @@
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>129218101</t>
+          <t>129218449</t>
         </is>
       </c>
       <c r="D621" t="inlineStr">
         <is>
-          <t>GO:0019901 [Name: protein kinase binding]; GO:0005634 [Name: nucleus]; GO:0007165 [Name: signal transduction]; GO:0005737 [Name: cytoplasm]; GO:0031588 [Name: nucleotide-activated protein kinase complex]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E621" t="inlineStr">
         <is>
-          <t>5'-AMP-activated protein kinase subunit beta-1-like</t>
+          <t>protein SERAC1-like</t>
         </is>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>N5.HOG0038057</t>
+          <t>N5.HOG0040178</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
@@ -16476,17 +16476,17 @@
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>129218449</t>
+          <t>129234511</t>
         </is>
       </c>
       <c r="D622" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GO:0005515 [Name: protein binding]; GO:0019005 [Name: SCF ubiquitin ligase complex]; GO:0031146 [Name: SCF-dependent proteasomal ubiquitin-dependent protein catabolic process]</t>
         </is>
       </c>
       <c r="E622" t="inlineStr">
         <is>
-          <t>protein SERAC1-like</t>
+          <t>uncharacterized LOC129234511</t>
         </is>
       </c>
     </row>
@@ -16503,24 +16503,24 @@
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>129234511</t>
+          <t>129231632</t>
         </is>
       </c>
       <c r="D623" t="inlineStr">
         <is>
-          <t>GO:0005515 [Name: protein binding]; GO:0019005 [Name: SCF ubiquitin ligase complex]; GO:0031146 [Name: SCF-dependent proteasomal ubiquitin-dependent protein catabolic process]</t>
+          <t>GO:0019786 [Name: Atg8-specific protease activity]</t>
         </is>
       </c>
       <c r="E623" t="inlineStr">
         <is>
-          <t>uncharacterized LOC129234511</t>
+          <t>cysteine protease ATG4B-like</t>
         </is>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>N5.HOG0040178</t>
+          <t>N5.HOG0041159</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
@@ -16530,24 +16530,24 @@
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>129231632</t>
+          <t>129224730</t>
         </is>
       </c>
       <c r="D624" t="inlineStr">
         <is>
-          <t>GO:0019786 [Name: Atg8-specific protease activity]</t>
+          <t>GO:0005524 [Name: ATP binding]; GO:0004672 [Name: protein kinase activity]; GO:0006468 [Name: protein phosphorylation]</t>
         </is>
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>cysteine protease ATG4B-like</t>
+          <t>dual specificity mitogen-activated protein kinase kinase 1-like</t>
         </is>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>N5.HOG0041159</t>
+          <t>N5.HOG0044950</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
@@ -16557,24 +16557,24 @@
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>129224730</t>
+          <t>129218670</t>
         </is>
       </c>
       <c r="D625" t="inlineStr">
         <is>
-          <t>GO:0005524 [Name: ATP binding]; GO:0004672 [Name: protein kinase activity]; GO:0006468 [Name: protein phosphorylation]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E625" t="inlineStr">
         <is>
-          <t>dual specificity mitogen-activated protein kinase kinase 1-like</t>
+          <t>uncharacterized LOC129218670</t>
         </is>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>N5.HOG0044950</t>
+          <t>N5.HOG0053389</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
@@ -16584,24 +16584,24 @@
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>129218670</t>
+          <t>129234342</t>
         </is>
       </c>
       <c r="D626" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GO:0006355 [Name: regulation of transcription, DNA-templated]; GO:0035267 [Name: NuA4 histone acetyltransferase complex]; GO:0006325 [Name: chromatin organization]; GO:0005634 [Name: nucleus]; GO:0072487 [Name: MSL complex]</t>
         </is>
       </c>
       <c r="E626" t="inlineStr">
         <is>
-          <t>uncharacterized LOC129218670</t>
+          <t>male-specific lethal 3</t>
         </is>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>N5.HOG0053389</t>
+          <t>N5.HOG0053555</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
@@ -16611,24 +16611,24 @@
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>129234342</t>
+          <t>129228121</t>
         </is>
       </c>
       <c r="D627" t="inlineStr">
         <is>
-          <t>GO:0006355 [Name: regulation of transcription, DNA-templated]; GO:0035267 [Name: NuA4 histone acetyltransferase complex]; GO:0006325 [Name: chromatin organization]; GO:0005634 [Name: nucleus]; GO:0072487 [Name: MSL complex]</t>
+          <t>GO:0004749 [Name: ribose phosphate diphosphokinase activity]; GO:0006015 [Name: 5-phosphoribose 1-diphosphate biosynthetic process]; GO:0005737 [Name: cytoplasm]; GO:0006164 [Name: purine nucleotide biosynthetic process]; GO:0000287 [Name: magnesium ion binding]; GO:0002189 [Name: ribose phosphate diphosphokinase complex]</t>
         </is>
       </c>
       <c r="E627" t="inlineStr">
         <is>
-          <t>male-specific lethal 3</t>
+          <t>phosphoribosyl pyrophosphate synthase-associated protein 2-like</t>
         </is>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>N5.HOG0053555</t>
+          <t>N5.HOG0056124</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
@@ -16638,24 +16638,24 @@
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>129228121</t>
+          <t>129224034</t>
         </is>
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>GO:0004749 [Name: ribose phosphate diphosphokinase activity]; GO:0006015 [Name: 5-phosphoribose 1-diphosphate biosynthetic process]; GO:0005737 [Name: cytoplasm]; GO:0006164 [Name: purine nucleotide biosynthetic process]; GO:0000287 [Name: magnesium ion binding]; GO:0002189 [Name: ribose phosphate diphosphokinase complex]</t>
+          <t>GO:0043130 [Name: ubiquitin binding]; GO:0016020 [Name: membrane]; GO:0035091 [Name: phosphatidylinositol binding]; GO:0007165 [Name: signal transduction]; GO:0005768 [Name: endosome]; GO:0030276 [Name: clathrin binding]</t>
         </is>
       </c>
       <c r="E628" t="inlineStr">
         <is>
-          <t>phosphoribosyl pyrophosphate synthase-associated protein 2-like</t>
+          <t>TOM1-like protein 2</t>
         </is>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>N5.HOG0056124</t>
+          <t>N5.HOG0058170</t>
         </is>
       </c>
       <c r="B629" t="inlineStr">
@@ -16665,24 +16665,24 @@
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>129224034</t>
+          <t>129233105</t>
         </is>
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>GO:0043130 [Name: ubiquitin binding]; GO:0016020 [Name: membrane]; GO:0035091 [Name: phosphatidylinositol binding]; GO:0007165 [Name: signal transduction]; GO:0005768 [Name: endosome]; GO:0030276 [Name: clathrin binding]</t>
+          <t>GO:0005737 [Name: cytoplasm]; GO:0016020 [Name: membrane]</t>
         </is>
       </c>
       <c r="E629" t="inlineStr">
         <is>
-          <t>TOM1-like protein 2</t>
+          <t>protein Mpv17-like</t>
         </is>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>N5.HOG0058170</t>
+          <t>N5.HOG0063949</t>
         </is>
       </c>
       <c r="B630" t="inlineStr">
@@ -16692,24 +16692,24 @@
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>129233105</t>
+          <t>129218659</t>
         </is>
       </c>
       <c r="D630" t="inlineStr">
         <is>
-          <t>GO:0005737 [Name: cytoplasm]; GO:0016020 [Name: membrane]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E630" t="inlineStr">
         <is>
-          <t>protein Mpv17-like</t>
+          <t>uncharacterized LOC129218659</t>
         </is>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>N5.HOG0063949</t>
+          <t>N5.HOG0065829</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
@@ -16717,26 +16717,14 @@
           <t>busted_ph_rev, loss_50_nonorb</t>
         </is>
       </c>
-      <c r="C631" t="inlineStr">
-        <is>
-          <t>129218659</t>
-        </is>
-      </c>
-      <c r="D631" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E631" t="inlineStr">
-        <is>
-          <t>uncharacterized LOC129218659</t>
-        </is>
-      </c>
+      <c r="C631" t="inlineStr"/>
+      <c r="D631" t="inlineStr"/>
+      <c r="E631" t="inlineStr"/>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>N5.HOG0065829</t>
+          <t>N5.HOG0066329</t>
         </is>
       </c>
       <c r="B632" t="inlineStr">
@@ -16744,14 +16732,26 @@
           <t>busted_ph_rev, loss_50_nonorb</t>
         </is>
       </c>
-      <c r="C632" t="inlineStr"/>
-      <c r="D632" t="inlineStr"/>
-      <c r="E632" t="inlineStr"/>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>129224857</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>uncharacterized LOC129224857</t>
+        </is>
+      </c>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>N5.HOG0066329</t>
+          <t>N5.HOG0067927</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
@@ -16761,51 +16761,51 @@
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>129224857</t>
+          <t>129223042</t>
         </is>
       </c>
       <c r="D633" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GO:0000981 [Name: RNA polymerase II transcription factor activity, sequence-specific DNA binding]; GO:0000978 [Name: RNA polymerase II core promoter proximal region sequence-specific DNA binding]; GO:0006357 [Name: regulation of transcription from RNA polymerase II promoter]; GO:0046983 [Name: protein dimerization activity]</t>
         </is>
       </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>uncharacterized LOC129224857</t>
+          <t>uncharacterized LOC129223042</t>
         </is>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>N5.HOG0067927</t>
+          <t>N5.HOG0018631</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>busted_ph_rev, loss_50_nonorb</t>
+          <t>relaxed, busted_ph_rev</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>129223042</t>
+          <t>129217666</t>
         </is>
       </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>GO:0000981 [Name: RNA polymerase II transcription factor activity, sequence-specific DNA binding]; GO:0000978 [Name: RNA polymerase II core promoter proximal region sequence-specific DNA binding]; GO:0006357 [Name: regulation of transcription from RNA polymerase II promoter]; GO:0046983 [Name: protein dimerization activity]</t>
+          <t>GO:0005524 [Name: ATP binding]; GO:0007052 [Name: mitotic spindle organization]; GO:0008017 [Name: microtubule binding]; GO:0003777 [Name: microtubule motor activity]; GO:0007018 [Name: microtubule-based movement]</t>
         </is>
       </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t>uncharacterized LOC129223042</t>
+          <t>kinesin-like protein KIF21A</t>
         </is>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>N5.HOG0018631</t>
+          <t>N5.HOG0030307</t>
         </is>
       </c>
       <c r="B635" t="inlineStr">
@@ -16815,24 +16815,24 @@
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>129217666</t>
+          <t>129219340</t>
         </is>
       </c>
       <c r="D635" t="inlineStr">
         <is>
-          <t>GO:0005524 [Name: ATP binding]; GO:0007052 [Name: mitotic spindle organization]; GO:0008017 [Name: microtubule binding]; GO:0003777 [Name: microtubule motor activity]; GO:0007018 [Name: microtubule-based movement]</t>
+          <t>GO:0003924 [Name: GTPase activity]; GO:0005525 [Name: GTP binding]; GO:0007264 [Name: small GTPase mediated signal transduction]</t>
         </is>
       </c>
       <c r="E635" t="inlineStr">
         <is>
-          <t>kinesin-like protein KIF21A</t>
+          <t>ras-like GTP-binding protein RHO</t>
         </is>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>N5.HOG0030307</t>
+          <t>N5.HOG0034643</t>
         </is>
       </c>
       <c r="B636" t="inlineStr">
@@ -16842,24 +16842,24 @@
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>129219340</t>
+          <t>129228045</t>
         </is>
       </c>
       <c r="D636" t="inlineStr">
         <is>
-          <t>GO:0003924 [Name: GTPase activity]; GO:0005525 [Name: GTP binding]; GO:0007264 [Name: small GTPase mediated signal transduction]</t>
+          <t>GO:0005737 [Name: cytoplasm]; GO:0007165 [Name: signal transduction]</t>
         </is>
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>ras-like GTP-binding protein RHO</t>
+          <t>14-3-3 protein epsilon</t>
         </is>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>N5.HOG0034643</t>
+          <t>N5.HOG0037873</t>
         </is>
       </c>
       <c r="B637" t="inlineStr">
@@ -16869,24 +16869,24 @@
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>129228045</t>
+          <t>129234290</t>
         </is>
       </c>
       <c r="D637" t="inlineStr">
         <is>
-          <t>GO:0005737 [Name: cytoplasm]; GO:0007165 [Name: signal transduction]</t>
+          <t>GO:0000462 [Name: maturation of SSU-rRNA from tricistronic rRNA transcript (SSU-rRNA, 5.8S rRNA, LSU-rRNA)]; GO:0030686 [Name: 90S preribosome]; GO:0045943 [Name: positive regulation of transcription from RNA polymerase I promoter]; GO:0034455 [Name: t-UTP complex]; GO:0030515 [Name: snoRNA binding]; GO:0032040 [Name: small-subunit processome]</t>
         </is>
       </c>
       <c r="E637" t="inlineStr">
         <is>
-          <t>14-3-3 protein epsilon</t>
+          <t>HEAT repeat containing 1 homolog l(2)k09022</t>
         </is>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>N5.HOG0037873</t>
+          <t>N5.HOG0038243</t>
         </is>
       </c>
       <c r="B638" t="inlineStr">
@@ -16896,24 +16896,24 @@
       </c>
       <c r="C638" t="inlineStr">
         <is>
-          <t>129234290</t>
+          <t>129221524</t>
         </is>
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>GO:0000462 [Name: maturation of SSU-rRNA from tricistronic rRNA transcript (SSU-rRNA, 5.8S rRNA, LSU-rRNA)]; GO:0030686 [Name: 90S preribosome]; GO:0045943 [Name: positive regulation of transcription from RNA polymerase I promoter]; GO:0034455 [Name: t-UTP complex]; GO:0030515 [Name: snoRNA binding]; GO:0032040 [Name: small-subunit processome]</t>
+          <t>GO:0030162 [Name: regulation of proteolysis]; GO:0031625 [Name: ubiquitin protein ligase binding]; GO:0005737 [Name: cytoplasm]; GO:0043161 [Name: proteasome-mediated ubiquitin-dependent protein catabolic process]; GO:0005634 [Name: nucleus]</t>
         </is>
       </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>HEAT repeat containing 1 homolog l(2)k09022</t>
+          <t>protein roadkill-like</t>
         </is>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>N5.HOG0038243</t>
+          <t>N5.HOG0043542</t>
         </is>
       </c>
       <c r="B639" t="inlineStr">
@@ -16923,24 +16923,24 @@
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>129221524</t>
+          <t>129233311</t>
         </is>
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>GO:0030162 [Name: regulation of proteolysis]; GO:0031625 [Name: ubiquitin protein ligase binding]; GO:0005737 [Name: cytoplasm]; GO:0043161 [Name: proteasome-mediated ubiquitin-dependent protein catabolic process]; GO:0005634 [Name: nucleus]</t>
+          <t>GO:0003712 [Name: transcription cofactor activity]; GO:0006355 [Name: regulation of transcription, DNA-templated]; GO:0003723 [Name: RNA binding]; GO:0005634 [Name: nucleus]</t>
         </is>
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>protein roadkill-like</t>
+          <t>RNA-binding protein FUS-like</t>
         </is>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>N5.HOG0043542</t>
+          <t>N5.HOG0052156</t>
         </is>
       </c>
       <c r="B640" t="inlineStr">
@@ -16950,24 +16950,24 @@
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>129233311</t>
+          <t>129228216</t>
         </is>
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>GO:0003712 [Name: transcription cofactor activity]; GO:0006355 [Name: regulation of transcription, DNA-templated]; GO:0003723 [Name: RNA binding]; GO:0005634 [Name: nucleus]</t>
+          <t>GO:0003924 [Name: GTPase activity]; GO:0007264 [Name: small GTPase mediated signal transduction]; GO:0005525 [Name: GTP binding]</t>
         </is>
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>RNA-binding protein FUS-like</t>
+          <t>Cell division cycle 42</t>
         </is>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>N5.HOG0052156</t>
+          <t>N5.HOG0058053</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
@@ -16977,24 +16977,24 @@
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>129228216</t>
+          <t>129223910</t>
         </is>
       </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>GO:0003924 [Name: GTPase activity]; GO:0007264 [Name: small GTPase mediated signal transduction]; GO:0005525 [Name: GTP binding]</t>
+          <t>GO:0000139 [Name: Golgi membrane]; GO:0007030 [Name: Golgi organization]; GO:0000301 [Name: retrograde transport, vesicle recycling within Golgi]; GO:0031985 [Name: Golgi cisterna]</t>
         </is>
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>Cell division cycle 42</t>
+          <t>golgin subfamily A member 5-like</t>
         </is>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>N5.HOG0058053</t>
+          <t>N5.HOG0058287</t>
         </is>
       </c>
       <c r="B642" t="inlineStr">
@@ -17004,24 +17004,24 @@
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>129223910</t>
+          <t>129221939</t>
         </is>
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>GO:0000139 [Name: Golgi membrane]; GO:0007030 [Name: Golgi organization]; GO:0000301 [Name: retrograde transport, vesicle recycling within Golgi]; GO:0031985 [Name: Golgi cisterna]</t>
+          <t>GO:0004674 [Name: protein serine/threonine kinase activity]; GO:0043408 [Name: regulation of MAPK cascade]; GO:0005524 [Name: ATP binding]; GO:0006468 [Name: protein phosphorylation]; GO:0005737 [Name: cytoplasm]; GO:0035556 [Name: intracellular signal transduction]</t>
         </is>
       </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>golgin subfamily A member 5-like</t>
+          <t>serine/threonine-protein kinase PAK mbt</t>
         </is>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>N5.HOG0058287</t>
+          <t>N5.HOG0062664</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
@@ -17031,24 +17031,24 @@
       </c>
       <c r="C643" t="inlineStr">
         <is>
-          <t>129221939</t>
+          <t>129229267</t>
         </is>
       </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t>GO:0004674 [Name: protein serine/threonine kinase activity]; GO:0043408 [Name: regulation of MAPK cascade]; GO:0005524 [Name: ATP binding]; GO:0006468 [Name: protein phosphorylation]; GO:0005737 [Name: cytoplasm]; GO:0035556 [Name: intracellular signal transduction]</t>
+          <t>GO:0006999 [Name: nuclear pore organization]; GO:0036228 [Name: protein targeting to nuclear inner membrane]; GO:0017056 [Name: structural constituent of nuclear pore]; GO:0005643 [Name: nuclear pore]; GO:0006607 [Name: NLS-bearing protein import into nucleus]; GO:0044613 [Name: nuclear pore central transport channel]</t>
         </is>
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>serine/threonine-protein kinase PAK mbt</t>
+          <t>nuclear pore complex protein Nup54</t>
         </is>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>N5.HOG0062664</t>
+          <t>N5.HOG0065179</t>
         </is>
       </c>
       <c r="B644" t="inlineStr">
@@ -17058,24 +17058,24 @@
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>129229267</t>
+          <t>129220281</t>
         </is>
       </c>
       <c r="D644" t="inlineStr">
         <is>
-          <t>GO:0006999 [Name: nuclear pore organization]; GO:0036228 [Name: protein targeting to nuclear inner membrane]; GO:0017056 [Name: structural constituent of nuclear pore]; GO:0005643 [Name: nuclear pore]; GO:0006607 [Name: NLS-bearing protein import into nucleus]; GO:0044613 [Name: nuclear pore central transport channel]</t>
+          <t>GO:0005686 [Name: U2 snRNP]; GO:0003723 [Name: RNA binding]; GO:0000398 [Name: mRNA splicing, via spliceosome]; GO:0005684 [Name: U2-type spliceosomal complex]</t>
         </is>
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>nuclear pore complex protein Nup54</t>
+          <t>RRM1_TatSF1_like and RRM2_TatSF1_like domain-containing protein barc</t>
         </is>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>N5.HOG0065179</t>
+          <t>N5.HOG0065687</t>
         </is>
       </c>
       <c r="B645" t="inlineStr">
@@ -17085,24 +17085,24 @@
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>129220281</t>
+          <t>129222387</t>
         </is>
       </c>
       <c r="D645" t="inlineStr">
         <is>
-          <t>GO:0005686 [Name: U2 snRNP]; GO:0003723 [Name: RNA binding]; GO:0000398 [Name: mRNA splicing, via spliceosome]; GO:0005684 [Name: U2-type spliceosomal complex]</t>
+          <t>GO:0045046 [Name: protein import into peroxisome membrane]; GO:0005778 [Name: peroxisomal membrane]; GO:0005777 [Name: peroxisome]; GO:0033328 [Name: peroxisome membrane targeting sequence binding]</t>
         </is>
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>RRM1_TatSF1_like and RRM2_TatSF1_like domain-containing protein barc</t>
+          <t>peroxisomal biogenesis factor 19-like</t>
         </is>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>N5.HOG0065687</t>
+          <t>N5.HOG0067535</t>
         </is>
       </c>
       <c r="B646" t="inlineStr">
@@ -17112,24 +17112,24 @@
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>129222387</t>
+          <t>129217312</t>
         </is>
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>GO:0045046 [Name: protein import into peroxisome membrane]; GO:0005778 [Name: peroxisomal membrane]; GO:0005777 [Name: peroxisome]; GO:0033328 [Name: peroxisome membrane targeting sequence binding]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>peroxisomal biogenesis factor 19-like</t>
+          <t>uncharacterized LOC129217312</t>
         </is>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>N5.HOG0067535</t>
+          <t>N5.HOG0067814</t>
         </is>
       </c>
       <c r="B647" t="inlineStr">
@@ -17137,26 +17137,14 @@
           <t>relaxed, busted_ph_rev</t>
         </is>
       </c>
-      <c r="C647" t="inlineStr">
-        <is>
-          <t>129217312</t>
-        </is>
-      </c>
-      <c r="D647" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E647" t="inlineStr">
-        <is>
-          <t>uncharacterized LOC129217312</t>
-        </is>
-      </c>
+      <c r="C647" t="inlineStr"/>
+      <c r="D647" t="inlineStr"/>
+      <c r="E647" t="inlineStr"/>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>N5.HOG0067814</t>
+          <t>N5.HOG0068607</t>
         </is>
       </c>
       <c r="B648" t="inlineStr">
@@ -17164,34 +17152,46 @@
           <t>relaxed, busted_ph_rev</t>
         </is>
       </c>
-      <c r="C648" t="inlineStr"/>
-      <c r="D648" t="inlineStr"/>
-      <c r="E648" t="inlineStr"/>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>129229867</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>GO:0005634 [Name: nucleus]</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>zinc finger TRAF-type-containing protein 1 homolog</t>
+        </is>
+      </c>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>N5.HOG0068607</t>
+          <t>N5.HOG0015039</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>relaxed, busted_ph_rev</t>
+          <t>intensified, dup_50_orb, loss_50_nonorb</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>129229867</t>
+          <t>129223329</t>
         </is>
       </c>
       <c r="D649" t="inlineStr">
         <is>
-          <t>GO:0005634 [Name: nucleus]</t>
+          <t>GO:0004867 [Name: serine-type endopeptidase inhibitor activity]; GO:0005615 [Name: extracellular space]</t>
         </is>
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>zinc finger TRAF-type-containing protein 1 homolog</t>
+          <t>intracellular coagulation inhibitor 1-like</t>
         </is>
       </c>
     </row>
@@ -17208,24 +17208,24 @@
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>129223329</t>
+          <t>129222854</t>
         </is>
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>GO:0004867 [Name: serine-type endopeptidase inhibitor activity]; GO:0005615 [Name: extracellular space]</t>
+          <t>GO:0005615 [Name: extracellular space]; GO:0004867 [Name: serine-type endopeptidase inhibitor activity]</t>
         </is>
       </c>
       <c r="E650" t="inlineStr">
         <is>
-          <t>intracellular coagulation inhibitor 1-like</t>
+          <t>intracellular coagulation inhibitor 2-like</t>
         </is>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>N5.HOG0015039</t>
+          <t>N5.HOG0028062</t>
         </is>
       </c>
       <c r="B651" t="inlineStr">
@@ -17235,24 +17235,24 @@
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>129222854</t>
+          <t>129224046</t>
         </is>
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>GO:0005615 [Name: extracellular space]; GO:0004867 [Name: serine-type endopeptidase inhibitor activity]</t>
+          <t>GO:0016791 [Name: phosphatase activity]</t>
         </is>
       </c>
       <c r="E651" t="inlineStr">
         <is>
-          <t>intracellular coagulation inhibitor 2-like</t>
+          <t>pseudouridine-5'-phosphatase-like</t>
         </is>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>N5.HOG0028062</t>
+          <t>N5.HOG0032489</t>
         </is>
       </c>
       <c r="B652" t="inlineStr">
@@ -17262,17 +17262,17 @@
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>129224046</t>
+          <t>129224760</t>
         </is>
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>GO:0016791 [Name: phosphatase activity]</t>
+          <t>GO:0000285 [Name: 1-phosphatidylinositol-3-phosphate 5-kinase activity]; GO:0046488 [Name: phosphatidylinositol metabolic process]; GO:0005515 [Name: protein binding]</t>
         </is>
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>pseudouridine-5'-phosphatase-like</t>
+          <t>1-phosphatidylinositol 3-phosphate 5-kinase-like</t>
         </is>
       </c>
     </row>
@@ -17289,24 +17289,24 @@
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>129224760</t>
+          <t>129216368</t>
         </is>
       </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>GO:0000285 [Name: 1-phosphatidylinositol-3-phosphate 5-kinase activity]; GO:0046488 [Name: phosphatidylinositol metabolic process]; GO:0005515 [Name: protein binding]</t>
+          <t>GO:0005515 [Name: protein binding]</t>
         </is>
       </c>
       <c r="E653" t="inlineStr">
         <is>
-          <t>1-phosphatidylinositol 3-phosphate 5-kinase-like</t>
+          <t>uncharacterized LOC129216368</t>
         </is>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>N5.HOG0032489</t>
+          <t>N5.HOG0038436</t>
         </is>
       </c>
       <c r="B654" t="inlineStr">
@@ -17316,24 +17316,24 @@
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>129216368</t>
+          <t>129224024</t>
         </is>
       </c>
       <c r="D654" t="inlineStr">
         <is>
-          <t>GO:0005515 [Name: protein binding]</t>
+          <t>GO:0012505 [Name: endomembrane system]; GO:0061630 [Name: ubiquitin protein ligase activity]</t>
         </is>
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>uncharacterized LOC129216368</t>
+          <t>uncharacterized LOC129224024</t>
         </is>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>N5.HOG0038436</t>
+          <t>N5.HOG0039412</t>
         </is>
       </c>
       <c r="B655" t="inlineStr">
@@ -17343,24 +17343,24 @@
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>129224024</t>
+          <t>129228466</t>
         </is>
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>GO:0012505 [Name: endomembrane system]; GO:0061630 [Name: ubiquitin protein ligase activity]</t>
+          <t>GO:0045727 [Name: positive regulation of translation]; GO:0005737 [Name: cytoplasm]; GO:1901190 [Name: regulation of formation of translation initiation ternary complex]; GO:0003723 [Name: RNA binding]; GO:0003743 [Name: translation initiation factor activity]; GO:0008190 [Name: eukaryotic initiation factor 4E binding]; GO:0034518 [Name: RNA cap binding complex]</t>
         </is>
       </c>
       <c r="E655" t="inlineStr">
         <is>
-          <t>uncharacterized LOC129224024</t>
+          <t>Eukaryotic translation initiation factor mextil</t>
         </is>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>N5.HOG0039412</t>
+          <t>N5.HOG0041634</t>
         </is>
       </c>
       <c r="B656" t="inlineStr">
@@ -17370,24 +17370,24 @@
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>129228466</t>
+          <t>129227265</t>
         </is>
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>GO:0045727 [Name: positive regulation of translation]; GO:0005737 [Name: cytoplasm]; GO:1901190 [Name: regulation of formation of translation initiation ternary complex]; GO:0003723 [Name: RNA binding]; GO:0003743 [Name: translation initiation factor activity]; GO:0008190 [Name: eukaryotic initiation factor 4E binding]; GO:0034518 [Name: RNA cap binding complex]</t>
+          <t>GO:0016311 [Name: dephosphorylation]; GO:0052629 [Name: phosphatidylinositol-3,5-bisphosphate 3-phosphatase activity]; GO:0010506 [Name: regulation of autophagy]; GO:0019903 [Name: protein phosphatase binding]</t>
         </is>
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>Eukaryotic translation initiation factor mextil</t>
+          <t>myotubularin-related protein 3-like</t>
         </is>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>N5.HOG0041634</t>
+          <t>N5.HOG0041752</t>
         </is>
       </c>
       <c r="B657" t="inlineStr">
@@ -17397,24 +17397,24 @@
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>129227265</t>
+          <t>129228475</t>
         </is>
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>GO:0016311 [Name: dephosphorylation]; GO:0052629 [Name: phosphatidylinositol-3,5-bisphosphate 3-phosphatase activity]; GO:0010506 [Name: regulation of autophagy]; GO:0019903 [Name: protein phosphatase binding]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>myotubularin-related protein 3-like</t>
+          <t>zinc finger and SCAN domain-containing protein 29-like</t>
         </is>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>N5.HOG0041752</t>
+          <t>N5.HOG0043353</t>
         </is>
       </c>
       <c r="B658" t="inlineStr">
@@ -17424,24 +17424,24 @@
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>129228475</t>
+          <t>129228295</t>
         </is>
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GO:0004032 [Name: alditol:NADP+ 1-oxidoreductase activity]; GO:0005829 [Name: cytosol]</t>
         </is>
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>zinc finger and SCAN domain-containing protein 29-like</t>
+          <t>aldo-keto reductase family 1 member B1-like</t>
         </is>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>N5.HOG0043353</t>
+          <t>N5.HOG0046173</t>
         </is>
       </c>
       <c r="B659" t="inlineStr">
@@ -17451,24 +17451,24 @@
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>129228295</t>
+          <t>129219138</t>
         </is>
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>GO:0004032 [Name: alditol:NADP+ 1-oxidoreductase activity]; GO:0005829 [Name: cytosol]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>aldo-keto reductase family 1 member B1-like</t>
+          <t>cysteine-rich hydrophobic domain-containing protein 2-like</t>
         </is>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>N5.HOG0046173</t>
+          <t>N5.HOG0049044</t>
         </is>
       </c>
       <c r="B660" t="inlineStr">
@@ -17478,24 +17478,24 @@
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>129219138</t>
+          <t>129226944</t>
         </is>
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GO:0035267 [Name: NuA4 histone acetyltransferase complex]; GO:0042393 [Name: histone binding]; GO:0006338 [Name: chromatin remodeling]; GO:0006357 [Name: regulation of transcription from RNA polymerase II promoter]</t>
         </is>
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>cysteine-rich hydrophobic domain-containing protein 2-like</t>
+          <t>YEATS domain containing 2 homolog D12</t>
         </is>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>N5.HOG0049044</t>
+          <t>N5.HOG0058825</t>
         </is>
       </c>
       <c r="B661" t="inlineStr">
@@ -17505,24 +17505,24 @@
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>129226944</t>
+          <t>129231218</t>
         </is>
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>GO:0035267 [Name: NuA4 histone acetyltransferase complex]; GO:0042393 [Name: histone binding]; GO:0006338 [Name: chromatin remodeling]; GO:0006357 [Name: regulation of transcription from RNA polymerase II promoter]</t>
+          <t>GO:0005829 [Name: cytosol]; GO:0006457 [Name: protein folding]; GO:0001671 [Name: ATPase activator activity]; GO:0032781 [Name: positive regulation of ATPase activity]; GO:0051087 [Name: chaperone binding]</t>
         </is>
       </c>
       <c r="E661" t="inlineStr">
         <is>
-          <t>YEATS domain containing 2 homolog D12</t>
+          <t>activator of 90 kDa heat shock protein ATPase homolog 1-like</t>
         </is>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>N5.HOG0058825</t>
+          <t>N5.HOG0064130</t>
         </is>
       </c>
       <c r="B662" t="inlineStr">
@@ -17530,26 +17530,14 @@
           <t>intensified, dup_50_orb, loss_50_nonorb</t>
         </is>
       </c>
-      <c r="C662" t="inlineStr">
-        <is>
-          <t>129231218</t>
-        </is>
-      </c>
-      <c r="D662" t="inlineStr">
-        <is>
-          <t>GO:0005829 [Name: cytosol]; GO:0006457 [Name: protein folding]; GO:0001671 [Name: ATPase activator activity]; GO:0032781 [Name: positive regulation of ATPase activity]; GO:0051087 [Name: chaperone binding]</t>
-        </is>
-      </c>
-      <c r="E662" t="inlineStr">
-        <is>
-          <t>activator of 90 kDa heat shock protein ATPase homolog 1-like</t>
-        </is>
-      </c>
+      <c r="C662" t="inlineStr"/>
+      <c r="D662" t="inlineStr"/>
+      <c r="E662" t="inlineStr"/>
     </row>
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>N5.HOG0064130</t>
+          <t>N5.HOG0067350</t>
         </is>
       </c>
       <c r="B663" t="inlineStr">
@@ -17564,22 +17552,34 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>N5.HOG0067350</t>
+          <t>N5.HOG0022701</t>
         </is>
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>intensified, dup_50_orb, loss_50_nonorb</t>
-        </is>
-      </c>
-      <c r="C664" t="inlineStr"/>
-      <c r="D664" t="inlineStr"/>
-      <c r="E664" t="inlineStr"/>
+          <t>silk_genes, intensified</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>129216968</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>GO:0097176 [Name: epoxide metabolic process]; GO:0004301 [Name: epoxide hydrolase activity]</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>epoxide hydrolase 1-like</t>
+        </is>
+      </c>
     </row>
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>N5.HOG0022701</t>
+          <t>N5.HOG0028613</t>
         </is>
       </c>
       <c r="B665" t="inlineStr">
@@ -17589,24 +17589,24 @@
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>129216968</t>
+          <t>129229415</t>
         </is>
       </c>
       <c r="D665" t="inlineStr">
         <is>
-          <t>GO:0097176 [Name: epoxide metabolic process]; GO:0004301 [Name: epoxide hydrolase activity]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E665" t="inlineStr">
         <is>
-          <t>epoxide hydrolase 1-like</t>
+          <t>uncharacterized LOC129229415</t>
         </is>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>N5.HOG0028613</t>
+          <t>N5.HOG0048349</t>
         </is>
       </c>
       <c r="B666" t="inlineStr">
@@ -17616,24 +17616,24 @@
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>129229415</t>
+          <t>129221511</t>
         </is>
       </c>
       <c r="D666" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GO:0005741 [Name: mitochondrial outer membrane]; GO:0070189 [Name: kynurenine metabolic process]; GO:0071949 [Name: FAD binding]; GO:0006569 [Name: tryptophan catabolic process]; GO:0016174 [Name: NAD(P)H oxidase activity]; GO:0019805 [Name: quinolinate biosynthetic process]; GO:0019674 [Name: NAD metabolic process]; GO:0004502 [Name: kynurenine 3-monooxygenase activity]</t>
         </is>
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>uncharacterized LOC129229415</t>
+          <t>Kynurenine 3-monooxygenase cn</t>
         </is>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>N5.HOG0048349</t>
+          <t>N5.HOG0053703</t>
         </is>
       </c>
       <c r="B667" t="inlineStr">
@@ -17643,24 +17643,24 @@
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>129221511</t>
+          <t>129231281</t>
         </is>
       </c>
       <c r="D667" t="inlineStr">
         <is>
-          <t>GO:0005741 [Name: mitochondrial outer membrane]; GO:0070189 [Name: kynurenine metabolic process]; GO:0071949 [Name: FAD binding]; GO:0006569 [Name: tryptophan catabolic process]; GO:0016174 [Name: NAD(P)H oxidase activity]; GO:0019805 [Name: quinolinate biosynthetic process]; GO:0019674 [Name: NAD metabolic process]; GO:0004502 [Name: kynurenine 3-monooxygenase activity]</t>
+          <t>GO:0016787 [Name: hydrolase activity]</t>
         </is>
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>Kynurenine 3-monooxygenase cn</t>
+          <t>acid sphingomyelinase-like phosphodiesterase 3b</t>
         </is>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>N5.HOG0053703</t>
+          <t>N5.HOG0054831</t>
         </is>
       </c>
       <c r="B668" t="inlineStr">
@@ -17670,24 +17670,24 @@
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>129231281</t>
+          <t>129219045</t>
         </is>
       </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>GO:0016787 [Name: hydrolase activity]</t>
+          <t>GO:0003723 [Name: RNA binding]</t>
         </is>
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>acid sphingomyelinase-like phosphodiesterase 3b</t>
+          <t>uncharacterized LOC129219045</t>
         </is>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>N5.HOG0054831</t>
+          <t>N5.HOG0058242</t>
         </is>
       </c>
       <c r="B669" t="inlineStr">
@@ -17697,24 +17697,24 @@
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>129219045</t>
+          <t>129220585</t>
         </is>
       </c>
       <c r="D669" t="inlineStr">
         <is>
-          <t>GO:0003723 [Name: RNA binding]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>uncharacterized LOC129219045</t>
+          <t>protein Skeletor</t>
         </is>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>N5.HOG0058242</t>
+          <t>N5.HOG0062528</t>
         </is>
       </c>
       <c r="B670" t="inlineStr">
@@ -17724,24 +17724,24 @@
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>129220585</t>
+          <t>129229235</t>
         </is>
       </c>
       <c r="D670" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GO:0000287 [Name: magnesium ion binding]; GO:0006048 [Name: UDP-N-acetylglucosamine biosynthetic process]; GO:0005975 [Name: carbohydrate metabolic process]; GO:0004610 [Name: phosphoacetylglucosamine mutase activity]</t>
         </is>
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>protein Skeletor</t>
+          <t>phosphoacetylglucosamine mutase-like</t>
         </is>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>N5.HOG0062528</t>
+          <t>N5.HOG0066105</t>
         </is>
       </c>
       <c r="B671" t="inlineStr">
@@ -17751,17 +17751,17 @@
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>129229235</t>
+          <t>129233808</t>
         </is>
       </c>
       <c r="D671" t="inlineStr">
         <is>
-          <t>GO:0000287 [Name: magnesium ion binding]; GO:0006048 [Name: UDP-N-acetylglucosamine biosynthetic process]; GO:0005975 [Name: carbohydrate metabolic process]; GO:0004610 [Name: phosphoacetylglucosamine mutase activity]</t>
+          <t>GO:0016791 [Name: phosphatase activity]; GO:0000298 [Name: endopolyphosphatase activity]; GO:0005737 [Name: cytoplasm]; GO:0006798 [Name: polyphosphate catabolic process]</t>
         </is>
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>phosphoacetylglucosamine mutase-like</t>
+          <t>bis(5'-nucleosyl)-tetraphosphatase PrpE [asymmetrical]-like</t>
         </is>
       </c>
     </row>
@@ -17778,7 +17778,7 @@
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>129233808</t>
+          <t>129229510</t>
         </is>
       </c>
       <c r="D672" t="inlineStr">
@@ -17788,14 +17788,14 @@
       </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>bis(5'-nucleosyl)-tetraphosphatase PrpE [asymmetrical]-like</t>
+          <t>bis(5'-nucleosyl)-tetraphosphatase, symmetrical-like</t>
         </is>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>N5.HOG0066105</t>
+          <t>N5.HOG0067970</t>
         </is>
       </c>
       <c r="B673" t="inlineStr">
@@ -17805,24 +17805,24 @@
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>129229510</t>
+          <t>129222148</t>
         </is>
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>GO:0016791 [Name: phosphatase activity]; GO:0000298 [Name: endopolyphosphatase activity]; GO:0005737 [Name: cytoplasm]; GO:0006798 [Name: polyphosphate catabolic process]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>bis(5'-nucleosyl)-tetraphosphatase, symmetrical-like</t>
+          <t>uncharacterized LOC129222148</t>
         </is>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>N5.HOG0067970</t>
+          <t>N5.HOG0068205</t>
         </is>
       </c>
       <c r="B674" t="inlineStr">
@@ -17832,7 +17832,7 @@
       </c>
       <c r="C674" t="inlineStr">
         <is>
-          <t>129222148</t>
+          <t>129222716</t>
         </is>
       </c>
       <c r="D674" t="inlineStr">
@@ -17842,41 +17842,29 @@
       </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>uncharacterized LOC129222148</t>
+          <t>uncharacterized LOC129222716</t>
         </is>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>N5.HOG0068205</t>
+          <t>N5.HOG0010662</t>
         </is>
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>silk_genes, intensified</t>
-        </is>
-      </c>
-      <c r="C675" t="inlineStr">
-        <is>
-          <t>129222716</t>
-        </is>
-      </c>
-      <c r="D675" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E675" t="inlineStr">
-        <is>
-          <t>uncharacterized LOC129222716</t>
-        </is>
-      </c>
+          <t>intensified, busted_ph</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr"/>
+      <c r="D675" t="inlineStr"/>
+      <c r="E675" t="inlineStr"/>
     </row>
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>N5.HOG0010662</t>
+          <t>N5.HOG0028454</t>
         </is>
       </c>
       <c r="B676" t="inlineStr">
@@ -17884,14 +17872,26 @@
           <t>intensified, busted_ph</t>
         </is>
       </c>
-      <c r="C676" t="inlineStr"/>
-      <c r="D676" t="inlineStr"/>
-      <c r="E676" t="inlineStr"/>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>129216029</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>GO:0032222 [Name: regulation of synaptic transmission, cholinergic]; GO:1903818 [Name: positive regulation of voltage-gated potassium channel activity]; GO:0030431 [Name: sleep]</t>
+        </is>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>uncharacterized LOC129216029</t>
+        </is>
+      </c>
     </row>
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>N5.HOG0028454</t>
+          <t>N5.HOG0049287</t>
         </is>
       </c>
       <c r="B677" t="inlineStr">
@@ -17901,24 +17901,24 @@
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>129216029</t>
+          <t>129231587</t>
         </is>
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>GO:0032222 [Name: regulation of synaptic transmission, cholinergic]; GO:1903818 [Name: positive regulation of voltage-gated potassium channel activity]; GO:0030431 [Name: sleep]</t>
+          <t>GO:0004843 [Name: thiol-dependent ubiquitin-specific protease activity]; GO:0016579 [Name: protein deubiquitination]</t>
         </is>
       </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>uncharacterized LOC129216029</t>
+          <t>deubiquitinase OTUD6B-like</t>
         </is>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>N5.HOG0049287</t>
+          <t>N5.HOG0053657</t>
         </is>
       </c>
       <c r="B678" t="inlineStr">
@@ -17928,24 +17928,24 @@
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>129231587</t>
+          <t>129225549</t>
         </is>
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>GO:0004843 [Name: thiol-dependent ubiquitin-specific protease activity]; GO:0016579 [Name: protein deubiquitination]</t>
+          <t>GO:0004821 [Name: histidine-tRNA ligase activity]; GO:0005524 [Name: ATP binding]; GO:0005737 [Name: cytoplasm]; GO:0006427 [Name: histidyl-tRNA aminoacylation]; GO:0032543 [Name: mitochondrial translation]; GO:0005739 [Name: mitochondrion]</t>
         </is>
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>deubiquitinase OTUD6B-like</t>
+          <t>histidine--tRNA ligase, cytoplasmic-like</t>
         </is>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>N5.HOG0053657</t>
+          <t>N5.HOG0055149</t>
         </is>
       </c>
       <c r="B679" t="inlineStr">
@@ -17955,24 +17955,24 @@
       </c>
       <c r="C679" t="inlineStr">
         <is>
-          <t>129225549</t>
+          <t>129216055</t>
         </is>
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>GO:0004821 [Name: histidine-tRNA ligase activity]; GO:0005524 [Name: ATP binding]; GO:0005737 [Name: cytoplasm]; GO:0006427 [Name: histidyl-tRNA aminoacylation]; GO:0032543 [Name: mitochondrial translation]; GO:0005739 [Name: mitochondrion]</t>
+          <t>GO:0004672 [Name: protein kinase activity]; GO:0007283 [Name: spermatogenesis]; GO:0005524 [Name: ATP binding]; GO:0006468 [Name: protein phosphorylation]</t>
         </is>
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>histidine--tRNA ligase, cytoplasmic-like</t>
+          <t>serine/threonine-protein kinase 31-like</t>
         </is>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>N5.HOG0055149</t>
+          <t>N5.HOG0056632</t>
         </is>
       </c>
       <c r="B680" t="inlineStr">
@@ -17982,24 +17982,24 @@
       </c>
       <c r="C680" t="inlineStr">
         <is>
-          <t>129216055</t>
+          <t>129230356</t>
         </is>
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>GO:0004672 [Name: protein kinase activity]; GO:0007283 [Name: spermatogenesis]; GO:0005524 [Name: ATP binding]; GO:0006468 [Name: protein phosphorylation]</t>
+          <t>GO:0005654 [Name: nucleoplasm]; GO:0005515 [Name: protein binding]</t>
         </is>
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>serine/threonine-protein kinase 31-like</t>
+          <t>ankyrin repeat domain-containing protein 12-like</t>
         </is>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>N5.HOG0056632</t>
+          <t>N5.HOG0062421</t>
         </is>
       </c>
       <c r="B681" t="inlineStr">
@@ -18009,24 +18009,24 @@
       </c>
       <c r="C681" t="inlineStr">
         <is>
-          <t>129230356</t>
+          <t>129228491</t>
         </is>
       </c>
       <c r="D681" t="inlineStr">
         <is>
-          <t>GO:0005654 [Name: nucleoplasm]; GO:0005515 [Name: protein binding]</t>
+          <t>GO:0005774 [Name: vacuolar membrane]; GO:0072665 [Name: protein localization to vacuole]</t>
         </is>
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>ankyrin repeat domain-containing protein 12-like</t>
+          <t>lysosomal cobalamin transport escort protein LMBD1-like</t>
         </is>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>N5.HOG0062421</t>
+          <t>N5.HOG0064264</t>
         </is>
       </c>
       <c r="B682" t="inlineStr">
@@ -18036,24 +18036,24 @@
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>129228491</t>
+          <t>129227243</t>
         </is>
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>GO:0005774 [Name: vacuolar membrane]; GO:0072665 [Name: protein localization to vacuole]</t>
+          <t>GO:0006729 [Name: tetrahydrobiopterin biosynthetic process]; GO:0008124 [Name: 4-alpha-hydroxytetrahydrobiopterin dehydratase activity]</t>
         </is>
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>lysosomal cobalamin transport escort protein LMBD1-like</t>
+          <t>probable pterin-4-alpha-carbinolamine dehydratase</t>
         </is>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>N5.HOG0064264</t>
+          <t>N5.HOG0065364</t>
         </is>
       </c>
       <c r="B683" t="inlineStr">
@@ -18063,24 +18063,24 @@
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>129227243</t>
+          <t>129229728</t>
         </is>
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>GO:0006729 [Name: tetrahydrobiopterin biosynthetic process]; GO:0008124 [Name: 4-alpha-hydroxytetrahydrobiopterin dehydratase activity]</t>
+          <t>GO:0004252 [Name: serine-type endopeptidase activity]; GO:0004176 [Name: ATP-dependent peptidase activity]; GO:0009368 [Name: endopeptidase Clp complex]; GO:0006515 [Name: misfolded or incompletely synthesized protein catabolic process]; GO:0051117 [Name: ATPase binding]</t>
         </is>
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>probable pterin-4-alpha-carbinolamine dehydratase</t>
+          <t>Caseinolytic protease proteolytic subunit</t>
         </is>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>N5.HOG0065364</t>
+          <t>N5.HOG0069800</t>
         </is>
       </c>
       <c r="B684" t="inlineStr">
@@ -18090,44 +18090,44 @@
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>129229728</t>
+          <t>129232798</t>
         </is>
       </c>
       <c r="D684" t="inlineStr">
         <is>
-          <t>GO:0004252 [Name: serine-type endopeptidase activity]; GO:0004176 [Name: ATP-dependent peptidase activity]; GO:0009368 [Name: endopeptidase Clp complex]; GO:0006515 [Name: misfolded or incompletely synthesized protein catabolic process]; GO:0051117 [Name: ATPase binding]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>Caseinolytic protease proteolytic subunit</t>
+          <t>uncharacterized LOC129232798</t>
         </is>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>N5.HOG0069800</t>
+          <t>N5.HOG0036254</t>
         </is>
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>intensified, busted_ph</t>
+          <t>busted_ph_rev, dup_50_nonorb</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
         <is>
-          <t>129232798</t>
+          <t>129223783</t>
         </is>
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GO:0006412 [Name: translation]; GO:0003735 [Name: structural constituent of ribosome]; GO:0005840 [Name: ribosome]; GO:0005515 [Name: protein binding]; GO:0022627 [Name: cytosolic small ribosomal subunit]</t>
         </is>
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>uncharacterized LOC129232798</t>
+          <t>FAU ubiquitin-like and ribosomal protein S30</t>
         </is>
       </c>
     </row>
@@ -18144,12 +18144,12 @@
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>129223783</t>
+          <t>129234264</t>
         </is>
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>GO:0006412 [Name: translation]; GO:0003735 [Name: structural constituent of ribosome]; GO:0005840 [Name: ribosome]; GO:0005515 [Name: protein binding]; GO:0022627 [Name: cytosolic small ribosomal subunit]</t>
+          <t>GO:0022627 [Name: cytosolic small ribosomal subunit]; GO:0005515 [Name: protein binding]; GO:0006412 [Name: translation]; GO:0003735 [Name: structural constituent of ribosome]; GO:0005840 [Name: ribosome]</t>
         </is>
       </c>
       <c r="E686" t="inlineStr">
@@ -18169,26 +18169,14 @@
           <t>busted_ph_rev, dup_50_nonorb</t>
         </is>
       </c>
-      <c r="C687" t="inlineStr">
-        <is>
-          <t>129234264</t>
-        </is>
-      </c>
-      <c r="D687" t="inlineStr">
-        <is>
-          <t>GO:0022627 [Name: cytosolic small ribosomal subunit]; GO:0005515 [Name: protein binding]; GO:0006412 [Name: translation]; GO:0003735 [Name: structural constituent of ribosome]; GO:0005840 [Name: ribosome]</t>
-        </is>
-      </c>
-      <c r="E687" t="inlineStr">
-        <is>
-          <t>FAU ubiquitin-like and ribosomal protein S30</t>
-        </is>
-      </c>
+      <c r="C687" t="inlineStr"/>
+      <c r="D687" t="inlineStr"/>
+      <c r="E687" t="inlineStr"/>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>N5.HOG0036254</t>
+          <t>N5.HOG0045486</t>
         </is>
       </c>
       <c r="B688" t="inlineStr">
@@ -18196,14 +18184,26 @@
           <t>busted_ph_rev, dup_50_nonorb</t>
         </is>
       </c>
-      <c r="C688" t="inlineStr"/>
-      <c r="D688" t="inlineStr"/>
-      <c r="E688" t="inlineStr"/>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>129229768</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>GO:0005634 [Name: nucleus]; GO:0006325 [Name: chromatin organization]; GO:0006355 [Name: regulation of transcription, DNA-templated]; GO:0043565 [Name: sequence-specific DNA binding]; GO:0008270 [Name: zinc ion binding]</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>GATA zinc finger domain-containing protein 1-like</t>
+        </is>
+      </c>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>N5.HOG0045486</t>
+          <t>N5.HOG0063077</t>
         </is>
       </c>
       <c r="B689" t="inlineStr">
@@ -18213,24 +18213,24 @@
       </c>
       <c r="C689" t="inlineStr">
         <is>
-          <t>129229768</t>
+          <t>129219268</t>
         </is>
       </c>
       <c r="D689" t="inlineStr">
         <is>
-          <t>GO:0005634 [Name: nucleus]; GO:0006325 [Name: chromatin organization]; GO:0006355 [Name: regulation of transcription, DNA-templated]; GO:0043565 [Name: sequence-specific DNA binding]; GO:0008270 [Name: zinc ion binding]</t>
+          <t>GO:0043025 [Name: neuronal cell body]; GO:0045727 [Name: positive regulation of translation]; GO:0043197 [Name: dendritic spine]; GO:0048814 [Name: regulation of dendrite morphogenesis]; GO:0016020 [Name: membrane]; GO:0071598 [Name: neuronal ribonucleoprotein granule]; GO:0003730 [Name: mRNA 3'-UTR binding]; GO:0030424 [Name: axon]; GO:0042803 [Name: protein homodimerization activity]; GO:0043488 [Name: regulation of mRNA stability]; GO:0060998 [Name: regulation of dendritic spine development]; GO:0099578 [Name: regulation of translation at postsynapse, modulating synaptic transmission]; GO:0008089 [Name: anterograde axonal transport]; GO:0014069 [Name: postsynaptic density]; GO:0045182 [Name: translation regulator activity]; GO:0005634 [Name: nucleus]; GO:0007417 [Name: central nervous system development]; GO:0017148 [Name: negative regulation of translation]; GO:1905244 [Name: regulation of modification of synaptic structure]</t>
         </is>
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>GATA zinc finger domain-containing protein 1-like</t>
+          <t>fragile X messenger ribonucleoprotein 1 homolog</t>
         </is>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>N5.HOG0063077</t>
+          <t>N5.HOG0063977</t>
         </is>
       </c>
       <c r="B690" t="inlineStr">
@@ -18238,26 +18238,14 @@
           <t>busted_ph_rev, dup_50_nonorb</t>
         </is>
       </c>
-      <c r="C690" t="inlineStr">
-        <is>
-          <t>129219268</t>
-        </is>
-      </c>
-      <c r="D690" t="inlineStr">
-        <is>
-          <t>GO:0043025 [Name: neuronal cell body]; GO:0045727 [Name: positive regulation of translation]; GO:0043197 [Name: dendritic spine]; GO:0048814 [Name: regulation of dendrite morphogenesis]; GO:0016020 [Name: membrane]; GO:0071598 [Name: neuronal ribonucleoprotein granule]; GO:0003730 [Name: mRNA 3'-UTR binding]; GO:0030424 [Name: axon]; GO:0042803 [Name: protein homodimerization activity]; GO:0043488 [Name: regulation of mRNA stability]; GO:0060998 [Name: regulation of dendritic spine development]; GO:0099578 [Name: regulation of translation at postsynapse, modulating synaptic transmission]; GO:0008089 [Name: anterograde axonal transport]; GO:0014069 [Name: postsynaptic density]; GO:0045182 [Name: translation regulator activity]; GO:0005634 [Name: nucleus]; GO:0007417 [Name: central nervous system development]; GO:0017148 [Name: negative regulation of translation]; GO:1905244 [Name: regulation of modification of synaptic structure]</t>
-        </is>
-      </c>
-      <c r="E690" t="inlineStr">
-        <is>
-          <t>fragile X messenger ribonucleoprotein 1 homolog</t>
-        </is>
-      </c>
+      <c r="C690" t="inlineStr"/>
+      <c r="D690" t="inlineStr"/>
+      <c r="E690" t="inlineStr"/>
     </row>
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>N5.HOG0063977</t>
+          <t>N5.HOG0064953</t>
         </is>
       </c>
       <c r="B691" t="inlineStr">
@@ -18265,9 +18253,21 @@
           <t>busted_ph_rev, dup_50_nonorb</t>
         </is>
       </c>
-      <c r="C691" t="inlineStr"/>
-      <c r="D691" t="inlineStr"/>
-      <c r="E691" t="inlineStr"/>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>129227739</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>Actin-related protein 1</t>
+        </is>
+      </c>
     </row>
     <row r="692">
       <c r="A692" t="inlineStr">
@@ -18282,24 +18282,24 @@
       </c>
       <c r="C692" t="inlineStr">
         <is>
-          <t>129227739</t>
+          <t>129234279</t>
         </is>
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GO:0003712 [Name: transcription cofactor activity]; GO:0016592 [Name: mediator complex]; GO:0006357 [Name: regulation of transcription from RNA polymerase II promoter]</t>
         </is>
       </c>
       <c r="E692" t="inlineStr">
         <is>
-          <t>Actin-related protein 1</t>
+          <t>mediator complex subunit 21</t>
         </is>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>N5.HOG0064953</t>
+          <t>N5.HOG0066667</t>
         </is>
       </c>
       <c r="B693" t="inlineStr">
@@ -18309,24 +18309,24 @@
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>129234279</t>
+          <t>129229252</t>
         </is>
       </c>
       <c r="D693" t="inlineStr">
         <is>
-          <t>GO:0003712 [Name: transcription cofactor activity]; GO:0016592 [Name: mediator complex]; GO:0006357 [Name: regulation of transcription from RNA polymerase II promoter]</t>
+          <t>GO:0005515 [Name: protein binding]; GO:0035556 [Name: intracellular signal transduction]; GO:0043161 [Name: proteasome-mediated ubiquitin-dependent protein catabolic process]; GO:0019005 [Name: SCF ubiquitin ligase complex]</t>
         </is>
       </c>
       <c r="E693" t="inlineStr">
         <is>
-          <t>mediator complex subunit 21</t>
+          <t>splA/ryanodine receptor domain and SOCS box containing gustavus</t>
         </is>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>N5.HOG0066667</t>
+          <t>N5.HOG0067234</t>
         </is>
       </c>
       <c r="B694" t="inlineStr">
@@ -18336,24 +18336,24 @@
       </c>
       <c r="C694" t="inlineStr">
         <is>
-          <t>129229252</t>
+          <t>129225607</t>
         </is>
       </c>
       <c r="D694" t="inlineStr">
         <is>
-          <t>GO:0005515 [Name: protein binding]; GO:0035556 [Name: intracellular signal transduction]; GO:0043161 [Name: proteasome-mediated ubiquitin-dependent protein catabolic process]; GO:0019005 [Name: SCF ubiquitin ligase complex]</t>
+          <t>GO:0005742 [Name: mitochondrial outer membrane translocase complex]; GO:0030150 [Name: protein import into mitochondrial matrix]; GO:0008320 [Name: protein transmembrane transporter activity]; GO:0005741 [Name: mitochondrial outer membrane]</t>
         </is>
       </c>
       <c r="E694" t="inlineStr">
         <is>
-          <t>splA/ryanodine receptor domain and SOCS box containing gustavus</t>
+          <t>Translocase of outer membrane 40</t>
         </is>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>N5.HOG0067234</t>
+          <t>N5.HOG0067682</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
@@ -18363,24 +18363,24 @@
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>129225607</t>
+          <t>129219688</t>
         </is>
       </c>
       <c r="D695" t="inlineStr">
         <is>
-          <t>GO:0005742 [Name: mitochondrial outer membrane translocase complex]; GO:0030150 [Name: protein import into mitochondrial matrix]; GO:0008320 [Name: protein transmembrane transporter activity]; GO:0005741 [Name: mitochondrial outer membrane]</t>
+          <t>GO:0016887 [Name: ATPase activity]; GO:0005524 [Name: ATP binding]; GO:0005737 [Name: cytoplasm]; GO:0005525 [Name: GTP binding]</t>
         </is>
       </c>
       <c r="E695" t="inlineStr">
         <is>
-          <t>Translocase of outer membrane 40</t>
+          <t>obg-like ATPase 1</t>
         </is>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>N5.HOG0067682</t>
+          <t>N5.HOG0068240</t>
         </is>
       </c>
       <c r="B696" t="inlineStr">
@@ -18390,17 +18390,17 @@
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>129219688</t>
+          <t>129218522</t>
         </is>
       </c>
       <c r="D696" t="inlineStr">
         <is>
-          <t>GO:0016887 [Name: ATPase activity]; GO:0005524 [Name: ATP binding]; GO:0005737 [Name: cytoplasm]; GO:0005525 [Name: GTP binding]</t>
+          <t>GO:0007064 [Name: mitotic sister chromatid cohesion]; GO:0031390 [Name: Ctf18 RFC-like complex]</t>
         </is>
       </c>
       <c r="E696" t="inlineStr">
         <is>
-          <t>obg-like ATPase 1</t>
+          <t>chromosome transmission fidelity protein 8 homolog</t>
         </is>
       </c>
     </row>
@@ -18417,24 +18417,24 @@
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>129218522</t>
+          <t>129218521</t>
         </is>
       </c>
       <c r="D697" t="inlineStr">
         <is>
-          <t>GO:0007064 [Name: mitotic sister chromatid cohesion]; GO:0031390 [Name: Ctf18 RFC-like complex]</t>
+          <t>GO:0003712 [Name: transcription cofactor activity]; GO:0005634 [Name: nucleus]; GO:0070063 [Name: RNA polymerase binding]</t>
         </is>
       </c>
       <c r="E697" t="inlineStr">
         <is>
-          <t>chromosome transmission fidelity protein 8 homolog</t>
+          <t>transcription elongation regulator 1-like</t>
         </is>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>N5.HOG0068240</t>
+          <t>N5.HOG0068541</t>
         </is>
       </c>
       <c r="B698" t="inlineStr">
@@ -18444,51 +18444,51 @@
       </c>
       <c r="C698" t="inlineStr">
         <is>
-          <t>129218521</t>
+          <t>129229869</t>
         </is>
       </c>
       <c r="D698" t="inlineStr">
         <is>
-          <t>GO:0003712 [Name: transcription cofactor activity]; GO:0005634 [Name: nucleus]; GO:0070063 [Name: RNA polymerase binding]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E698" t="inlineStr">
         <is>
-          <t>transcription elongation regulator 1-like</t>
+          <t>UPF0488 protein C8orf33 homolog</t>
         </is>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>N5.HOG0068541</t>
+          <t>N5.HOG0002072</t>
         </is>
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>busted_ph_rev, dup_50_nonorb</t>
+          <t>silk_genes, loss_50_orb</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
         <is>
-          <t>129229869</t>
+          <t>129217362</t>
         </is>
       </c>
       <c r="D699" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GO:0008010 [Name: structural constituent of chitin-based larval cuticle]</t>
         </is>
       </c>
       <c r="E699" t="inlineStr">
         <is>
-          <t>UPF0488 protein C8orf33 homolog</t>
+          <t>proteoglycan 4-like</t>
         </is>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>N5.HOG0002072</t>
+          <t>N5.HOG0007639</t>
         </is>
       </c>
       <c r="B700" t="inlineStr">
@@ -18498,17 +18498,17 @@
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>129217362</t>
+          <t>129226755</t>
         </is>
       </c>
       <c r="D700" t="inlineStr">
         <is>
-          <t>GO:0008010 [Name: structural constituent of chitin-based larval cuticle]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E700" t="inlineStr">
         <is>
-          <t>proteoglycan 4-like</t>
+          <t>D-beta-hydroxybutyrate dehydrogenase, mitochondrial-like</t>
         </is>
       </c>
     </row>
@@ -18525,7 +18525,7 @@
       </c>
       <c r="C701" t="inlineStr">
         <is>
-          <t>129226755</t>
+          <t>129226301</t>
         </is>
       </c>
       <c r="D701" t="inlineStr">
@@ -18535,7 +18535,7 @@
       </c>
       <c r="E701" t="inlineStr">
         <is>
-          <t>D-beta-hydroxybutyrate dehydrogenase, mitochondrial-like</t>
+          <t>estradiol 17-beta-dehydrogenase 2-like</t>
         </is>
       </c>
     </row>
@@ -18552,7 +18552,7 @@
       </c>
       <c r="C702" t="inlineStr">
         <is>
-          <t>129226301</t>
+          <t>129226451</t>
         </is>
       </c>
       <c r="D702" t="inlineStr">
@@ -18562,7 +18562,7 @@
       </c>
       <c r="E702" t="inlineStr">
         <is>
-          <t>estradiol 17-beta-dehydrogenase 2-like</t>
+          <t>17-beta-hydroxysteroid dehydrogenase type 6-like</t>
         </is>
       </c>
     </row>
@@ -18579,7 +18579,7 @@
       </c>
       <c r="C703" t="inlineStr">
         <is>
-          <t>129226451</t>
+          <t>129225899</t>
         </is>
       </c>
       <c r="D703" t="inlineStr">
@@ -18589,14 +18589,14 @@
       </c>
       <c r="E703" t="inlineStr">
         <is>
-          <t>17-beta-hydroxysteroid dehydrogenase type 6-like</t>
+          <t>retinol dehydrogenase 16-like</t>
         </is>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>N5.HOG0007639</t>
+          <t>N5.HOG0011871</t>
         </is>
       </c>
       <c r="B704" t="inlineStr">
@@ -18606,24 +18606,24 @@
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>129225899</t>
+          <t>129217021</t>
         </is>
       </c>
       <c r="D704" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GO:0005506 [Name: iron ion binding]; GO:0005789 [Name: endoplasmic reticulum membrane]; GO:0006636 [Name: unsaturated fatty acid biosynthetic process]; GO:0004768 [Name: stearoyl-CoA 9-desaturase activity]</t>
         </is>
       </c>
       <c r="E704" t="inlineStr">
         <is>
-          <t>retinol dehydrogenase 16-like</t>
+          <t>acyl-CoA Delta-9 desaturase-like</t>
         </is>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>N5.HOG0011871</t>
+          <t>N5.HOG0013841</t>
         </is>
       </c>
       <c r="B705" t="inlineStr">
@@ -18633,17 +18633,17 @@
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>129217021</t>
+          <t>129220240</t>
         </is>
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>GO:0005506 [Name: iron ion binding]; GO:0005789 [Name: endoplasmic reticulum membrane]; GO:0006636 [Name: unsaturated fatty acid biosynthetic process]; GO:0004768 [Name: stearoyl-CoA 9-desaturase activity]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E705" t="inlineStr">
         <is>
-          <t>acyl-CoA Delta-9 desaturase-like</t>
+          <t>uncharacterized LOC129220240</t>
         </is>
       </c>
     </row>
@@ -18660,24 +18660,24 @@
       </c>
       <c r="C706" t="inlineStr">
         <is>
-          <t>129220240</t>
+          <t>129220023</t>
         </is>
       </c>
       <c r="D706" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GO:0016020 [Name: membrane]; GO:0071805 [Name: potassium ion transmembrane transport]; GO:0030322 [Name: stabilization of membrane potential]; GO:0022841 [Name: potassium ion leak channel activity]</t>
         </is>
       </c>
       <c r="E706" t="inlineStr">
         <is>
-          <t>uncharacterized LOC129220240</t>
+          <t>TWiK family of potassium channels protein 7-like</t>
         </is>
       </c>
     </row>
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>N5.HOG0013841</t>
+          <t>N5.HOG0017816</t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
@@ -18687,24 +18687,24 @@
       </c>
       <c r="C707" t="inlineStr">
         <is>
-          <t>129220023</t>
+          <t>129234236</t>
         </is>
       </c>
       <c r="D707" t="inlineStr">
         <is>
-          <t>GO:0016020 [Name: membrane]; GO:0071805 [Name: potassium ion transmembrane transport]; GO:0030322 [Name: stabilization of membrane potential]; GO:0022841 [Name: potassium ion leak channel activity]</t>
+          <t>GO:0030148 [Name: sphingolipid biosynthetic process]; GO:0019367 [Name: fatty acid elongation, saturated fatty acid]; GO:0034626 [Name: fatty acid elongation, polyunsaturated fatty acid]; GO:0042761 [Name: very long-chain fatty acid biosynthetic process]; GO:0005789 [Name: endoplasmic reticulum membrane]; GO:0009922 [Name: fatty acid elongase activity]; GO:0034625 [Name: fatty acid elongation, monounsaturated fatty acid]</t>
         </is>
       </c>
       <c r="E707" t="inlineStr">
         <is>
-          <t>TWiK family of potassium channels protein 7-like</t>
+          <t>elongation of very long chain fatty acids protein 1-like</t>
         </is>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>N5.HOG0017816</t>
+          <t>N5.HOG0019010</t>
         </is>
       </c>
       <c r="B708" t="inlineStr">
@@ -18714,24 +18714,24 @@
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>129234236</t>
+          <t>129219694</t>
         </is>
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>GO:0030148 [Name: sphingolipid biosynthetic process]; GO:0019367 [Name: fatty acid elongation, saturated fatty acid]; GO:0034626 [Name: fatty acid elongation, polyunsaturated fatty acid]; GO:0042761 [Name: very long-chain fatty acid biosynthetic process]; GO:0005789 [Name: endoplasmic reticulum membrane]; GO:0009922 [Name: fatty acid elongase activity]; GO:0034625 [Name: fatty acid elongation, monounsaturated fatty acid]</t>
+          <t>GO:0003676 [Name: nucleic acid binding]; GO:0046872 [Name: metal ion binding]; GO:0016787 [Name: hydrolase activity]</t>
         </is>
       </c>
       <c r="E708" t="inlineStr">
         <is>
-          <t>elongation of very long chain fatty acids protein 1-like</t>
+          <t>venom phosphodiesterase-like</t>
         </is>
       </c>
     </row>
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>N5.HOG0019010</t>
+          <t>N5.HOG0058483</t>
         </is>
       </c>
       <c r="B709" t="inlineStr">
@@ -18741,24 +18741,24 @@
       </c>
       <c r="C709" t="inlineStr">
         <is>
-          <t>129219694</t>
+          <t>129221471</t>
         </is>
       </c>
       <c r="D709" t="inlineStr">
         <is>
-          <t>GO:0003676 [Name: nucleic acid binding]; GO:0046872 [Name: metal ion binding]; GO:0016787 [Name: hydrolase activity]</t>
+          <t>GO:0004674 [Name: protein serine/threonine kinase activity]; GO:0030688 [Name: preribosome, small subunit precursor]; GO:0005634 [Name: nucleus]; GO:0030490 [Name: maturation of SSU-rRNA]; GO:0005829 [Name: cytosol]; GO:0006468 [Name: protein phosphorylation]; GO:0005524 [Name: ATP binding]</t>
         </is>
       </c>
       <c r="E709" t="inlineStr">
         <is>
-          <t>venom phosphodiesterase-like</t>
+          <t>RIO kinase 2</t>
         </is>
       </c>
     </row>
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>N5.HOG0058483</t>
+          <t>N5.HOG0064011</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
@@ -18768,44 +18768,44 @@
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>129221471</t>
+          <t>129231229</t>
         </is>
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>GO:0004674 [Name: protein serine/threonine kinase activity]; GO:0030688 [Name: preribosome, small subunit precursor]; GO:0005634 [Name: nucleus]; GO:0030490 [Name: maturation of SSU-rRNA]; GO:0005829 [Name: cytosol]; GO:0006468 [Name: protein phosphorylation]; GO:0005524 [Name: ATP binding]</t>
+          <t>GO:0016747 [Name: transferase activity, transferring acyl groups other than amino-acyl groups]</t>
         </is>
       </c>
       <c r="E710" t="inlineStr">
         <is>
-          <t>RIO kinase 2</t>
+          <t>uncharacterized LOC129231229</t>
         </is>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>N5.HOG0064011</t>
+          <t>N5.HOG0041541</t>
         </is>
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>silk_genes, loss_50_orb</t>
+          <t>busted_ph_rev, loss_50_orb</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
         <is>
-          <t>129231229</t>
+          <t>129219436</t>
         </is>
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>GO:0016747 [Name: transferase activity, transferring acyl groups other than amino-acyl groups]</t>
+          <t>GO:0046872 [Name: metal ion binding]; GO:0005634 [Name: nucleus]; GO:0006397 [Name: mRNA processing]; GO:0003723 [Name: RNA binding]</t>
         </is>
       </c>
       <c r="E711" t="inlineStr">
         <is>
-          <t>uncharacterized LOC129231229</t>
+          <t>RNA-binding protein 26-like</t>
         </is>
       </c>
     </row>
@@ -18822,12 +18822,12 @@
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>129219436</t>
+          <t>129222231</t>
         </is>
       </c>
       <c r="D712" t="inlineStr">
         <is>
-          <t>GO:0046872 [Name: metal ion binding]; GO:0005634 [Name: nucleus]; GO:0006397 [Name: mRNA processing]; GO:0003723 [Name: RNA binding]</t>
+          <t>GO:0006397 [Name: mRNA processing]; GO:0046872 [Name: metal ion binding]; GO:0003723 [Name: RNA binding]; GO:0005634 [Name: nucleus]</t>
         </is>
       </c>
       <c r="E712" t="inlineStr">
@@ -18839,7 +18839,7 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>N5.HOG0041541</t>
+          <t>N5.HOG0061595</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
@@ -18849,24 +18849,24 @@
       </c>
       <c r="C713" t="inlineStr">
         <is>
-          <t>129222231</t>
+          <t>129220821</t>
         </is>
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>GO:0006397 [Name: mRNA processing]; GO:0046872 [Name: metal ion binding]; GO:0003723 [Name: RNA binding]; GO:0005634 [Name: nucleus]</t>
+          <t>GO:0005215 [Name: transporter activity]; GO:0006810 [Name: transport]</t>
         </is>
       </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t>RNA-binding protein 26-like</t>
+          <t>transmembrane protein 184B-like</t>
         </is>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>N5.HOG0061595</t>
+          <t>N5.HOG0062169</t>
         </is>
       </c>
       <c r="B714" t="inlineStr">
@@ -18876,24 +18876,24 @@
       </c>
       <c r="C714" t="inlineStr">
         <is>
-          <t>129220821</t>
+          <t>129217728</t>
         </is>
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t>GO:0005215 [Name: transporter activity]; GO:0006810 [Name: transport]</t>
+          <t>GO:0005515 [Name: protein binding]</t>
         </is>
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>transmembrane protein 184B-like</t>
+          <t>F-box protein 42</t>
         </is>
       </c>
     </row>
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>N5.HOG0062169</t>
+          <t>N5.HOG0062483</t>
         </is>
       </c>
       <c r="B715" t="inlineStr">
@@ -18903,24 +18903,24 @@
       </c>
       <c r="C715" t="inlineStr">
         <is>
-          <t>129217728</t>
+          <t>129224909</t>
         </is>
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>GO:0005515 [Name: protein binding]</t>
+          <t>GO:0005814 [Name: centriole]; GO:0060271 [Name: cilium assembly]; GO:0045162 [Name: clustering of voltage-gated sodium channels]</t>
         </is>
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>F-box protein 42</t>
+          <t>sodium channel and clathrin linker 1-like</t>
         </is>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>N5.HOG0062483</t>
+          <t>N5.HOG0065529</t>
         </is>
       </c>
       <c r="B716" t="inlineStr">
@@ -18930,24 +18930,24 @@
       </c>
       <c r="C716" t="inlineStr">
         <is>
-          <t>129224909</t>
+          <t>129221907</t>
         </is>
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>GO:0005814 [Name: centriole]; GO:0060271 [Name: cilium assembly]; GO:0045162 [Name: clustering of voltage-gated sodium channels]</t>
+          <t>GO:0005515 [Name: protein binding]; GO:0005524 [Name: ATP binding]; GO:0004674 [Name: protein serine/threonine kinase activity]; GO:0007163 [Name: establishment or maintenance of cell polarity]; GO:0006468 [Name: protein phosphorylation]</t>
         </is>
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>sodium channel and clathrin linker 1-like</t>
+          <t>protein kinase C iota type</t>
         </is>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>N5.HOG0065529</t>
+          <t>N5.HOG0069099</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
@@ -18957,24 +18957,24 @@
       </c>
       <c r="C717" t="inlineStr">
         <is>
-          <t>129221907</t>
+          <t>129219728</t>
         </is>
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>GO:0005515 [Name: protein binding]; GO:0005524 [Name: ATP binding]; GO:0004674 [Name: protein serine/threonine kinase activity]; GO:0007163 [Name: establishment or maintenance of cell polarity]; GO:0006468 [Name: protein phosphorylation]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>protein kinase C iota type</t>
+          <t>uncharacterized LOC129219728</t>
         </is>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>N5.HOG0069099</t>
+          <t>N5.HOG0069528</t>
         </is>
       </c>
       <c r="B718" t="inlineStr">
@@ -18984,24 +18984,24 @@
       </c>
       <c r="C718" t="inlineStr">
         <is>
-          <t>129219728</t>
+          <t>129227418</t>
         </is>
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GO:0046983 [Name: protein dimerization activity]</t>
         </is>
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>uncharacterized LOC129219728</t>
+          <t>uncharacterized LOC129227418</t>
         </is>
       </c>
     </row>
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>N5.HOG0069528</t>
+          <t>N5.HOG0069782</t>
         </is>
       </c>
       <c r="B719" t="inlineStr">
@@ -19011,51 +19011,51 @@
       </c>
       <c r="C719" t="inlineStr">
         <is>
-          <t>129227418</t>
+          <t>129218312</t>
         </is>
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>GO:0046983 [Name: protein dimerization activity]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>uncharacterized LOC129227418</t>
+          <t>uncharacterized LOC129218312</t>
         </is>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>N5.HOG0069782</t>
+          <t>N5.HOG0032852</t>
         </is>
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>busted_ph_rev, loss_50_orb</t>
+          <t>busted_ph, loss_50_nonorb</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>129218312</t>
+          <t>129218644</t>
         </is>
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GO:0000407 [Name: pre-autophagosomal structure]; GO:0000045 [Name: autophagosome assembly]; GO:0034497 [Name: protein localization to pre-autophagosomal structure]; GO:0000423 [Name: macromitophagy]; GO:0034727 [Name: piecemeal microautophagy of nucleus]; GO:1990316 [Name: ATG1/ULK1 kinase complex]; GO:0005829 [Name: cytosol]; GO:0019898 [Name: extrinsic component of membrane]</t>
         </is>
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>uncharacterized LOC129218312</t>
+          <t>autophagy-related protein 13-like</t>
         </is>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>N5.HOG0032852</t>
+          <t>N5.HOG0048599</t>
         </is>
       </c>
       <c r="B721" t="inlineStr">
@@ -19065,24 +19065,24 @@
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>129218644</t>
+          <t>129223894</t>
         </is>
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>GO:0000407 [Name: pre-autophagosomal structure]; GO:0000045 [Name: autophagosome assembly]; GO:0034497 [Name: protein localization to pre-autophagosomal structure]; GO:0000423 [Name: macromitophagy]; GO:0034727 [Name: piecemeal microautophagy of nucleus]; GO:1990316 [Name: ATG1/ULK1 kinase complex]; GO:0005829 [Name: cytosol]; GO:0019898 [Name: extrinsic component of membrane]</t>
+          <t>GO:0004825 [Name: methionine-tRNA ligase activity]; GO:0005524 [Name: ATP binding]; GO:0006431 [Name: methionyl-tRNA aminoacylation]</t>
         </is>
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>autophagy-related protein 13-like</t>
+          <t>Methionyl-tRNA synthetase, mitochondrial</t>
         </is>
       </c>
     </row>
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>N5.HOG0048599</t>
+          <t>N5.HOG0066106</t>
         </is>
       </c>
       <c r="B722" t="inlineStr">
@@ -19092,24 +19092,24 @@
       </c>
       <c r="C722" t="inlineStr">
         <is>
-          <t>129223894</t>
+          <t>129222606</t>
         </is>
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>GO:0004825 [Name: methionine-tRNA ligase activity]; GO:0005524 [Name: ATP binding]; GO:0006431 [Name: methionyl-tRNA aminoacylation]</t>
+          <t>GO:0005634 [Name: nucleus]; GO:0070773 [Name: protein-N-terminal glutamine amidohydrolase activity]; GO:0005829 [Name: cytosol]; GO:0008418 [Name: protein-N-terminal asparagine amidohydrolase activity]</t>
         </is>
       </c>
       <c r="E722" t="inlineStr">
         <is>
-          <t>Methionyl-tRNA synthetase, mitochondrial</t>
+          <t>N-terminal glutamine amidase tungus</t>
         </is>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>N5.HOG0066106</t>
+          <t>N5.HOG0066729</t>
         </is>
       </c>
       <c r="B723" t="inlineStr">
@@ -19119,24 +19119,24 @@
       </c>
       <c r="C723" t="inlineStr">
         <is>
-          <t>129222606</t>
+          <t>129234541</t>
         </is>
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t>GO:0005634 [Name: nucleus]; GO:0070773 [Name: protein-N-terminal glutamine amidohydrolase activity]; GO:0005829 [Name: cytosol]; GO:0008418 [Name: protein-N-terminal asparagine amidohydrolase activity]</t>
+          <t>GO:0016020 [Name: membrane]</t>
         </is>
       </c>
       <c r="E723" t="inlineStr">
         <is>
-          <t>N-terminal glutamine amidase tungus</t>
+          <t>transmembrane protein 209-like</t>
         </is>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>N5.HOG0066729</t>
+          <t>N5.HOG0067048</t>
         </is>
       </c>
       <c r="B724" t="inlineStr">
@@ -19146,24 +19146,24 @@
       </c>
       <c r="C724" t="inlineStr">
         <is>
-          <t>129234541</t>
+          <t>129221334</t>
         </is>
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>GO:0016020 [Name: membrane]</t>
+          <t>GO:0005737 [Name: cytoplasm]; GO:0008173 [Name: RNA methyltransferase activity]; GO:0010586 [Name: miRNA metabolic process]; GO:2000632 [Name: negative regulation of pre-miRNA processing]; GO:0008171 [Name: O-methyltransferase activity]</t>
         </is>
       </c>
       <c r="E724" t="inlineStr">
         <is>
-          <t>transmembrane protein 209-like</t>
+          <t>pre-miRNA 5'-monophosphate methyltransferase-like</t>
         </is>
       </c>
     </row>
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>N5.HOG0067048</t>
+          <t>N5.HOG0068962</t>
         </is>
       </c>
       <c r="B725" t="inlineStr">
@@ -19173,24 +19173,24 @@
       </c>
       <c r="C725" t="inlineStr">
         <is>
-          <t>129221334</t>
+          <t>129217212</t>
         </is>
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>GO:0005737 [Name: cytoplasm]; GO:0008173 [Name: RNA methyltransferase activity]; GO:0010586 [Name: miRNA metabolic process]; GO:2000632 [Name: negative regulation of pre-miRNA processing]; GO:0008171 [Name: O-methyltransferase activity]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>pre-miRNA 5'-monophosphate methyltransferase-like</t>
+          <t>out at first</t>
         </is>
       </c>
     </row>
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>N5.HOG0068962</t>
+          <t>N5.HOG0069577</t>
         </is>
       </c>
       <c r="B726" t="inlineStr">
@@ -19200,44 +19200,44 @@
       </c>
       <c r="C726" t="inlineStr">
         <is>
-          <t>129217212</t>
+          <t>129219120</t>
         </is>
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GO:0000981 [Name: RNA polymerase II transcription factor activity, sequence-specific DNA binding]; GO:0005634 [Name: nucleus]; GO:0006357 [Name: regulation of transcription from RNA polymerase II promoter]; GO:0030154 [Name: cell differentiation]; GO:0000978 [Name: RNA polymerase II core promoter proximal region sequence-specific DNA binding]</t>
         </is>
       </c>
       <c r="E726" t="inlineStr">
         <is>
-          <t>out at first</t>
+          <t>homeobox protein vnd-like</t>
         </is>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>N5.HOG0069577</t>
+          <t>N5.HOG0004508</t>
         </is>
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>busted_ph, loss_50_nonorb</t>
+          <t>silk_genes, dup_50_orb</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
         <is>
-          <t>129219120</t>
+          <t>129220187</t>
         </is>
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>GO:0000981 [Name: RNA polymerase II transcription factor activity, sequence-specific DNA binding]; GO:0005634 [Name: nucleus]; GO:0006357 [Name: regulation of transcription from RNA polymerase II promoter]; GO:0030154 [Name: cell differentiation]; GO:0000978 [Name: RNA polymerase II core promoter proximal region sequence-specific DNA binding]</t>
+          <t>GO:0000281 [Name: mitotic cytokinesis]; GO:0040001 [Name: establishment of mitotic spindle localization]; GO:0005874 [Name: microtubule]; GO:0007076 [Name: mitotic chromosome condensation]; GO:0072686 [Name: mitotic spindle]; GO:0005730 [Name: nucleolus]; GO:0008017 [Name: microtubule binding]</t>
         </is>
       </c>
       <c r="E727" t="inlineStr">
         <is>
-          <t>homeobox protein vnd-like</t>
+          <t>Mitotic spindle and nuclear protein</t>
         </is>
       </c>
     </row>
@@ -19254,24 +19254,24 @@
       </c>
       <c r="C728" t="inlineStr">
         <is>
-          <t>129220187</t>
+          <t>129220188</t>
         </is>
       </c>
       <c r="D728" t="inlineStr">
         <is>
-          <t>GO:0000281 [Name: mitotic cytokinesis]; GO:0040001 [Name: establishment of mitotic spindle localization]; GO:0005874 [Name: microtubule]; GO:0007076 [Name: mitotic chromosome condensation]; GO:0072686 [Name: mitotic spindle]; GO:0005730 [Name: nucleolus]; GO:0008017 [Name: microtubule binding]</t>
+          <t>GO:0004867 [Name: serine-type endopeptidase inhibitor activity]; GO:0005615 [Name: extracellular space]</t>
         </is>
       </c>
       <c r="E728" t="inlineStr">
         <is>
-          <t>Mitotic spindle and nuclear protein</t>
+          <t>actinia tenebrosa protease inhibitors-like</t>
         </is>
       </c>
     </row>
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>N5.HOG0004508</t>
+          <t>N5.HOG0026249</t>
         </is>
       </c>
       <c r="B729" t="inlineStr">
@@ -19281,17 +19281,17 @@
       </c>
       <c r="C729" t="inlineStr">
         <is>
-          <t>129220188</t>
+          <t>129231419</t>
         </is>
       </c>
       <c r="D729" t="inlineStr">
         <is>
-          <t>GO:0004867 [Name: serine-type endopeptidase inhibitor activity]; GO:0005615 [Name: extracellular space]</t>
+          <t>GO:0008757 [Name: S-adenosylmethionine-dependent methyltransferase activity]</t>
         </is>
       </c>
       <c r="E729" t="inlineStr">
         <is>
-          <t>actinia tenebrosa protease inhibitors-like</t>
+          <t>thiol S-methyltransferase METTL7B-like</t>
         </is>
       </c>
     </row>
@@ -19308,7 +19308,7 @@
       </c>
       <c r="C730" t="inlineStr">
         <is>
-          <t>129231419</t>
+          <t>129231241</t>
         </is>
       </c>
       <c r="D730" t="inlineStr">
@@ -19318,14 +19318,14 @@
       </c>
       <c r="E730" t="inlineStr">
         <is>
-          <t>thiol S-methyltransferase METTL7B-like</t>
+          <t>putative methyltransferase-like protein 7A</t>
         </is>
       </c>
     </row>
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>N5.HOG0026249</t>
+          <t>N5.HOG0032766</t>
         </is>
       </c>
       <c r="B731" t="inlineStr">
@@ -19335,24 +19335,24 @@
       </c>
       <c r="C731" t="inlineStr">
         <is>
-          <t>129231241</t>
+          <t>129231860</t>
         </is>
       </c>
       <c r="D731" t="inlineStr">
         <is>
-          <t>GO:0008757 [Name: S-adenosylmethionine-dependent methyltransferase activity]</t>
+          <t>GO:0006508 [Name: proteolysis]; GO:0004197 [Name: cysteine-type endopeptidase activity]</t>
         </is>
       </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>putative methyltransferase-like protein 7A</t>
+          <t>caspase-7-like</t>
         </is>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>N5.HOG0032766</t>
+          <t>N5.HOG0035603</t>
         </is>
       </c>
       <c r="B732" t="inlineStr">
@@ -19362,24 +19362,24 @@
       </c>
       <c r="C732" t="inlineStr">
         <is>
-          <t>129231860</t>
+          <t>129225032</t>
         </is>
       </c>
       <c r="D732" t="inlineStr">
         <is>
-          <t>GO:0006508 [Name: proteolysis]; GO:0004197 [Name: cysteine-type endopeptidase activity]</t>
+          <t>GO:0016020 [Name: membrane]; GO:0006955 [Name: immune response]; GO:0002224 [Name: toll-like receptor signaling pathway]; GO:0004888 [Name: transmembrane signaling receptor activity]; GO:0005515 [Name: protein binding]</t>
         </is>
       </c>
       <c r="E732" t="inlineStr">
         <is>
-          <t>caspase-7-like</t>
+          <t>protein toll-like</t>
         </is>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>N5.HOG0035603</t>
+          <t>N5.HOG0044354</t>
         </is>
       </c>
       <c r="B733" t="inlineStr">
@@ -19389,24 +19389,24 @@
       </c>
       <c r="C733" t="inlineStr">
         <is>
-          <t>129225032</t>
+          <t>129222205</t>
         </is>
       </c>
       <c r="D733" t="inlineStr">
         <is>
-          <t>GO:0016020 [Name: membrane]; GO:0006955 [Name: immune response]; GO:0002224 [Name: toll-like receptor signaling pathway]; GO:0004888 [Name: transmembrane signaling receptor activity]; GO:0005515 [Name: protein binding]</t>
+          <t>GO:0006357 [Name: regulation of transcription from RNA polymerase II promoter]; GO:0000981 [Name: RNA polymerase II transcription factor activity, sequence-specific DNA binding]; GO:0005634 [Name: nucleus]; GO:0000978 [Name: RNA polymerase II core promoter proximal region sequence-specific DNA binding]</t>
         </is>
       </c>
       <c r="E733" t="inlineStr">
         <is>
-          <t>protein toll-like</t>
+          <t>homeobox protein abdominal-B-like</t>
         </is>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>N5.HOG0044354</t>
+          <t>N5.HOG0053556</t>
         </is>
       </c>
       <c r="B734" t="inlineStr">
@@ -19416,17 +19416,17 @@
       </c>
       <c r="C734" t="inlineStr">
         <is>
-          <t>129222205</t>
+          <t>129230277</t>
         </is>
       </c>
       <c r="D734" t="inlineStr">
         <is>
-          <t>GO:0006357 [Name: regulation of transcription from RNA polymerase II promoter]; GO:0000981 [Name: RNA polymerase II transcription factor activity, sequence-specific DNA binding]; GO:0005634 [Name: nucleus]; GO:0000978 [Name: RNA polymerase II core promoter proximal region sequence-specific DNA binding]</t>
+          <t>GO:0005793 [Name: endoplasmic reticulum-Golgi intermediate compartment]; GO:0005537 [Name: mannose binding]; GO:0000139 [Name: Golgi membrane]; GO:0030134 [Name: ER to Golgi transport vesicle]; GO:0005789 [Name: endoplasmic reticulum membrane]; GO:0006888 [Name: ER to Golgi vesicle-mediated transport]; GO:0007030 [Name: Golgi organization]; GO:0007029 [Name: endoplasmic reticulum organization]</t>
         </is>
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>homeobox protein abdominal-B-like</t>
+          <t>VIP36-like protein</t>
         </is>
       </c>
     </row>
@@ -19441,31 +19441,19 @@
           <t>silk_genes, dup_50_orb</t>
         </is>
       </c>
-      <c r="C735" t="inlineStr">
-        <is>
-          <t>129230277</t>
-        </is>
-      </c>
-      <c r="D735" t="inlineStr">
-        <is>
-          <t>GO:0005793 [Name: endoplasmic reticulum-Golgi intermediate compartment]; GO:0005537 [Name: mannose binding]; GO:0000139 [Name: Golgi membrane]; GO:0030134 [Name: ER to Golgi transport vesicle]; GO:0005789 [Name: endoplasmic reticulum membrane]; GO:0006888 [Name: ER to Golgi vesicle-mediated transport]; GO:0007030 [Name: Golgi organization]; GO:0007029 [Name: endoplasmic reticulum organization]</t>
-        </is>
-      </c>
-      <c r="E735" t="inlineStr">
-        <is>
-          <t>VIP36-like protein</t>
-        </is>
-      </c>
+      <c r="C735" t="inlineStr"/>
+      <c r="D735" t="inlineStr"/>
+      <c r="E735" t="inlineStr"/>
     </row>
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>N5.HOG0053556</t>
+          <t>N5.HOG0019239</t>
         </is>
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>silk_genes, dup_50_orb</t>
+          <t>dup_50_nonorb, loss_50_nonorb</t>
         </is>
       </c>
       <c r="C736" t="inlineStr"/>
@@ -19475,7 +19463,7 @@
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>N5.HOG0019239</t>
+          <t>N5.HOG0034119</t>
         </is>
       </c>
       <c r="B737" t="inlineStr">
@@ -19483,14 +19471,26 @@
           <t>dup_50_nonorb, loss_50_nonorb</t>
         </is>
       </c>
-      <c r="C737" t="inlineStr"/>
-      <c r="D737" t="inlineStr"/>
-      <c r="E737" t="inlineStr"/>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>129235181</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>GO:0042989 [Name: sequestering of actin monomers]; GO:0003785 [Name: actin monomer binding]; GO:0005938 [Name: cell cortex]</t>
+        </is>
+      </c>
+      <c r="E737" t="inlineStr">
+        <is>
+          <t>uncharacterized LOC129235181</t>
+        </is>
+      </c>
     </row>
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>N5.HOG0034119</t>
+          <t>N5.HOG0055703</t>
         </is>
       </c>
       <c r="B738" t="inlineStr">
@@ -19500,24 +19500,24 @@
       </c>
       <c r="C738" t="inlineStr">
         <is>
-          <t>129235181</t>
+          <t>129222075</t>
         </is>
       </c>
       <c r="D738" t="inlineStr">
         <is>
-          <t>GO:0042989 [Name: sequestering of actin monomers]; GO:0003785 [Name: actin monomer binding]; GO:0005938 [Name: cell cortex]</t>
+          <t>GO:0006368 [Name: transcription elongation from RNA polymerase II promoter]; GO:0000993 [Name: RNA polymerase II core binding]; GO:0032968 [Name: positive regulation of transcription elongation from RNA polymerase II promoter]; GO:0016593 [Name: Cdc73/Paf1 complex]</t>
         </is>
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t>uncharacterized LOC129235181</t>
+          <t>cell division cycle 73 hyrax</t>
         </is>
       </c>
     </row>
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>N5.HOG0055703</t>
+          <t>N5.HOG0061901</t>
         </is>
       </c>
       <c r="B739" t="inlineStr">
@@ -19527,24 +19527,24 @@
       </c>
       <c r="C739" t="inlineStr">
         <is>
-          <t>129222075</t>
+          <t>129221481</t>
         </is>
       </c>
       <c r="D739" t="inlineStr">
         <is>
-          <t>GO:0006368 [Name: transcription elongation from RNA polymerase II promoter]; GO:0000993 [Name: RNA polymerase II core binding]; GO:0032968 [Name: positive regulation of transcription elongation from RNA polymerase II promoter]; GO:0016593 [Name: Cdc73/Paf1 complex]</t>
+          <t>GO:0016020 [Name: membrane]</t>
         </is>
       </c>
       <c r="E739" t="inlineStr">
         <is>
-          <t>cell division cycle 73 hyrax</t>
+          <t>uncharacterized LOC129221481</t>
         </is>
       </c>
     </row>
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>N5.HOG0061901</t>
+          <t>N5.HOG0065745</t>
         </is>
       </c>
       <c r="B740" t="inlineStr">
@@ -19552,26 +19552,14 @@
           <t>dup_50_nonorb, loss_50_nonorb</t>
         </is>
       </c>
-      <c r="C740" t="inlineStr">
-        <is>
-          <t>129221481</t>
-        </is>
-      </c>
-      <c r="D740" t="inlineStr">
-        <is>
-          <t>GO:0016020 [Name: membrane]</t>
-        </is>
-      </c>
-      <c r="E740" t="inlineStr">
-        <is>
-          <t>uncharacterized LOC129221481</t>
-        </is>
-      </c>
+      <c r="C740" t="inlineStr"/>
+      <c r="D740" t="inlineStr"/>
+      <c r="E740" t="inlineStr"/>
     </row>
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>N5.HOG0065745</t>
+          <t>N5.HOG0067467</t>
         </is>
       </c>
       <c r="B741" t="inlineStr">
@@ -19579,41 +19567,53 @@
           <t>dup_50_nonorb, loss_50_nonorb</t>
         </is>
       </c>
-      <c r="C741" t="inlineStr"/>
-      <c r="D741" t="inlineStr"/>
-      <c r="E741" t="inlineStr"/>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>129218113</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>GO:0005886 [Name: plasma membrane]; GO:0071577 [Name: zinc II ion transmembrane transport]; GO:0005385 [Name: zinc ion transmembrane transporter activity]</t>
+        </is>
+      </c>
+      <c r="E741" t="inlineStr">
+        <is>
+          <t>zinc transporter ZIP3-like</t>
+        </is>
+      </c>
     </row>
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>N5.HOG0067467</t>
+          <t>N5.HOG0002083</t>
         </is>
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>dup_50_nonorb, loss_50_nonorb</t>
+          <t>silk_genes, dup_50_orb, loss_50_nonorb</t>
         </is>
       </c>
       <c r="C742" t="inlineStr">
         <is>
-          <t>129218113</t>
+          <t>129231815</t>
         </is>
       </c>
       <c r="D742" t="inlineStr">
         <is>
-          <t>GO:0005886 [Name: plasma membrane]; GO:0071577 [Name: zinc II ion transmembrane transport]; GO:0005385 [Name: zinc ion transmembrane transporter activity]</t>
+          <t>GO:0008010 [Name: structural constituent of chitin-based larval cuticle]</t>
         </is>
       </c>
       <c r="E742" t="inlineStr">
         <is>
-          <t>zinc transporter ZIP3-like</t>
+          <t>uncharacterized LOC129231815</t>
         </is>
       </c>
     </row>
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>N5.HOG0002083</t>
+          <t>N5.HOG0011514</t>
         </is>
       </c>
       <c r="B743" t="inlineStr">
@@ -19623,24 +19623,24 @@
       </c>
       <c r="C743" t="inlineStr">
         <is>
-          <t>129231815</t>
+          <t>129223432</t>
         </is>
       </c>
       <c r="D743" t="inlineStr">
         <is>
-          <t>GO:0008010 [Name: structural constituent of chitin-based larval cuticle]</t>
+          <t>GO:0005243 [Name: gap junction channel activity]; GO:0005886 [Name: plasma membrane]; GO:0005921 [Name: gap junction]; GO:0007602 [Name: phototransduction]</t>
         </is>
       </c>
       <c r="E743" t="inlineStr">
         <is>
-          <t>uncharacterized LOC129231815</t>
+          <t>innexin inx2-like</t>
         </is>
       </c>
     </row>
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>N5.HOG0011514</t>
+          <t>N5.HOG0013383</t>
         </is>
       </c>
       <c r="B744" t="inlineStr">
@@ -19650,24 +19650,24 @@
       </c>
       <c r="C744" t="inlineStr">
         <is>
-          <t>129223432</t>
+          <t>129226844</t>
         </is>
       </c>
       <c r="D744" t="inlineStr">
         <is>
-          <t>GO:0005243 [Name: gap junction channel activity]; GO:0005886 [Name: plasma membrane]; GO:0005921 [Name: gap junction]; GO:0007602 [Name: phototransduction]</t>
+          <t>GO:0005615 [Name: extracellular space]</t>
         </is>
       </c>
       <c r="E744" t="inlineStr">
         <is>
-          <t>innexin inx2-like</t>
+          <t>uncharacterized LOC129226844</t>
         </is>
       </c>
     </row>
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>N5.HOG0013383</t>
+          <t>N5.HOG0019011</t>
         </is>
       </c>
       <c r="B745" t="inlineStr">
@@ -19677,17 +19677,17 @@
       </c>
       <c r="C745" t="inlineStr">
         <is>
-          <t>129226844</t>
+          <t>129226341</t>
         </is>
       </c>
       <c r="D745" t="inlineStr">
         <is>
-          <t>GO:0005615 [Name: extracellular space]</t>
+          <t>GO:0003676 [Name: nucleic acid binding]; GO:0046872 [Name: metal ion binding]; GO:0016787 [Name: hydrolase activity]</t>
         </is>
       </c>
       <c r="E745" t="inlineStr">
         <is>
-          <t>uncharacterized LOC129226844</t>
+          <t>venom phosphodiesterase-like</t>
         </is>
       </c>
     </row>
@@ -19704,7 +19704,7 @@
       </c>
       <c r="C746" t="inlineStr">
         <is>
-          <t>129226341</t>
+          <t>129219694</t>
         </is>
       </c>
       <c r="D746" t="inlineStr">
@@ -19721,7 +19721,7 @@
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>N5.HOG0019011</t>
+          <t>N5.HOG0026879</t>
         </is>
       </c>
       <c r="B747" t="inlineStr">
@@ -19731,24 +19731,24 @@
       </c>
       <c r="C747" t="inlineStr">
         <is>
-          <t>129219694</t>
+          <t>129224479</t>
         </is>
       </c>
       <c r="D747" t="inlineStr">
         <is>
-          <t>GO:0003676 [Name: nucleic acid binding]; GO:0046872 [Name: metal ion binding]; GO:0016787 [Name: hydrolase activity]</t>
+          <t>GO:0004518 [Name: nuclease activity]; GO:0005634 [Name: nucleus]</t>
         </is>
       </c>
       <c r="E747" t="inlineStr">
         <is>
-          <t>venom phosphodiesterase-like</t>
+          <t>constitutive coactivator of peroxisome proliferator-activated receptor gamma-like</t>
         </is>
       </c>
     </row>
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>N5.HOG0026879</t>
+          <t>N5.HOG0071283</t>
         </is>
       </c>
       <c r="B748" t="inlineStr">
@@ -19758,51 +19758,51 @@
       </c>
       <c r="C748" t="inlineStr">
         <is>
-          <t>129224479</t>
+          <t>129226255</t>
         </is>
       </c>
       <c r="D748" t="inlineStr">
         <is>
-          <t>GO:0004518 [Name: nuclease activity]; GO:0005634 [Name: nucleus]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E748" t="inlineStr">
         <is>
-          <t>constitutive coactivator of peroxisome proliferator-activated receptor gamma-like</t>
+          <t>uncharacterized LOC129226255</t>
         </is>
       </c>
     </row>
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>N5.HOG0071283</t>
+          <t>N5.HOG0037303</t>
         </is>
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>silk_genes, dup_50_orb, loss_50_nonorb</t>
+          <t>relaxed, dup_50_orb, loss_50_nonorb</t>
         </is>
       </c>
       <c r="C749" t="inlineStr">
         <is>
-          <t>129226255</t>
+          <t>129225975</t>
         </is>
       </c>
       <c r="D749" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GO:0000978 [Name: RNA polymerase II core promoter proximal region sequence-specific DNA binding]; GO:0000981 [Name: RNA polymerase II transcription factor activity, sequence-specific DNA binding]; GO:0006357 [Name: regulation of transcription from RNA polymerase II promoter]; GO:0005634 [Name: nucleus]</t>
         </is>
       </c>
       <c r="E749" t="inlineStr">
         <is>
-          <t>uncharacterized LOC129226255</t>
+          <t>transcription factor SOX-9-like</t>
         </is>
       </c>
     </row>
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>N5.HOG0037303</t>
+          <t>N5.HOG0037817</t>
         </is>
       </c>
       <c r="B750" t="inlineStr">
@@ -19812,17 +19812,17 @@
       </c>
       <c r="C750" t="inlineStr">
         <is>
-          <t>129225975</t>
+          <t>129225174</t>
         </is>
       </c>
       <c r="D750" t="inlineStr">
         <is>
-          <t>GO:0000978 [Name: RNA polymerase II core promoter proximal region sequence-specific DNA binding]; GO:0000981 [Name: RNA polymerase II transcription factor activity, sequence-specific DNA binding]; GO:0006357 [Name: regulation of transcription from RNA polymerase II promoter]; GO:0005634 [Name: nucleus]</t>
+          <t>GO:0030170 [Name: pyridoxal phosphate binding]; GO:0004069 [Name: L-aspartate:2-oxoglutarate aminotransferase activity]; GO:0005829 [Name: cytosol]; GO:0006532 [Name: aspartate biosynthetic process]</t>
         </is>
       </c>
       <c r="E750" t="inlineStr">
         <is>
-          <t>transcription factor SOX-9-like</t>
+          <t>aspartate aminotransferase, cytoplasmic-like</t>
         </is>
       </c>
     </row>
@@ -19837,26 +19837,14 @@
           <t>relaxed, dup_50_orb, loss_50_nonorb</t>
         </is>
       </c>
-      <c r="C751" t="inlineStr">
-        <is>
-          <t>129225174</t>
-        </is>
-      </c>
-      <c r="D751" t="inlineStr">
-        <is>
-          <t>GO:0030170 [Name: pyridoxal phosphate binding]; GO:0004069 [Name: L-aspartate:2-oxoglutarate aminotransferase activity]; GO:0005829 [Name: cytosol]; GO:0006532 [Name: aspartate biosynthetic process]</t>
-        </is>
-      </c>
-      <c r="E751" t="inlineStr">
-        <is>
-          <t>aspartate aminotransferase, cytoplasmic-like</t>
-        </is>
-      </c>
+      <c r="C751" t="inlineStr"/>
+      <c r="D751" t="inlineStr"/>
+      <c r="E751" t="inlineStr"/>
     </row>
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>N5.HOG0037817</t>
+          <t>N5.HOG0045216</t>
         </is>
       </c>
       <c r="B752" t="inlineStr">
@@ -19864,14 +19852,26 @@
           <t>relaxed, dup_50_orb, loss_50_nonorb</t>
         </is>
       </c>
-      <c r="C752" t="inlineStr"/>
-      <c r="D752" t="inlineStr"/>
-      <c r="E752" t="inlineStr"/>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>129235254</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>GO:0000981 [Name: RNA polymerase II transcription factor activity, sequence-specific DNA binding]; GO:0006357 [Name: regulation of transcription from RNA polymerase II promoter]; GO:0046983 [Name: protein dimerization activity]; GO:0000978 [Name: RNA polymerase II core promoter proximal region sequence-specific DNA binding]</t>
+        </is>
+      </c>
+      <c r="E752" t="inlineStr">
+        <is>
+          <t>upstream transcription factor usf</t>
+        </is>
+      </c>
     </row>
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>N5.HOG0045216</t>
+          <t>N5.HOG0047033</t>
         </is>
       </c>
       <c r="B753" t="inlineStr">
@@ -19881,24 +19881,24 @@
       </c>
       <c r="C753" t="inlineStr">
         <is>
-          <t>129235254</t>
+          <t>129227540</t>
         </is>
       </c>
       <c r="D753" t="inlineStr">
         <is>
-          <t>GO:0000981 [Name: RNA polymerase II transcription factor activity, sequence-specific DNA binding]; GO:0006357 [Name: regulation of transcription from RNA polymerase II promoter]; GO:0046983 [Name: protein dimerization activity]; GO:0000978 [Name: RNA polymerase II core promoter proximal region sequence-specific DNA binding]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E753" t="inlineStr">
         <is>
-          <t>upstream transcription factor usf</t>
+          <t>uncharacterized LOC129227540</t>
         </is>
       </c>
     </row>
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>N5.HOG0047033</t>
+          <t>N5.HOG0055752</t>
         </is>
       </c>
       <c r="B754" t="inlineStr">
@@ -19906,26 +19906,14 @@
           <t>relaxed, dup_50_orb, loss_50_nonorb</t>
         </is>
       </c>
-      <c r="C754" t="inlineStr">
-        <is>
-          <t>129227540</t>
-        </is>
-      </c>
-      <c r="D754" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E754" t="inlineStr">
-        <is>
-          <t>uncharacterized LOC129227540</t>
-        </is>
-      </c>
+      <c r="C754" t="inlineStr"/>
+      <c r="D754" t="inlineStr"/>
+      <c r="E754" t="inlineStr"/>
     </row>
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>N5.HOG0055752</t>
+          <t>N5.HOG0067221</t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
@@ -19933,41 +19921,53 @@
           <t>relaxed, dup_50_orb, loss_50_nonorb</t>
         </is>
       </c>
-      <c r="C755" t="inlineStr"/>
-      <c r="D755" t="inlineStr"/>
-      <c r="E755" t="inlineStr"/>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>129222939</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>GO:0006670 [Name: sphingosine metabolic process]; GO:0046839 [Name: phospholipid dephosphorylation]; GO:0042392 [Name: sphingosine-1-phosphate phosphatase activity]; GO:0005789 [Name: endoplasmic reticulum membrane]</t>
+        </is>
+      </c>
+      <c r="E755" t="inlineStr">
+        <is>
+          <t>sphingosine-1-phosphate phosphatase 2-like</t>
+        </is>
+      </c>
     </row>
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>N5.HOG0067221</t>
+          <t>N5.HOG0003890</t>
         </is>
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>relaxed, dup_50_orb, loss_50_nonorb</t>
+          <t>relaxed, dup_50_orb</t>
         </is>
       </c>
       <c r="C756" t="inlineStr">
         <is>
-          <t>129222939</t>
+          <t>129219841</t>
         </is>
       </c>
       <c r="D756" t="inlineStr">
         <is>
-          <t>GO:0006670 [Name: sphingosine metabolic process]; GO:0046839 [Name: phospholipid dephosphorylation]; GO:0042392 [Name: sphingosine-1-phosphate phosphatase activity]; GO:0005789 [Name: endoplasmic reticulum membrane]</t>
+          <t>GO:0005506 [Name: iron ion binding]; GO:0020037 [Name: heme binding]; GO:0008395 [Name: steroid hydroxylase activity]; GO:0016705 [Name: oxidoreductase activity, acting on paired donors, with incorporation or reduction of molecular oxygen]</t>
         </is>
       </c>
       <c r="E756" t="inlineStr">
         <is>
-          <t>sphingosine-1-phosphate phosphatase 2-like</t>
+          <t>cytochrome P450 3A8-like</t>
         </is>
       </c>
     </row>
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>N5.HOG0003890</t>
+          <t>N5.HOG0017344</t>
         </is>
       </c>
       <c r="B757" t="inlineStr">
@@ -19977,17 +19977,17 @@
       </c>
       <c r="C757" t="inlineStr">
         <is>
-          <t>129219841</t>
+          <t>129220321</t>
         </is>
       </c>
       <c r="D757" t="inlineStr">
         <is>
-          <t>GO:0005506 [Name: iron ion binding]; GO:0020037 [Name: heme binding]; GO:0008395 [Name: steroid hydroxylase activity]; GO:0016705 [Name: oxidoreductase activity, acting on paired donors, with incorporation or reduction of molecular oxygen]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E757" t="inlineStr">
         <is>
-          <t>cytochrome P450 3A8-like</t>
+          <t>nose resistant to fluoxetine protein 6-like</t>
         </is>
       </c>
     </row>
@@ -20004,7 +20004,7 @@
       </c>
       <c r="C758" t="inlineStr">
         <is>
-          <t>129220321</t>
+          <t>129220715</t>
         </is>
       </c>
       <c r="D758" t="inlineStr">
@@ -20014,14 +20014,14 @@
       </c>
       <c r="E758" t="inlineStr">
         <is>
-          <t>nose resistant to fluoxetine protein 6-like</t>
+          <t>uncharacterized LOC129220715</t>
         </is>
       </c>
     </row>
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>N5.HOG0017344</t>
+          <t>N5.HOG0036366</t>
         </is>
       </c>
       <c r="B759" t="inlineStr">
@@ -20031,24 +20031,24 @@
       </c>
       <c r="C759" t="inlineStr">
         <is>
-          <t>129220715</t>
+          <t>129227244</t>
         </is>
       </c>
       <c r="D759" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GO:0005773 [Name: vacuole]; GO:0004565 [Name: beta-galactosidase activity]; GO:0005975 [Name: carbohydrate metabolic process]</t>
         </is>
       </c>
       <c r="E759" t="inlineStr">
         <is>
-          <t>uncharacterized LOC129220715</t>
+          <t>beta-galactosidase-like</t>
         </is>
       </c>
     </row>
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>N5.HOG0036366</t>
+          <t>N5.HOG0044635</t>
         </is>
       </c>
       <c r="B760" t="inlineStr">
@@ -20058,24 +20058,24 @@
       </c>
       <c r="C760" t="inlineStr">
         <is>
-          <t>129227244</t>
+          <t>129218089</t>
         </is>
       </c>
       <c r="D760" t="inlineStr">
         <is>
-          <t>GO:0005773 [Name: vacuole]; GO:0004565 [Name: beta-galactosidase activity]; GO:0005975 [Name: carbohydrate metabolic process]</t>
+          <t>GO:0016020 [Name: membrane]</t>
         </is>
       </c>
       <c r="E760" t="inlineStr">
         <is>
-          <t>beta-galactosidase-like</t>
+          <t>major facilitator superfamily domain-containing protein 6-like</t>
         </is>
       </c>
     </row>
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>N5.HOG0044635</t>
+          <t>N5.HOG0066668</t>
         </is>
       </c>
       <c r="B761" t="inlineStr">
@@ -20083,21 +20083,9 @@
           <t>relaxed, dup_50_orb</t>
         </is>
       </c>
-      <c r="C761" t="inlineStr">
-        <is>
-          <t>129218089</t>
-        </is>
-      </c>
-      <c r="D761" t="inlineStr">
-        <is>
-          <t>GO:0016020 [Name: membrane]</t>
-        </is>
-      </c>
-      <c r="E761" t="inlineStr">
-        <is>
-          <t>major facilitator superfamily domain-containing protein 6-like</t>
-        </is>
-      </c>
+      <c r="C761" t="inlineStr"/>
+      <c r="D761" t="inlineStr"/>
+      <c r="E761" t="inlineStr"/>
     </row>
     <row r="762">
       <c r="A762" t="inlineStr">
@@ -20110,41 +20098,53 @@
           <t>relaxed, dup_50_orb</t>
         </is>
       </c>
-      <c r="C762" t="inlineStr"/>
-      <c r="D762" t="inlineStr"/>
-      <c r="E762" t="inlineStr"/>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>129225896</t>
+        </is>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>GO:0007346 [Name: regulation of mitotic cell cycle]; GO:0004861 [Name: cyclin-dependent protein serine/threonine kinase inhibitor activity]; GO:0005634 [Name: nucleus]; GO:0072331 [Name: signal transduction by p53 class mediator]</t>
+        </is>
+      </c>
+      <c r="E762" t="inlineStr">
+        <is>
+          <t>uncharacterized LOC129225896</t>
+        </is>
+      </c>
     </row>
     <row r="763">
       <c r="A763" t="inlineStr">
         <is>
-          <t>N5.HOG0066668</t>
+          <t>N5.HOG0033745</t>
         </is>
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>relaxed, dup_50_orb</t>
+          <t>intensified, busted_ph, loss_50_nonorb</t>
         </is>
       </c>
       <c r="C763" t="inlineStr">
         <is>
-          <t>129225896</t>
+          <t>129220339</t>
         </is>
       </c>
       <c r="D763" t="inlineStr">
         <is>
-          <t>GO:0007346 [Name: regulation of mitotic cell cycle]; GO:0004861 [Name: cyclin-dependent protein serine/threonine kinase inhibitor activity]; GO:0005634 [Name: nucleus]; GO:0072331 [Name: signal transduction by p53 class mediator]</t>
+          <t>GO:0043565 [Name: sequence-specific DNA binding]; GO:0003700 [Name: transcription factor activity, sequence-specific DNA binding]; GO:0006355 [Name: regulation of transcription, DNA-templated]</t>
         </is>
       </c>
       <c r="E763" t="inlineStr">
         <is>
-          <t>uncharacterized LOC129225896</t>
+          <t>heat shock factor protein 1-like</t>
         </is>
       </c>
     </row>
     <row r="764">
       <c r="A764" t="inlineStr">
         <is>
-          <t>N5.HOG0033745</t>
+          <t>N5.HOG0056667</t>
         </is>
       </c>
       <c r="B764" t="inlineStr">
@@ -20154,24 +20154,24 @@
       </c>
       <c r="C764" t="inlineStr">
         <is>
-          <t>129220339</t>
+          <t>129220497</t>
         </is>
       </c>
       <c r="D764" t="inlineStr">
         <is>
-          <t>GO:0043565 [Name: sequence-specific DNA binding]; GO:0003700 [Name: transcription factor activity, sequence-specific DNA binding]; GO:0006355 [Name: regulation of transcription, DNA-templated]</t>
+          <t>GO:0006285 [Name: base-excision repair, AP site formation]; GO:0005634 [Name: nucleus]; GO:0034039 [Name: 8-oxo-7,8-dihydroguanine DNA N-glycosylase activity]; GO:0003684 [Name: damaged DNA binding]; GO:0006284 [Name: base-excision repair]; GO:0006289 [Name: nucleotide-excision repair]</t>
         </is>
       </c>
       <c r="E764" t="inlineStr">
         <is>
-          <t>heat shock factor protein 1-like</t>
+          <t>8-oxoguanine DNA glycosylase</t>
         </is>
       </c>
     </row>
     <row r="765">
       <c r="A765" t="inlineStr">
         <is>
-          <t>N5.HOG0056667</t>
+          <t>N5.HOG0058262</t>
         </is>
       </c>
       <c r="B765" t="inlineStr">
@@ -20181,24 +20181,24 @@
       </c>
       <c r="C765" t="inlineStr">
         <is>
-          <t>129220497</t>
+          <t>129215997</t>
         </is>
       </c>
       <c r="D765" t="inlineStr">
         <is>
-          <t>GO:0006285 [Name: base-excision repair, AP site formation]; GO:0005634 [Name: nucleus]; GO:0034039 [Name: 8-oxo-7,8-dihydroguanine DNA N-glycosylase activity]; GO:0003684 [Name: damaged DNA binding]; GO:0006284 [Name: base-excision repair]; GO:0006289 [Name: nucleotide-excision repair]</t>
+          <t>GO:0006470 [Name: protein dephosphorylation]; GO:0043169 [Name: cation binding]; GO:0004722 [Name: protein serine/threonine phosphatase activity]</t>
         </is>
       </c>
       <c r="E765" t="inlineStr">
         <is>
-          <t>8-oxoguanine DNA glycosylase</t>
+          <t>TGF-beta-activated kinase 1 and MAP3K7-binding protein 1-like</t>
         </is>
       </c>
     </row>
     <row r="766">
       <c r="A766" t="inlineStr">
         <is>
-          <t>N5.HOG0058262</t>
+          <t>N5.HOG0066719</t>
         </is>
       </c>
       <c r="B766" t="inlineStr">
@@ -20208,24 +20208,24 @@
       </c>
       <c r="C766" t="inlineStr">
         <is>
-          <t>129215997</t>
+          <t>129234259</t>
         </is>
       </c>
       <c r="D766" t="inlineStr">
         <is>
-          <t>GO:0006470 [Name: protein dephosphorylation]; GO:0043169 [Name: cation binding]; GO:0004722 [Name: protein serine/threonine phosphatase activity]</t>
+          <t>GO:0004222 [Name: metalloendopeptidase activity]; GO:0006627 [Name: protein processing involved in protein targeting to mitochondrion]; GO:0046872 [Name: metal ion binding]; GO:0005739 [Name: mitochondrion]</t>
         </is>
       </c>
       <c r="E766" t="inlineStr">
         <is>
-          <t>TGF-beta-activated kinase 1 and MAP3K7-binding protein 1-like</t>
+          <t>mitochondrial-processing peptidase subunit alpha-like</t>
         </is>
       </c>
     </row>
     <row r="767">
       <c r="A767" t="inlineStr">
         <is>
-          <t>N5.HOG0066719</t>
+          <t>N5.HOG0067534</t>
         </is>
       </c>
       <c r="B767" t="inlineStr">
@@ -20235,51 +20235,51 @@
       </c>
       <c r="C767" t="inlineStr">
         <is>
-          <t>129234259</t>
+          <t>129218618</t>
         </is>
       </c>
       <c r="D767" t="inlineStr">
         <is>
-          <t>GO:0004222 [Name: metalloendopeptidase activity]; GO:0006627 [Name: protein processing involved in protein targeting to mitochondrion]; GO:0046872 [Name: metal ion binding]; GO:0005739 [Name: mitochondrion]</t>
+          <t>GO:0018022 [Name: peptidyl-lysine methylation]; GO:0005829 [Name: cytosol]; GO:0005737 [Name: cytoplasm]; GO:0016279 [Name: protein-lysine N-methyltransferase activity]</t>
         </is>
       </c>
       <c r="E767" t="inlineStr">
         <is>
-          <t>mitochondrial-processing peptidase subunit alpha-like</t>
+          <t>protein N-lysine methyltransferase METTL21D-like</t>
         </is>
       </c>
     </row>
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>N5.HOG0067534</t>
+          <t>N5.HOG0045582</t>
         </is>
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>intensified, busted_ph, loss_50_nonorb</t>
+          <t>silk_genes, relaxed</t>
         </is>
       </c>
       <c r="C768" t="inlineStr">
         <is>
-          <t>129218618</t>
+          <t>129234631</t>
         </is>
       </c>
       <c r="D768" t="inlineStr">
         <is>
-          <t>GO:0018022 [Name: peptidyl-lysine methylation]; GO:0005829 [Name: cytosol]; GO:0005737 [Name: cytoplasm]; GO:0016279 [Name: protein-lysine N-methyltransferase activity]</t>
+          <t>GO:0005515 [Name: protein binding]</t>
         </is>
       </c>
       <c r="E768" t="inlineStr">
         <is>
-          <t>protein N-lysine methyltransferase METTL21D-like</t>
+          <t>pre-mRNA splicing regulator USH1G-like</t>
         </is>
       </c>
     </row>
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t>N5.HOG0045582</t>
+          <t>N5.HOG0055553</t>
         </is>
       </c>
       <c r="B769" t="inlineStr">
@@ -20289,24 +20289,24 @@
       </c>
       <c r="C769" t="inlineStr">
         <is>
-          <t>129234631</t>
+          <t>129226671</t>
         </is>
       </c>
       <c r="D769" t="inlineStr">
         <is>
-          <t>GO:0005515 [Name: protein binding]</t>
+          <t>GO:0005604 [Name: basement membrane]; GO:0005615 [Name: extracellular space]; GO:0007160 [Name: cell-matrix adhesion]</t>
         </is>
       </c>
       <c r="E769" t="inlineStr">
         <is>
-          <t>pre-mRNA splicing regulator USH1G-like</t>
+          <t>SPARC-related modular calcium-binding protein 1-like</t>
         </is>
       </c>
     </row>
     <row r="770">
       <c r="A770" t="inlineStr">
         <is>
-          <t>N5.HOG0055553</t>
+          <t>N5.HOG0057412</t>
         </is>
       </c>
       <c r="B770" t="inlineStr">
@@ -20316,24 +20316,24 @@
       </c>
       <c r="C770" t="inlineStr">
         <is>
-          <t>129226671</t>
+          <t>129223015</t>
         </is>
       </c>
       <c r="D770" t="inlineStr">
         <is>
-          <t>GO:0005604 [Name: basement membrane]; GO:0005615 [Name: extracellular space]; GO:0007160 [Name: cell-matrix adhesion]</t>
+          <t>GO:0050839 [Name: cell adhesion molecule binding]; GO:0030198 [Name: extracellular matrix organization]; GO:0031012 [Name: extracellular matrix]; GO:0007155 [Name: cell adhesion]</t>
         </is>
       </c>
       <c r="E770" t="inlineStr">
         <is>
-          <t>SPARC-related modular calcium-binding protein 1-like</t>
+          <t>transforming growth factor-beta-induced protein ig-h3-like</t>
         </is>
       </c>
     </row>
     <row r="771">
       <c r="A771" t="inlineStr">
         <is>
-          <t>N5.HOG0057412</t>
+          <t>N5.HOG0060299</t>
         </is>
       </c>
       <c r="B771" t="inlineStr">
@@ -20343,51 +20343,51 @@
       </c>
       <c r="C771" t="inlineStr">
         <is>
-          <t>129223015</t>
+          <t>129227654</t>
         </is>
       </c>
       <c r="D771" t="inlineStr">
         <is>
-          <t>GO:0050839 [Name: cell adhesion molecule binding]; GO:0030198 [Name: extracellular matrix organization]; GO:0031012 [Name: extracellular matrix]; GO:0007155 [Name: cell adhesion]</t>
+          <t>GO:0009897 [Name: external side of plasma membrane]; GO:0038023 [Name: signaling receptor activity]</t>
         </is>
       </c>
       <c r="E771" t="inlineStr">
         <is>
-          <t>transforming growth factor-beta-induced protein ig-h3-like</t>
+          <t>folate receptor gamma-like</t>
         </is>
       </c>
     </row>
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
-          <t>N5.HOG0060299</t>
+          <t>N5.HOG0063881</t>
         </is>
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>silk_genes, relaxed</t>
+          <t>relaxed, busted_ph</t>
         </is>
       </c>
       <c r="C772" t="inlineStr">
         <is>
-          <t>129227654</t>
+          <t>129233017</t>
         </is>
       </c>
       <c r="D772" t="inlineStr">
         <is>
-          <t>GO:0009897 [Name: external side of plasma membrane]; GO:0038023 [Name: signaling receptor activity]</t>
+          <t>GO:0005737 [Name: cytoplasm]; GO:0016925 [Name: protein sumoylation]; GO:0019948 [Name: SUMO activating enzyme activity]; GO:0031510 [Name: SUMO activating enzyme complex]</t>
         </is>
       </c>
       <c r="E772" t="inlineStr">
         <is>
-          <t>folate receptor gamma-like</t>
+          <t>Ubiquitin-like activating enzyme 2</t>
         </is>
       </c>
     </row>
     <row r="773">
       <c r="A773" t="inlineStr">
         <is>
-          <t>N5.HOG0063881</t>
+          <t>N5.HOG0065195</t>
         </is>
       </c>
       <c r="B773" t="inlineStr">
@@ -20397,24 +20397,24 @@
       </c>
       <c r="C773" t="inlineStr">
         <is>
-          <t>129233017</t>
+          <t>129220805</t>
         </is>
       </c>
       <c r="D773" t="inlineStr">
         <is>
-          <t>GO:0005737 [Name: cytoplasm]; GO:0016925 [Name: protein sumoylation]; GO:0019948 [Name: SUMO activating enzyme activity]; GO:0031510 [Name: SUMO activating enzyme complex]</t>
+          <t>GO:0043001 [Name: Golgi to plasma membrane protein transport]; GO:0000139 [Name: Golgi membrane]; GO:0007030 [Name: Golgi organization]</t>
         </is>
       </c>
       <c r="E773" t="inlineStr">
         <is>
-          <t>Ubiquitin-like activating enzyme 2</t>
+          <t>golgin-45-like</t>
         </is>
       </c>
     </row>
     <row r="774">
       <c r="A774" t="inlineStr">
         <is>
-          <t>N5.HOG0065195</t>
+          <t>N5.HOG0065284</t>
         </is>
       </c>
       <c r="B774" t="inlineStr">
@@ -20424,24 +20424,24 @@
       </c>
       <c r="C774" t="inlineStr">
         <is>
-          <t>129220805</t>
+          <t>129223855</t>
         </is>
       </c>
       <c r="D774" t="inlineStr">
         <is>
-          <t>GO:0043001 [Name: Golgi to plasma membrane protein transport]; GO:0000139 [Name: Golgi membrane]; GO:0007030 [Name: Golgi organization]</t>
+          <t>GO:0016671 [Name: oxidoreductase activity, acting on a sulfur group of donors, disulfide as acceptor]</t>
         </is>
       </c>
       <c r="E774" t="inlineStr">
         <is>
-          <t>golgin-45-like</t>
+          <t>gamma-interferon-inducible lysosomal thiol reductase-like</t>
         </is>
       </c>
     </row>
     <row r="775">
       <c r="A775" t="inlineStr">
         <is>
-          <t>N5.HOG0065284</t>
+          <t>N5.HOG0066404</t>
         </is>
       </c>
       <c r="B775" t="inlineStr">
@@ -20451,51 +20451,51 @@
       </c>
       <c r="C775" t="inlineStr">
         <is>
-          <t>129223855</t>
+          <t>129230255</t>
         </is>
       </c>
       <c r="D775" t="inlineStr">
         <is>
-          <t>GO:0016671 [Name: oxidoreductase activity, acting on a sulfur group of donors, disulfide as acceptor]</t>
+          <t>GO:0005385 [Name: zinc ion transmembrane transporter activity]; GO:0016020 [Name: membrane]; GO:0071577 [Name: zinc II ion transmembrane transport]; GO:0006882 [Name: cellular zinc ion homeostasis]</t>
         </is>
       </c>
       <c r="E775" t="inlineStr">
         <is>
-          <t>gamma-interferon-inducible lysosomal thiol reductase-like</t>
+          <t>Zinc transporter Zip99C</t>
         </is>
       </c>
     </row>
     <row r="776">
       <c r="A776" t="inlineStr">
         <is>
-          <t>N5.HOG0066404</t>
+          <t>N5.HOG0034912</t>
         </is>
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>relaxed, busted_ph</t>
+          <t>busted_ph, loss_50_orb</t>
         </is>
       </c>
       <c r="C776" t="inlineStr">
         <is>
-          <t>129230255</t>
+          <t>129226716</t>
         </is>
       </c>
       <c r="D776" t="inlineStr">
         <is>
-          <t>GO:0005385 [Name: zinc ion transmembrane transporter activity]; GO:0016020 [Name: membrane]; GO:0071577 [Name: zinc II ion transmembrane transport]; GO:0006882 [Name: cellular zinc ion homeostasis]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E776" t="inlineStr">
         <is>
-          <t>Zinc transporter Zip99C</t>
+          <t>uncharacterized LOC129226716</t>
         </is>
       </c>
     </row>
     <row r="777">
       <c r="A777" t="inlineStr">
         <is>
-          <t>N5.HOG0034912</t>
+          <t>N5.HOG0047895</t>
         </is>
       </c>
       <c r="B777" t="inlineStr">
@@ -20505,24 +20505,24 @@
       </c>
       <c r="C777" t="inlineStr">
         <is>
-          <t>129226716</t>
+          <t>129220954</t>
         </is>
       </c>
       <c r="D777" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GO:0005515 [Name: protein binding]</t>
         </is>
       </c>
       <c r="E777" t="inlineStr">
         <is>
-          <t>uncharacterized LOC129226716</t>
+          <t>ankyrin repeat and SAM domain-containing protein 6-like</t>
         </is>
       </c>
     </row>
     <row r="778">
       <c r="A778" t="inlineStr">
         <is>
-          <t>N5.HOG0047895</t>
+          <t>N5.HOG0057723</t>
         </is>
       </c>
       <c r="B778" t="inlineStr">
@@ -20532,24 +20532,24 @@
       </c>
       <c r="C778" t="inlineStr">
         <is>
-          <t>129220954</t>
+          <t>129229411</t>
         </is>
       </c>
       <c r="D778" t="inlineStr">
         <is>
-          <t>GO:0005515 [Name: protein binding]</t>
+          <t>GO:0005515 [Name: protein binding]; GO:0031146 [Name: SCF-dependent proteasomal ubiquitin-dependent protein catabolic process]; GO:0019005 [Name: SCF ubiquitin ligase complex]; GO:0031398 [Name: positive regulation of protein ubiquitination]</t>
         </is>
       </c>
       <c r="E778" t="inlineStr">
         <is>
-          <t>ankyrin repeat and SAM domain-containing protein 6-like</t>
+          <t>F-box only protein 33-like</t>
         </is>
       </c>
     </row>
     <row r="779">
       <c r="A779" t="inlineStr">
         <is>
-          <t>N5.HOG0057723</t>
+          <t>N5.HOG0063804</t>
         </is>
       </c>
       <c r="B779" t="inlineStr">
@@ -20559,51 +20559,51 @@
       </c>
       <c r="C779" t="inlineStr">
         <is>
-          <t>129229411</t>
+          <t>129227478</t>
         </is>
       </c>
       <c r="D779" t="inlineStr">
         <is>
-          <t>GO:0005515 [Name: protein binding]; GO:0031146 [Name: SCF-dependent proteasomal ubiquitin-dependent protein catabolic process]; GO:0019005 [Name: SCF ubiquitin ligase complex]; GO:0031398 [Name: positive regulation of protein ubiquitination]</t>
+          <t>GO:0005615 [Name: extracellular space]; GO:0005515 [Name: protein binding]; GO:0031012 [Name: extracellular matrix]</t>
         </is>
       </c>
       <c r="E779" t="inlineStr">
         <is>
-          <t>F-box only protein 33-like</t>
+          <t>leucine-rich repeat-containing protein 15-like</t>
         </is>
       </c>
     </row>
     <row r="780">
       <c r="A780" t="inlineStr">
         <is>
-          <t>N5.HOG0063804</t>
+          <t>N5.HOG0025732</t>
         </is>
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>busted_ph, loss_50_orb</t>
+          <t>silk_genes, intensified, loss_50_nonorb</t>
         </is>
       </c>
       <c r="C780" t="inlineStr">
         <is>
-          <t>129227478</t>
+          <t>129216873</t>
         </is>
       </c>
       <c r="D780" t="inlineStr">
         <is>
-          <t>GO:0005615 [Name: extracellular space]; GO:0005515 [Name: protein binding]; GO:0031012 [Name: extracellular matrix]</t>
+          <t>GO:0016020 [Name: membrane]; GO:0022857 [Name: transmembrane transporter activity]; GO:0055085 [Name: transmembrane transport]</t>
         </is>
       </c>
       <c r="E780" t="inlineStr">
         <is>
-          <t>leucine-rich repeat-containing protein 15-like</t>
+          <t>organic cation transporter protein-like</t>
         </is>
       </c>
     </row>
     <row r="781">
       <c r="A781" t="inlineStr">
         <is>
-          <t>N5.HOG0025732</t>
+          <t>N5.HOG0037878</t>
         </is>
       </c>
       <c r="B781" t="inlineStr">
@@ -20613,24 +20613,24 @@
       </c>
       <c r="C781" t="inlineStr">
         <is>
-          <t>129216873</t>
+          <t>129230240</t>
         </is>
       </c>
       <c r="D781" t="inlineStr">
         <is>
-          <t>GO:0016020 [Name: membrane]; GO:0022857 [Name: transmembrane transporter activity]; GO:0055085 [Name: transmembrane transport]</t>
+          <t>GO:0016020 [Name: membrane]; GO:0015721 [Name: bile acid and bile salt transport]; GO:0008508 [Name: bile acid:sodium symporter activity]</t>
         </is>
       </c>
       <c r="E781" t="inlineStr">
         <is>
-          <t>organic cation transporter protein-like</t>
+          <t>ileal sodium/bile acid cotransporter-like</t>
         </is>
       </c>
     </row>
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t>N5.HOG0037878</t>
+          <t>N5.HOG0042193</t>
         </is>
       </c>
       <c r="B782" t="inlineStr">
@@ -20640,24 +20640,24 @@
       </c>
       <c r="C782" t="inlineStr">
         <is>
-          <t>129230240</t>
+          <t>129220591</t>
         </is>
       </c>
       <c r="D782" t="inlineStr">
         <is>
-          <t>GO:0016020 [Name: membrane]; GO:0015721 [Name: bile acid and bile salt transport]; GO:0008508 [Name: bile acid:sodium symporter activity]</t>
+          <t>GO:0007129 [Name: synapsis]; GO:0007131 [Name: reciprocal meiotic recombination]; GO:0019789 [Name: SUMO transferase activity]; GO:0000795 [Name: synaptonemal complex]; GO:0016925 [Name: protein sumoylation]</t>
         </is>
       </c>
       <c r="E782" t="inlineStr">
         <is>
-          <t>ileal sodium/bile acid cotransporter-like</t>
+          <t>probable E3 SUMO-protein ligase RNF212</t>
         </is>
       </c>
     </row>
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>N5.HOG0042193</t>
+          <t>N5.HOG0064389</t>
         </is>
       </c>
       <c r="B783" t="inlineStr">
@@ -20667,44 +20667,44 @@
       </c>
       <c r="C783" t="inlineStr">
         <is>
-          <t>129220591</t>
+          <t>129233173</t>
         </is>
       </c>
       <c r="D783" t="inlineStr">
         <is>
-          <t>GO:0007129 [Name: synapsis]; GO:0007131 [Name: reciprocal meiotic recombination]; GO:0019789 [Name: SUMO transferase activity]; GO:0000795 [Name: synaptonemal complex]; GO:0016925 [Name: protein sumoylation]</t>
+          <t>GO:0008254 [Name: 3'-nucleotidase activity]; GO:0046854 [Name: phosphatidylinositol phosphorylation]; GO:0012505 [Name: endomembrane system]</t>
         </is>
       </c>
       <c r="E783" t="inlineStr">
         <is>
-          <t>probable E3 SUMO-protein ligase RNF212</t>
+          <t>inositol monophosphatase 3-like</t>
         </is>
       </c>
     </row>
     <row r="784">
       <c r="A784" t="inlineStr">
         <is>
-          <t>N5.HOG0064389</t>
+          <t>N5.HOG0027246</t>
         </is>
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>silk_genes, intensified, loss_50_nonorb</t>
+          <t>relaxed, dup_50_nonorb, loss_50_orb</t>
         </is>
       </c>
       <c r="C784" t="inlineStr">
         <is>
-          <t>129233173</t>
+          <t>129230682</t>
         </is>
       </c>
       <c r="D784" t="inlineStr">
         <is>
-          <t>GO:0008254 [Name: 3'-nucleotidase activity]; GO:0046854 [Name: phosphatidylinositol phosphorylation]; GO:0012505 [Name: endomembrane system]</t>
+          <t>GO:0004888 [Name: transmembrane signaling receptor activity]; GO:0006955 [Name: immune response]; GO:0002224 [Name: toll-like receptor signaling pathway]; GO:0005515 [Name: protein binding]; GO:0016020 [Name: membrane]</t>
         </is>
       </c>
       <c r="E784" t="inlineStr">
         <is>
-          <t>inositol monophosphatase 3-like</t>
+          <t>protein toll-like</t>
         </is>
       </c>
     </row>
@@ -20721,12 +20721,12 @@
       </c>
       <c r="C785" t="inlineStr">
         <is>
-          <t>129230682</t>
+          <t>129229907</t>
         </is>
       </c>
       <c r="D785" t="inlineStr">
         <is>
-          <t>GO:0004888 [Name: transmembrane signaling receptor activity]; GO:0006955 [Name: immune response]; GO:0002224 [Name: toll-like receptor signaling pathway]; GO:0005515 [Name: protein binding]; GO:0016020 [Name: membrane]</t>
+          <t>GO:0016020 [Name: membrane]; GO:0002224 [Name: toll-like receptor signaling pathway]; GO:0004888 [Name: transmembrane signaling receptor activity]; GO:0006955 [Name: immune response]</t>
         </is>
       </c>
       <c r="E785" t="inlineStr">
@@ -20738,7 +20738,7 @@
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
-          <t>N5.HOG0027246</t>
+          <t>N5.HOG0032002</t>
         </is>
       </c>
       <c r="B786" t="inlineStr">
@@ -20748,17 +20748,17 @@
       </c>
       <c r="C786" t="inlineStr">
         <is>
-          <t>129229907</t>
+          <t>129220871</t>
         </is>
       </c>
       <c r="D786" t="inlineStr">
         <is>
-          <t>GO:0016020 [Name: membrane]; GO:0002224 [Name: toll-like receptor signaling pathway]; GO:0004888 [Name: transmembrane signaling receptor activity]; GO:0006955 [Name: immune response]</t>
+          <t>GO:0005515 [Name: protein binding]; GO:0005829 [Name: cytosol]; GO:0022008 [Name: neurogenesis]</t>
         </is>
       </c>
       <c r="E786" t="inlineStr">
         <is>
-          <t>protein toll-like</t>
+          <t>BTB/POZ domain-containing protein 6-like</t>
         </is>
       </c>
     </row>
@@ -20775,24 +20775,24 @@
       </c>
       <c r="C787" t="inlineStr">
         <is>
-          <t>129220871</t>
+          <t>129226009</t>
         </is>
       </c>
       <c r="D787" t="inlineStr">
         <is>
-          <t>GO:0005515 [Name: protein binding]; GO:0005829 [Name: cytosol]; GO:0022008 [Name: neurogenesis]</t>
+          <t>GO:0005515 [Name: protein binding]; GO:0005829 [Name: cytosol]; GO:0022008 [Name: neurogenesis]; GO:0000932 [Name: P-body]</t>
         </is>
       </c>
       <c r="E787" t="inlineStr">
         <is>
-          <t>BTB/POZ domain-containing protein 6-like</t>
+          <t>BTB/POZ domain-containing protein 3-like</t>
         </is>
       </c>
     </row>
     <row r="788">
       <c r="A788" t="inlineStr">
         <is>
-          <t>N5.HOG0032002</t>
+          <t>N5.HOG0048201</t>
         </is>
       </c>
       <c r="B788" t="inlineStr">
@@ -20802,24 +20802,24 @@
       </c>
       <c r="C788" t="inlineStr">
         <is>
-          <t>129226009</t>
+          <t>129223337</t>
         </is>
       </c>
       <c r="D788" t="inlineStr">
         <is>
-          <t>GO:0005515 [Name: protein binding]; GO:0005829 [Name: cytosol]; GO:0022008 [Name: neurogenesis]; GO:0000932 [Name: P-body]</t>
+          <t>GO:0055085 [Name: transmembrane transport]; GO:0016020 [Name: membrane]; GO:0022857 [Name: transmembrane transporter activity]</t>
         </is>
       </c>
       <c r="E788" t="inlineStr">
         <is>
-          <t>BTB/POZ domain-containing protein 3-like</t>
+          <t>choline transporter-like protein 2</t>
         </is>
       </c>
     </row>
     <row r="789">
       <c r="A789" t="inlineStr">
         <is>
-          <t>N5.HOG0048201</t>
+          <t>N5.HOG0058337</t>
         </is>
       </c>
       <c r="B789" t="inlineStr">
@@ -20829,17 +20829,17 @@
       </c>
       <c r="C789" t="inlineStr">
         <is>
-          <t>129223337</t>
+          <t>129226069</t>
         </is>
       </c>
       <c r="D789" t="inlineStr">
         <is>
-          <t>GO:0055085 [Name: transmembrane transport]; GO:0016020 [Name: membrane]; GO:0022857 [Name: transmembrane transporter activity]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E789" t="inlineStr">
         <is>
-          <t>choline transporter-like protein 2</t>
+          <t>uncharacterized LOC129226069</t>
         </is>
       </c>
     </row>
@@ -20856,7 +20856,7 @@
       </c>
       <c r="C790" t="inlineStr">
         <is>
-          <t>129226069</t>
+          <t>129225994</t>
         </is>
       </c>
       <c r="D790" t="inlineStr">
@@ -20866,34 +20866,34 @@
       </c>
       <c r="E790" t="inlineStr">
         <is>
-          <t>uncharacterized LOC129226069</t>
+          <t>uncharacterized LOC129225994</t>
         </is>
       </c>
     </row>
     <row r="791">
       <c r="A791" t="inlineStr">
         <is>
-          <t>N5.HOG0058337</t>
+          <t>N5.HOG0013420</t>
         </is>
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>relaxed, dup_50_nonorb, loss_50_orb</t>
+          <t>silk_genes, busted_ph_rev</t>
         </is>
       </c>
       <c r="C791" t="inlineStr">
         <is>
-          <t>129225994</t>
+          <t>129217804</t>
         </is>
       </c>
       <c r="D791" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GO:0016020 [Name: membrane]</t>
         </is>
       </c>
       <c r="E791" t="inlineStr">
         <is>
-          <t>uncharacterized LOC129225994</t>
+          <t>uncharacterized LOC129217804</t>
         </is>
       </c>
     </row>
@@ -20910,7 +20910,7 @@
       </c>
       <c r="C792" t="inlineStr">
         <is>
-          <t>129217804</t>
+          <t>129223890</t>
         </is>
       </c>
       <c r="D792" t="inlineStr">
@@ -20920,7 +20920,7 @@
       </c>
       <c r="E792" t="inlineStr">
         <is>
-          <t>uncharacterized LOC129217804</t>
+          <t>uncharacterized LOC129223890</t>
         </is>
       </c>
     </row>
@@ -20937,7 +20937,7 @@
       </c>
       <c r="C793" t="inlineStr">
         <is>
-          <t>129223890</t>
+          <t>129223906</t>
         </is>
       </c>
       <c r="D793" t="inlineStr">
@@ -20947,14 +20947,14 @@
       </c>
       <c r="E793" t="inlineStr">
         <is>
-          <t>uncharacterized LOC129223890</t>
+          <t>uncharacterized LOC129223906</t>
         </is>
       </c>
     </row>
     <row r="794">
       <c r="A794" t="inlineStr">
         <is>
-          <t>N5.HOG0013420</t>
+          <t>N5.HOG0054988</t>
         </is>
       </c>
       <c r="B794" t="inlineStr">
@@ -20964,24 +20964,24 @@
       </c>
       <c r="C794" t="inlineStr">
         <is>
-          <t>129223906</t>
+          <t>129223128</t>
         </is>
       </c>
       <c r="D794" t="inlineStr">
         <is>
-          <t>GO:0016020 [Name: membrane]</t>
+          <t>GO:0071949 [Name: FAD binding]; GO:0008610 [Name: lipid biosynthetic process]; GO:0008609 [Name: alkylglycerone-phosphate synthase activity]</t>
         </is>
       </c>
       <c r="E794" t="inlineStr">
         <is>
-          <t>uncharacterized LOC129223906</t>
+          <t>alkyldihydroxyacetonephosphate synthase, peroxisomal-like</t>
         </is>
       </c>
     </row>
     <row r="795">
       <c r="A795" t="inlineStr">
         <is>
-          <t>N5.HOG0054988</t>
+          <t>N5.HOG0066554</t>
         </is>
       </c>
       <c r="B795" t="inlineStr">
@@ -20991,51 +20991,51 @@
       </c>
       <c r="C795" t="inlineStr">
         <is>
-          <t>129223128</t>
+          <t>129222175</t>
         </is>
       </c>
       <c r="D795" t="inlineStr">
         <is>
-          <t>GO:0071949 [Name: FAD binding]; GO:0008610 [Name: lipid biosynthetic process]; GO:0008609 [Name: alkylglycerone-phosphate synthase activity]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E795" t="inlineStr">
         <is>
-          <t>alkyldihydroxyacetonephosphate synthase, peroxisomal-like</t>
+          <t>uncharacterized LOC129222175</t>
         </is>
       </c>
     </row>
     <row r="796">
       <c r="A796" t="inlineStr">
         <is>
-          <t>N5.HOG0066554</t>
+          <t>N5.HOG0026722</t>
         </is>
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>silk_genes, busted_ph_rev</t>
+          <t>silk_genes, relaxed, dup_50_orb</t>
         </is>
       </c>
       <c r="C796" t="inlineStr">
         <is>
-          <t>129222175</t>
+          <t>129219726</t>
         </is>
       </c>
       <c r="D796" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GO:0006814 [Name: sodium ion transport]; GO:0016020 [Name: membrane]; GO:0055085 [Name: transmembrane transport]; GO:0015293 [Name: symporter activity]</t>
         </is>
       </c>
       <c r="E796" t="inlineStr">
         <is>
-          <t>uncharacterized LOC129222175</t>
+          <t>putative sodium-dependent multivitamin transporter</t>
         </is>
       </c>
     </row>
     <row r="797">
       <c r="A797" t="inlineStr">
         <is>
-          <t>N5.HOG0026722</t>
+          <t>N5.HOG0044336</t>
         </is>
       </c>
       <c r="B797" t="inlineStr">
@@ -21045,17 +21045,17 @@
       </c>
       <c r="C797" t="inlineStr">
         <is>
-          <t>129219726</t>
+          <t>129226367</t>
         </is>
       </c>
       <c r="D797" t="inlineStr">
         <is>
-          <t>GO:0006814 [Name: sodium ion transport]; GO:0016020 [Name: membrane]; GO:0055085 [Name: transmembrane transport]; GO:0015293 [Name: symporter activity]</t>
+          <t>GO:0000387 [Name: spliceosomal snRNP assembly]</t>
         </is>
       </c>
       <c r="E797" t="inlineStr">
         <is>
-          <t>putative sodium-dependent multivitamin transporter</t>
+          <t>gem-associated protein 2-like</t>
         </is>
       </c>
     </row>
@@ -21072,7 +21072,7 @@
       </c>
       <c r="C798" t="inlineStr">
         <is>
-          <t>129226367</t>
+          <t>129232837</t>
         </is>
       </c>
       <c r="D798" t="inlineStr">
@@ -21082,14 +21082,14 @@
       </c>
       <c r="E798" t="inlineStr">
         <is>
-          <t>gem-associated protein 2-like</t>
+          <t>RNA-binding protein 25-like</t>
         </is>
       </c>
     </row>
     <row r="799">
       <c r="A799" t="inlineStr">
         <is>
-          <t>N5.HOG0044336</t>
+          <t>N5.HOG0065834</t>
         </is>
       </c>
       <c r="B799" t="inlineStr">
@@ -21099,51 +21099,51 @@
       </c>
       <c r="C799" t="inlineStr">
         <is>
-          <t>129232837</t>
+          <t>129227735</t>
         </is>
       </c>
       <c r="D799" t="inlineStr">
         <is>
-          <t>GO:0000387 [Name: spliceosomal snRNP assembly]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E799" t="inlineStr">
         <is>
-          <t>RNA-binding protein 25-like</t>
+          <t>uncharacterized LOC129227735</t>
         </is>
       </c>
     </row>
     <row r="800">
       <c r="A800" t="inlineStr">
         <is>
-          <t>N5.HOG0065834</t>
+          <t>N5.HOG0059005</t>
         </is>
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>silk_genes, relaxed, dup_50_orb</t>
+          <t>intensified, busted_ph, dup_50_orb</t>
         </is>
       </c>
       <c r="C800" t="inlineStr">
         <is>
-          <t>129227735</t>
+          <t>129232635</t>
         </is>
       </c>
       <c r="D800" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GO:0044782 [Name: cilium organization]; GO:0005929 [Name: cilium]</t>
         </is>
       </c>
       <c r="E800" t="inlineStr">
         <is>
-          <t>uncharacterized LOC129227735</t>
+          <t>protein FAM161B-like</t>
         </is>
       </c>
     </row>
     <row r="801">
       <c r="A801" t="inlineStr">
         <is>
-          <t>N5.HOG0059005</t>
+          <t>N5.HOG0059024</t>
         </is>
       </c>
       <c r="B801" t="inlineStr">
@@ -21153,24 +21153,24 @@
       </c>
       <c r="C801" t="inlineStr">
         <is>
-          <t>129232635</t>
+          <t>129220007</t>
         </is>
       </c>
       <c r="D801" t="inlineStr">
         <is>
-          <t>GO:0044782 [Name: cilium organization]; GO:0005929 [Name: cilium]</t>
+          <t>GO:0045944 [Name: positive regulation of transcription from RNA polymerase II promoter]; GO:0046872 [Name: metal ion binding]; GO:0000976 [Name: transcription regulatory region sequence-specific DNA binding]</t>
         </is>
       </c>
       <c r="E801" t="inlineStr">
         <is>
-          <t>protein FAM161B-like</t>
+          <t>RING finger protein 10-like</t>
         </is>
       </c>
     </row>
     <row r="802">
       <c r="A802" t="inlineStr">
         <is>
-          <t>N5.HOG0059024</t>
+          <t>N5.HOG0060473</t>
         </is>
       </c>
       <c r="B802" t="inlineStr">
@@ -21180,51 +21180,51 @@
       </c>
       <c r="C802" t="inlineStr">
         <is>
-          <t>129220007</t>
+          <t>129231803</t>
         </is>
       </c>
       <c r="D802" t="inlineStr">
         <is>
-          <t>GO:0045944 [Name: positive regulation of transcription from RNA polymerase II promoter]; GO:0046872 [Name: metal ion binding]; GO:0000976 [Name: transcription regulatory region sequence-specific DNA binding]</t>
+          <t>GO:0005515 [Name: protein binding]</t>
         </is>
       </c>
       <c r="E802" t="inlineStr">
         <is>
-          <t>RING finger protein 10-like</t>
+          <t>leucine-rich repeat-containing protein 59-like</t>
         </is>
       </c>
     </row>
     <row r="803">
       <c r="A803" t="inlineStr">
         <is>
-          <t>N5.HOG0060473</t>
+          <t>N5.HOG0028321</t>
         </is>
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>intensified, busted_ph, dup_50_orb</t>
+          <t>intensified, busted_ph_rev, loss_50_orb</t>
         </is>
       </c>
       <c r="C803" t="inlineStr">
         <is>
-          <t>129231803</t>
+          <t>129231267</t>
         </is>
       </c>
       <c r="D803" t="inlineStr">
         <is>
-          <t>GO:0005515 [Name: protein binding]</t>
+          <t>GO:0008270 [Name: zinc ion binding]; GO:0030371 [Name: translation repressor activity]; GO:0003730 [Name: mRNA 3'-UTR binding]; GO:0017148 [Name: negative regulation of translation]; GO:0005515 [Name: protein binding]</t>
         </is>
       </c>
       <c r="E803" t="inlineStr">
         <is>
-          <t>leucine-rich repeat-containing protein 59-like</t>
+          <t>B-box type zinc finger protein ncl-1-like</t>
         </is>
       </c>
     </row>
     <row r="804">
       <c r="A804" t="inlineStr">
         <is>
-          <t>N5.HOG0028321</t>
+          <t>N5.HOG0032955</t>
         </is>
       </c>
       <c r="B804" t="inlineStr">
@@ -21234,24 +21234,24 @@
       </c>
       <c r="C804" t="inlineStr">
         <is>
-          <t>129231267</t>
+          <t>129220397</t>
         </is>
       </c>
       <c r="D804" t="inlineStr">
         <is>
-          <t>GO:0008270 [Name: zinc ion binding]; GO:0030371 [Name: translation repressor activity]; GO:0003730 [Name: mRNA 3'-UTR binding]; GO:0017148 [Name: negative regulation of translation]; GO:0005515 [Name: protein binding]</t>
+          <t>GO:0005737 [Name: cytoplasm]; GO:0036211 [Name: protein modification process]; GO:0004719 [Name: protein-L-isoaspartate (D-aspartate) O-methyltransferase activity]</t>
         </is>
       </c>
       <c r="E804" t="inlineStr">
         <is>
-          <t>B-box type zinc finger protein ncl-1-like</t>
+          <t>uncharacterized LOC129220397</t>
         </is>
       </c>
     </row>
     <row r="805">
       <c r="A805" t="inlineStr">
         <is>
-          <t>N5.HOG0032955</t>
+          <t>N5.HOG0048489</t>
         </is>
       </c>
       <c r="B805" t="inlineStr">
@@ -21261,51 +21261,51 @@
       </c>
       <c r="C805" t="inlineStr">
         <is>
-          <t>129220397</t>
+          <t>129229281</t>
         </is>
       </c>
       <c r="D805" t="inlineStr">
         <is>
-          <t>GO:0005737 [Name: cytoplasm]; GO:0036211 [Name: protein modification process]; GO:0004719 [Name: protein-L-isoaspartate (D-aspartate) O-methyltransferase activity]</t>
+          <t>GO:0008757 [Name: S-adenosylmethionine-dependent methyltransferase activity]; GO:0003723 [Name: RNA binding]</t>
         </is>
       </c>
       <c r="E805" t="inlineStr">
         <is>
-          <t>uncharacterized LOC129220397</t>
+          <t>alkylated DNA repair protein alkB homolog 8-like</t>
         </is>
       </c>
     </row>
     <row r="806">
       <c r="A806" t="inlineStr">
         <is>
-          <t>N5.HOG0048489</t>
+          <t>N5.HOG0025279</t>
         </is>
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>intensified, busted_ph_rev, loss_50_orb</t>
+          <t>intensified, busted_ph_rev, loss_50_nonorb</t>
         </is>
       </c>
       <c r="C806" t="inlineStr">
         <is>
-          <t>129229281</t>
+          <t>129219900</t>
         </is>
       </c>
       <c r="D806" t="inlineStr">
         <is>
-          <t>GO:0008757 [Name: S-adenosylmethionine-dependent methyltransferase activity]; GO:0003723 [Name: RNA binding]</t>
+          <t>GO:0043130 [Name: ubiquitin binding]; GO:0071797 [Name: LUBAC complex]; GO:0043161 [Name: proteasome-mediated ubiquitin-dependent protein catabolic process]; GO:0097039 [Name: protein linear polyubiquitination]; GO:0004842 [Name: ubiquitin-protein transferase activity]</t>
         </is>
       </c>
       <c r="E806" t="inlineStr">
         <is>
-          <t>alkylated DNA repair protein alkB homolog 8-like</t>
+          <t>uncharacterized LOC129219900</t>
         </is>
       </c>
     </row>
     <row r="807">
       <c r="A807" t="inlineStr">
         <is>
-          <t>N5.HOG0025279</t>
+          <t>N5.HOG0029997</t>
         </is>
       </c>
       <c r="B807" t="inlineStr">
@@ -21315,24 +21315,24 @@
       </c>
       <c r="C807" t="inlineStr">
         <is>
-          <t>129219900</t>
+          <t>129218245</t>
         </is>
       </c>
       <c r="D807" t="inlineStr">
         <is>
-          <t>GO:0043130 [Name: ubiquitin binding]; GO:0071797 [Name: LUBAC complex]; GO:0043161 [Name: proteasome-mediated ubiquitin-dependent protein catabolic process]; GO:0097039 [Name: protein linear polyubiquitination]; GO:0004842 [Name: ubiquitin-protein transferase activity]</t>
+          <t>GO:0072669 [Name: tRNA-splicing ligase complex]</t>
         </is>
       </c>
       <c r="E807" t="inlineStr">
         <is>
-          <t>uncharacterized LOC129219900</t>
+          <t>protein FAM98A-like</t>
         </is>
       </c>
     </row>
     <row r="808">
       <c r="A808" t="inlineStr">
         <is>
-          <t>N5.HOG0029997</t>
+          <t>N5.HOG0056875</t>
         </is>
       </c>
       <c r="B808" t="inlineStr">
@@ -21340,41 +21340,41 @@
           <t>intensified, busted_ph_rev, loss_50_nonorb</t>
         </is>
       </c>
-      <c r="C808" t="inlineStr">
-        <is>
-          <t>129218245</t>
-        </is>
-      </c>
-      <c r="D808" t="inlineStr">
-        <is>
-          <t>GO:0072669 [Name: tRNA-splicing ligase complex]</t>
-        </is>
-      </c>
-      <c r="E808" t="inlineStr">
-        <is>
-          <t>protein FAM98A-like</t>
-        </is>
-      </c>
+      <c r="C808" t="inlineStr"/>
+      <c r="D808" t="inlineStr"/>
+      <c r="E808" t="inlineStr"/>
     </row>
     <row r="809">
       <c r="A809" t="inlineStr">
         <is>
-          <t>N5.HOG0056875</t>
+          <t>N5.HOG0027025</t>
         </is>
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>intensified, busted_ph_rev, loss_50_nonorb</t>
-        </is>
-      </c>
-      <c r="C809" t="inlineStr"/>
-      <c r="D809" t="inlineStr"/>
-      <c r="E809" t="inlineStr"/>
+          <t>busted_ph_rev, dup_50_orb</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>129224223</t>
+        </is>
+      </c>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>GO:0005524 [Name: ATP binding]; GO:0005007 [Name: fibroblast growth factor-activated receptor activity]; GO:0033674 [Name: positive regulation of kinase activity]; GO:0006468 [Name: protein phosphorylation]; GO:0008543 [Name: fibroblast growth factor receptor signaling pathway]; GO:0043235 [Name: receptor complex]; GO:0007275 [Name: multicellular organism development]; GO:0016020 [Name: membrane]; GO:0008284 [Name: positive regulation of cell proliferation]</t>
+        </is>
+      </c>
+      <c r="E809" t="inlineStr">
+        <is>
+          <t>fibroblast growth factor receptor 4-like</t>
+        </is>
+      </c>
     </row>
     <row r="810">
       <c r="A810" t="inlineStr">
         <is>
-          <t>N5.HOG0027025</t>
+          <t>N5.HOG0062754</t>
         </is>
       </c>
       <c r="B810" t="inlineStr">
@@ -21384,44 +21384,44 @@
       </c>
       <c r="C810" t="inlineStr">
         <is>
-          <t>129224223</t>
+          <t>129227428</t>
         </is>
       </c>
       <c r="D810" t="inlineStr">
         <is>
-          <t>GO:0005524 [Name: ATP binding]; GO:0005007 [Name: fibroblast growth factor-activated receptor activity]; GO:0033674 [Name: positive regulation of kinase activity]; GO:0006468 [Name: protein phosphorylation]; GO:0008543 [Name: fibroblast growth factor receptor signaling pathway]; GO:0043235 [Name: receptor complex]; GO:0007275 [Name: multicellular organism development]; GO:0016020 [Name: membrane]; GO:0008284 [Name: positive regulation of cell proliferation]</t>
+          <t>GO:0003676 [Name: nucleic acid binding]</t>
         </is>
       </c>
       <c r="E810" t="inlineStr">
         <is>
-          <t>fibroblast growth factor receptor 4-like</t>
+          <t>R3H domain-containing protein 4-like</t>
         </is>
       </c>
     </row>
     <row r="811">
       <c r="A811" t="inlineStr">
         <is>
-          <t>N5.HOG0062754</t>
+          <t>N5.HOG0027314</t>
         </is>
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>busted_ph_rev, dup_50_orb</t>
+          <t>silk_genes, relaxed, busted_ph_rev</t>
         </is>
       </c>
       <c r="C811" t="inlineStr">
         <is>
-          <t>129227428</t>
+          <t>129225789</t>
         </is>
       </c>
       <c r="D811" t="inlineStr">
         <is>
-          <t>GO:0003676 [Name: nucleic acid binding]</t>
+          <t>GO:0031012 [Name: extracellular matrix]; GO:0007155 [Name: cell adhesion]; GO:0004867 [Name: serine-type endopeptidase inhibitor activity]</t>
         </is>
       </c>
       <c r="E811" t="inlineStr">
         <is>
-          <t>R3H domain-containing protein 4-like</t>
+          <t>spondin-1-like</t>
         </is>
       </c>
     </row>
@@ -21438,12 +21438,12 @@
       </c>
       <c r="C812" t="inlineStr">
         <is>
-          <t>129225789</t>
+          <t>129225638</t>
         </is>
       </c>
       <c r="D812" t="inlineStr">
         <is>
-          <t>GO:0031012 [Name: extracellular matrix]; GO:0007155 [Name: cell adhesion]; GO:0004867 [Name: serine-type endopeptidase inhibitor activity]</t>
+          <t>GO:0031012 [Name: extracellular matrix]; GO:0004867 [Name: serine-type endopeptidase inhibitor activity]; GO:0007155 [Name: cell adhesion]</t>
         </is>
       </c>
       <c r="E812" t="inlineStr">
@@ -21455,7 +21455,7 @@
     <row r="813">
       <c r="A813" t="inlineStr">
         <is>
-          <t>N5.HOG0027314</t>
+          <t>N5.HOG0069313</t>
         </is>
       </c>
       <c r="B813" t="inlineStr">
@@ -21465,34 +21465,34 @@
       </c>
       <c r="C813" t="inlineStr">
         <is>
-          <t>129225638</t>
+          <t>129227835</t>
         </is>
       </c>
       <c r="D813" t="inlineStr">
         <is>
-          <t>GO:0031012 [Name: extracellular matrix]; GO:0004867 [Name: serine-type endopeptidase inhibitor activity]; GO:0007155 [Name: cell adhesion]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E813" t="inlineStr">
         <is>
-          <t>spondin-1-like</t>
+          <t>uncharacterized LOC129227835</t>
         </is>
       </c>
     </row>
     <row r="814">
       <c r="A814" t="inlineStr">
         <is>
-          <t>N5.HOG0069313</t>
+          <t>N5.HOG0039393</t>
         </is>
       </c>
       <c r="B814" t="inlineStr">
         <is>
-          <t>silk_genes, relaxed, busted_ph_rev</t>
+          <t>silk_genes, intensified, dup_50_orb</t>
         </is>
       </c>
       <c r="C814" t="inlineStr">
         <is>
-          <t>129227835</t>
+          <t>129229574</t>
         </is>
       </c>
       <c r="D814" t="inlineStr">
@@ -21502,14 +21502,14 @@
       </c>
       <c r="E814" t="inlineStr">
         <is>
-          <t>uncharacterized LOC129227835</t>
+          <t>protein RCC2 homolog</t>
         </is>
       </c>
     </row>
     <row r="815">
       <c r="A815" t="inlineStr">
         <is>
-          <t>N5.HOG0039393</t>
+          <t>N5.HOG0040014</t>
         </is>
       </c>
       <c r="B815" t="inlineStr">
@@ -21519,51 +21519,51 @@
       </c>
       <c r="C815" t="inlineStr">
         <is>
-          <t>129229574</t>
+          <t>129223275</t>
         </is>
       </c>
       <c r="D815" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GO:0005506 [Name: iron ion binding]; GO:0000254 [Name: C-4 methylsterol oxidase activity]; GO:0016126 [Name: sterol biosynthetic process]</t>
         </is>
       </c>
       <c r="E815" t="inlineStr">
         <is>
-          <t>protein RCC2 homolog</t>
+          <t>fatty acid hydroxylase domain-containing protein 2-like</t>
         </is>
       </c>
     </row>
     <row r="816">
       <c r="A816" t="inlineStr">
         <is>
-          <t>N5.HOG0040014</t>
+          <t>N5.HOG0013878</t>
         </is>
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>silk_genes, intensified, dup_50_orb</t>
+          <t>silk_genes, dup_50_nonorb, loss_50_orb</t>
         </is>
       </c>
       <c r="C816" t="inlineStr">
         <is>
-          <t>129223275</t>
+          <t>129225262</t>
         </is>
       </c>
       <c r="D816" t="inlineStr">
         <is>
-          <t>GO:0005506 [Name: iron ion binding]; GO:0000254 [Name: C-4 methylsterol oxidase activity]; GO:0016126 [Name: sterol biosynthetic process]</t>
+          <t>GO:0034625 [Name: fatty acid elongation, monounsaturated fatty acid]; GO:0042761 [Name: very long-chain fatty acid biosynthetic process]; GO:0005789 [Name: endoplasmic reticulum membrane]; GO:0009922 [Name: fatty acid elongase activity]; GO:0030148 [Name: sphingolipid biosynthetic process]; GO:0019367 [Name: fatty acid elongation, saturated fatty acid]; GO:0034626 [Name: fatty acid elongation, polyunsaturated fatty acid]</t>
         </is>
       </c>
       <c r="E816" t="inlineStr">
         <is>
-          <t>fatty acid hydroxylase domain-containing protein 2-like</t>
+          <t>elongation of very long chain fatty acids protein 7-like</t>
         </is>
       </c>
     </row>
     <row r="817">
       <c r="A817" t="inlineStr">
         <is>
-          <t>N5.HOG0013878</t>
+          <t>N5.HOG0057236</t>
         </is>
       </c>
       <c r="B817" t="inlineStr">
@@ -21573,44 +21573,44 @@
       </c>
       <c r="C817" t="inlineStr">
         <is>
-          <t>129225262</t>
+          <t>129222937</t>
         </is>
       </c>
       <c r="D817" t="inlineStr">
         <is>
-          <t>GO:0034625 [Name: fatty acid elongation, monounsaturated fatty acid]; GO:0042761 [Name: very long-chain fatty acid biosynthetic process]; GO:0005789 [Name: endoplasmic reticulum membrane]; GO:0009922 [Name: fatty acid elongase activity]; GO:0030148 [Name: sphingolipid biosynthetic process]; GO:0019367 [Name: fatty acid elongation, saturated fatty acid]; GO:0034626 [Name: fatty acid elongation, polyunsaturated fatty acid]</t>
+          <t>GO:0016020 [Name: membrane]; GO:0016758 [Name: transferase activity, transferring hexosyl groups]; GO:0006486 [Name: protein glycosylation]</t>
         </is>
       </c>
       <c r="E817" t="inlineStr">
         <is>
-          <t>elongation of very long chain fatty acids protein 7-like</t>
+          <t>beta-1,3-galactosyltransferase 5-like</t>
         </is>
       </c>
     </row>
     <row r="818">
       <c r="A818" t="inlineStr">
         <is>
-          <t>N5.HOG0057236</t>
+          <t>N5.HOG0043968</t>
         </is>
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>silk_genes, dup_50_nonorb, loss_50_orb</t>
+          <t>relaxed, busted_ph_rev, loss_50_nonorb</t>
         </is>
       </c>
       <c r="C818" t="inlineStr">
         <is>
-          <t>129222937</t>
+          <t>129217037</t>
         </is>
       </c>
       <c r="D818" t="inlineStr">
         <is>
-          <t>GO:0016020 [Name: membrane]; GO:0016758 [Name: transferase activity, transferring hexosyl groups]; GO:0006486 [Name: protein glycosylation]</t>
+          <t>GO:0006486 [Name: protein glycosylation]</t>
         </is>
       </c>
       <c r="E818" t="inlineStr">
         <is>
-          <t>beta-1,3-galactosyltransferase 5-like</t>
+          <t>ribitol-5-phosphate transferase FKTN-like</t>
         </is>
       </c>
     </row>
@@ -21627,7 +21627,7 @@
       </c>
       <c r="C819" t="inlineStr">
         <is>
-          <t>129217037</t>
+          <t>129217035</t>
         </is>
       </c>
       <c r="D819" t="inlineStr">
@@ -21644,7 +21644,7 @@
     <row r="820">
       <c r="A820" t="inlineStr">
         <is>
-          <t>N5.HOG0043968</t>
+          <t>N5.HOG0062791</t>
         </is>
       </c>
       <c r="B820" t="inlineStr">
@@ -21654,51 +21654,51 @@
       </c>
       <c r="C820" t="inlineStr">
         <is>
-          <t>129217035</t>
+          <t>129222392</t>
         </is>
       </c>
       <c r="D820" t="inlineStr">
         <is>
-          <t>GO:0006486 [Name: protein glycosylation]</t>
+          <t>GO:0007015 [Name: actin filament organization]; GO:0051015 [Name: actin filament binding]</t>
         </is>
       </c>
       <c r="E820" t="inlineStr">
         <is>
-          <t>ribitol-5-phosphate transferase FKTN-like</t>
+          <t>coronin-2B-like</t>
         </is>
       </c>
     </row>
     <row r="821">
       <c r="A821" t="inlineStr">
         <is>
-          <t>N5.HOG0062791</t>
+          <t>N5.HOG0054457</t>
         </is>
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>relaxed, busted_ph_rev, loss_50_nonorb</t>
+          <t>intensified, busted_ph, loss_50_orb</t>
         </is>
       </c>
       <c r="C821" t="inlineStr">
         <is>
-          <t>129222392</t>
+          <t>129220609</t>
         </is>
       </c>
       <c r="D821" t="inlineStr">
         <is>
-          <t>GO:0007015 [Name: actin filament organization]; GO:0051015 [Name: actin filament binding]</t>
+          <t>GO:0016020 [Name: membrane]; GO:0004930 [Name: G-protein coupled receptor activity]; GO:0007166 [Name: cell surface receptor signaling pathway]; GO:0007186 [Name: G-protein coupled receptor signaling pathway]</t>
         </is>
       </c>
       <c r="E821" t="inlineStr">
         <is>
-          <t>coronin-2B-like</t>
+          <t>uncharacterized LOC129220609</t>
         </is>
       </c>
     </row>
     <row r="822">
       <c r="A822" t="inlineStr">
         <is>
-          <t>N5.HOG0054457</t>
+          <t>N5.HOG0061780</t>
         </is>
       </c>
       <c r="B822" t="inlineStr">
@@ -21708,51 +21708,51 @@
       </c>
       <c r="C822" t="inlineStr">
         <is>
-          <t>129220609</t>
+          <t>129233970</t>
         </is>
       </c>
       <c r="D822" t="inlineStr">
         <is>
-          <t>GO:0016020 [Name: membrane]; GO:0004930 [Name: G-protein coupled receptor activity]; GO:0007166 [Name: cell surface receptor signaling pathway]; GO:0007186 [Name: G-protein coupled receptor signaling pathway]</t>
+          <t>GO:0055085 [Name: transmembrane transport]; GO:0016020 [Name: membrane]; GO:0022857 [Name: transmembrane transporter activity]</t>
         </is>
       </c>
       <c r="E822" t="inlineStr">
         <is>
-          <t>uncharacterized LOC129220609</t>
+          <t>hippocampus abundant transcript 1 protein-like</t>
         </is>
       </c>
     </row>
     <row r="823">
       <c r="A823" t="inlineStr">
         <is>
-          <t>N5.HOG0061780</t>
+          <t>N5.HOG0062479</t>
         </is>
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>intensified, busted_ph, loss_50_orb</t>
+          <t>intensified, busted_ph_rev, dup_50_orb</t>
         </is>
       </c>
       <c r="C823" t="inlineStr">
         <is>
-          <t>129233970</t>
+          <t>129224049</t>
         </is>
       </c>
       <c r="D823" t="inlineStr">
         <is>
-          <t>GO:0055085 [Name: transmembrane transport]; GO:0016020 [Name: membrane]; GO:0022857 [Name: transmembrane transporter activity]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E823" t="inlineStr">
         <is>
-          <t>hippocampus abundant transcript 1 protein-like</t>
+          <t>zygotic DNA replication licensing factor mcm3-like</t>
         </is>
       </c>
     </row>
     <row r="824">
       <c r="A824" t="inlineStr">
         <is>
-          <t>N5.HOG0062479</t>
+          <t>N5.HOG0063651</t>
         </is>
       </c>
       <c r="B824" t="inlineStr">
@@ -21762,7 +21762,7 @@
       </c>
       <c r="C824" t="inlineStr">
         <is>
-          <t>129224049</t>
+          <t>129220117</t>
         </is>
       </c>
       <c r="D824" t="inlineStr">
@@ -21772,41 +21772,41 @@
       </c>
       <c r="E824" t="inlineStr">
         <is>
-          <t>zygotic DNA replication licensing factor mcm3-like</t>
+          <t>uncharacterized LOC129220117</t>
         </is>
       </c>
     </row>
     <row r="825">
       <c r="A825" t="inlineStr">
         <is>
-          <t>N5.HOG0063651</t>
+          <t>N5.HOG0058793</t>
         </is>
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>intensified, busted_ph_rev, dup_50_orb</t>
+          <t>intensified, dup_50_nonorb, loss_50_nonorb</t>
         </is>
       </c>
       <c r="C825" t="inlineStr">
         <is>
-          <t>129220117</t>
+          <t>129222677</t>
         </is>
       </c>
       <c r="D825" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GO:0004352 [Name: glutamate dehydrogenase (NAD+) activity]; GO:0005739 [Name: mitochondrion]; GO:0006538 [Name: glutamate catabolic process]</t>
         </is>
       </c>
       <c r="E825" t="inlineStr">
         <is>
-          <t>uncharacterized LOC129220117</t>
+          <t>glutamate dehydrogenase, mitochondrial</t>
         </is>
       </c>
     </row>
     <row r="826">
       <c r="A826" t="inlineStr">
         <is>
-          <t>N5.HOG0058793</t>
+          <t>N5.HOG0067456</t>
         </is>
       </c>
       <c r="B826" t="inlineStr">
@@ -21816,51 +21816,39 @@
       </c>
       <c r="C826" t="inlineStr">
         <is>
-          <t>129222677</t>
+          <t>129230732</t>
         </is>
       </c>
       <c r="D826" t="inlineStr">
         <is>
-          <t>GO:0004352 [Name: glutamate dehydrogenase (NAD+) activity]; GO:0005739 [Name: mitochondrion]; GO:0006538 [Name: glutamate catabolic process]</t>
+          <t>GO:0005832 [Name: chaperonin-containing T-complex]; GO:0005524 [Name: ATP binding]; GO:0006457 [Name: protein folding]; GO:0051082 [Name: unfolded protein binding]; GO:0016887 [Name: ATPase activity]</t>
         </is>
       </c>
       <c r="E826" t="inlineStr">
         <is>
-          <t>glutamate dehydrogenase, mitochondrial</t>
+          <t>chaperonin containing TCP1 subunit 5</t>
         </is>
       </c>
     </row>
     <row r="827">
       <c r="A827" t="inlineStr">
         <is>
-          <t>N5.HOG0067456</t>
+          <t>N5.HOG0022376</t>
         </is>
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>intensified, dup_50_nonorb, loss_50_nonorb</t>
-        </is>
-      </c>
-      <c r="C827" t="inlineStr">
-        <is>
-          <t>129230732</t>
-        </is>
-      </c>
-      <c r="D827" t="inlineStr">
-        <is>
-          <t>GO:0005832 [Name: chaperonin-containing T-complex]; GO:0005524 [Name: ATP binding]; GO:0006457 [Name: protein folding]; GO:0051082 [Name: unfolded protein binding]; GO:0016887 [Name: ATPase activity]</t>
-        </is>
-      </c>
-      <c r="E827" t="inlineStr">
-        <is>
-          <t>chaperonin containing TCP1 subunit 5</t>
-        </is>
-      </c>
+          <t>busted_ph_rev, dup_50_orb, loss_50_nonorb</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr"/>
+      <c r="D827" t="inlineStr"/>
+      <c r="E827" t="inlineStr"/>
     </row>
     <row r="828">
       <c r="A828" t="inlineStr">
         <is>
-          <t>N5.HOG0022376</t>
+          <t>N5.HOG0068430</t>
         </is>
       </c>
       <c r="B828" t="inlineStr">
@@ -21875,17 +21863,29 @@
     <row r="829">
       <c r="A829" t="inlineStr">
         <is>
-          <t>N5.HOG0068430</t>
+          <t>N5.HOG0035167</t>
         </is>
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>busted_ph_rev, dup_50_orb, loss_50_nonorb</t>
-        </is>
-      </c>
-      <c r="C829" t="inlineStr"/>
-      <c r="D829" t="inlineStr"/>
-      <c r="E829" t="inlineStr"/>
+          <t>busted_ph_rev, dup_50_nonorb, loss_50_nonorb</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>129217078</t>
+        </is>
+      </c>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>GO:0004423 [Name: iduronate-2-sulfatase activity]</t>
+        </is>
+      </c>
+      <c r="E829" t="inlineStr">
+        <is>
+          <t>iduronate 2-sulfatase-like</t>
+        </is>
+      </c>
     </row>
     <row r="830">
       <c r="A830" t="inlineStr">
@@ -21900,7 +21900,7 @@
       </c>
       <c r="C830" t="inlineStr">
         <is>
-          <t>129217078</t>
+          <t>129217079</t>
         </is>
       </c>
       <c r="D830" t="inlineStr">
@@ -21917,7 +21917,7 @@
     <row r="831">
       <c r="A831" t="inlineStr">
         <is>
-          <t>N5.HOG0035167</t>
+          <t>N5.HOG0048186</t>
         </is>
       </c>
       <c r="B831" t="inlineStr">
@@ -21927,71 +21927,71 @@
       </c>
       <c r="C831" t="inlineStr">
         <is>
-          <t>129217079</t>
+          <t>129218892</t>
         </is>
       </c>
       <c r="D831" t="inlineStr">
         <is>
-          <t>GO:0004423 [Name: iduronate-2-sulfatase activity]</t>
+          <t>GO:0001678 [Name: cellular glucose homeostasis]; GO:0005739 [Name: mitochondrion]; GO:0006096 [Name: glycolytic process]; GO:0051156 [Name: glucose 6-phosphate metabolic process]; GO:0019158 [Name: mannokinase activity]; GO:0005829 [Name: cytosol]; GO:0008865 [Name: fructokinase activity]; GO:0004340 [Name: glucokinase activity]; GO:0005524 [Name: ATP binding]; GO:0005536 [Name: glucose binding]</t>
         </is>
       </c>
       <c r="E831" t="inlineStr">
         <is>
-          <t>iduronate 2-sulfatase-like</t>
+          <t>hexokinase-1-like</t>
         </is>
       </c>
     </row>
     <row r="832">
       <c r="A832" t="inlineStr">
         <is>
-          <t>N5.HOG0048186</t>
+          <t>N5.HOG0016317</t>
         </is>
       </c>
       <c r="B832" t="inlineStr">
         <is>
-          <t>busted_ph_rev, dup_50_nonorb, loss_50_nonorb</t>
+          <t>silk_genes, dup_50_nonorb</t>
         </is>
       </c>
       <c r="C832" t="inlineStr">
         <is>
-          <t>129218892</t>
+          <t>129218263</t>
         </is>
       </c>
       <c r="D832" t="inlineStr">
         <is>
-          <t>GO:0001678 [Name: cellular glucose homeostasis]; GO:0005739 [Name: mitochondrion]; GO:0006096 [Name: glycolytic process]; GO:0051156 [Name: glucose 6-phosphate metabolic process]; GO:0019158 [Name: mannokinase activity]; GO:0005829 [Name: cytosol]; GO:0008865 [Name: fructokinase activity]; GO:0004340 [Name: glucokinase activity]; GO:0005524 [Name: ATP binding]; GO:0005536 [Name: glucose binding]</t>
+          <t>GO:0016491 [Name: oxidoreductase activity]</t>
         </is>
       </c>
       <c r="E832" t="inlineStr">
         <is>
-          <t>hexokinase-1-like</t>
+          <t>amine oxidase [flavin-containing]-like</t>
         </is>
       </c>
     </row>
     <row r="833">
       <c r="A833" t="inlineStr">
         <is>
-          <t>N5.HOG0016317</t>
+          <t>N5.HOG0058985</t>
         </is>
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>silk_genes, dup_50_nonorb</t>
+          <t>busted_ph, dup_50_nonorb</t>
         </is>
       </c>
       <c r="C833" t="inlineStr">
         <is>
-          <t>129218263</t>
+          <t>129224178</t>
         </is>
       </c>
       <c r="D833" t="inlineStr">
         <is>
-          <t>GO:0016491 [Name: oxidoreductase activity]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E833" t="inlineStr">
         <is>
-          <t>amine oxidase [flavin-containing]-like</t>
+          <t>uncharacterized LOC129224178</t>
         </is>
       </c>
     </row>
@@ -22008,7 +22008,7 @@
       </c>
       <c r="C834" t="inlineStr">
         <is>
-          <t>129224178</t>
+          <t>129224188</t>
         </is>
       </c>
       <c r="D834" t="inlineStr">
@@ -22018,24 +22018,24 @@
       </c>
       <c r="E834" t="inlineStr">
         <is>
-          <t>uncharacterized LOC129224178</t>
+          <t>uncharacterized LOC129224188</t>
         </is>
       </c>
     </row>
     <row r="835">
       <c r="A835" t="inlineStr">
         <is>
-          <t>N5.HOG0058985</t>
+          <t>N5.HOG0072004</t>
         </is>
       </c>
       <c r="B835" t="inlineStr">
         <is>
-          <t>busted_ph, dup_50_nonorb</t>
+          <t>dup_50_orb, loss_50_orb</t>
         </is>
       </c>
       <c r="C835" t="inlineStr">
         <is>
-          <t>129224188</t>
+          <t>129227657</t>
         </is>
       </c>
       <c r="D835" t="inlineStr">
@@ -22045,36 +22045,24 @@
       </c>
       <c r="E835" t="inlineStr">
         <is>
-          <t>uncharacterized LOC129224188</t>
+          <t>protein PRQFV-amide-like</t>
         </is>
       </c>
     </row>
     <row r="836">
       <c r="A836" t="inlineStr">
         <is>
-          <t>N5.HOG0072004</t>
+          <t>N5.HOG0059689</t>
         </is>
       </c>
       <c r="B836" t="inlineStr">
         <is>
-          <t>dup_50_orb, loss_50_orb</t>
-        </is>
-      </c>
-      <c r="C836" t="inlineStr">
-        <is>
-          <t>129227657</t>
-        </is>
-      </c>
-      <c r="D836" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E836" t="inlineStr">
-        <is>
-          <t>protein PRQFV-amide-like</t>
-        </is>
-      </c>
+          <t>silk_genes, relaxed, busted_ph</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr"/>
+      <c r="D836" t="inlineStr"/>
+      <c r="E836" t="inlineStr"/>
     </row>
     <row r="837">
       <c r="A837" t="inlineStr">
@@ -22087,61 +22075,73 @@
           <t>silk_genes, relaxed, busted_ph</t>
         </is>
       </c>
-      <c r="C837" t="inlineStr"/>
-      <c r="D837" t="inlineStr"/>
-      <c r="E837" t="inlineStr"/>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>129225048</t>
+        </is>
+      </c>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E837" t="inlineStr">
+        <is>
+          <t>transmembrane protein 272-like</t>
+        </is>
+      </c>
     </row>
     <row r="838">
       <c r="A838" t="inlineStr">
         <is>
-          <t>N5.HOG0059689</t>
+          <t>N5.HOG0056631</t>
         </is>
       </c>
       <c r="B838" t="inlineStr">
         <is>
-          <t>silk_genes, relaxed, busted_ph</t>
+          <t>silk_genes, intensified, dup_50_nonorb</t>
         </is>
       </c>
       <c r="C838" t="inlineStr">
         <is>
-          <t>129225048</t>
+          <t>129221489</t>
         </is>
       </c>
       <c r="D838" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GO:0005789 [Name: endoplasmic reticulum membrane]; GO:0005459 [Name: UDP-galactose transmembrane transporter activity]; GO:0000139 [Name: Golgi membrane]; GO:0005460 [Name: UDP-glucose transmembrane transporter activity]; GO:0072334 [Name: UDP-galactose transmembrane transport]</t>
         </is>
       </c>
       <c r="E838" t="inlineStr">
         <is>
-          <t>transmembrane protein 272-like</t>
+          <t>solute carrier family 35 member B1-like</t>
         </is>
       </c>
     </row>
     <row r="839">
       <c r="A839" t="inlineStr">
         <is>
-          <t>N5.HOG0056631</t>
+          <t>N5.HOG0055293</t>
         </is>
       </c>
       <c r="B839" t="inlineStr">
         <is>
-          <t>silk_genes, intensified, dup_50_nonorb</t>
+          <t>silk_genes, dup_50_orb, loss_50_orb</t>
         </is>
       </c>
       <c r="C839" t="inlineStr">
         <is>
-          <t>129221489</t>
+          <t>129222069</t>
         </is>
       </c>
       <c r="D839" t="inlineStr">
         <is>
-          <t>GO:0005789 [Name: endoplasmic reticulum membrane]; GO:0005459 [Name: UDP-galactose transmembrane transporter activity]; GO:0000139 [Name: Golgi membrane]; GO:0005460 [Name: UDP-glucose transmembrane transporter activity]; GO:0072334 [Name: UDP-galactose transmembrane transport]</t>
+          <t>GO:0005509 [Name: calcium ion binding]; GO:0007160 [Name: cell-matrix adhesion]</t>
         </is>
       </c>
       <c r="E839" t="inlineStr">
         <is>
-          <t>solute carrier family 35 member B1-like</t>
+          <t>nidogen-like</t>
         </is>
       </c>
     </row>
@@ -22158,140 +22158,140 @@
       </c>
       <c r="C840" t="inlineStr">
         <is>
-          <t>129222069</t>
+          <t>129230150</t>
         </is>
       </c>
       <c r="D840" t="inlineStr">
         <is>
-          <t>GO:0005509 [Name: calcium ion binding]; GO:0007160 [Name: cell-matrix adhesion]</t>
+          <t>GO:0007160 [Name: cell-matrix adhesion]</t>
         </is>
       </c>
       <c r="E840" t="inlineStr">
         <is>
-          <t>nidogen-like</t>
+          <t>nidogen-2-like</t>
         </is>
       </c>
     </row>
     <row r="841">
       <c r="A841" t="inlineStr">
         <is>
-          <t>N5.HOG0055293</t>
+          <t>N5.HOG0037350</t>
         </is>
       </c>
       <c r="B841" t="inlineStr">
         <is>
-          <t>silk_genes, dup_50_orb, loss_50_orb</t>
+          <t>silk_genes, dup_50_nonorb, loss_50_nonorb</t>
         </is>
       </c>
       <c r="C841" t="inlineStr">
         <is>
-          <t>129230150</t>
+          <t>129225276</t>
         </is>
       </c>
       <c r="D841" t="inlineStr">
         <is>
-          <t>GO:0007160 [Name: cell-matrix adhesion]</t>
+          <t>GO:0005789 [Name: endoplasmic reticulum membrane]; GO:0015031 [Name: protein transport]</t>
         </is>
       </c>
       <c r="E841" t="inlineStr">
         <is>
-          <t>nidogen-2-like</t>
+          <t>dual oxidase maturation factor 2-like</t>
         </is>
       </c>
     </row>
     <row r="842">
       <c r="A842" t="inlineStr">
         <is>
-          <t>N5.HOG0037350</t>
+          <t>N5.HOG0067416</t>
         </is>
       </c>
       <c r="B842" t="inlineStr">
         <is>
-          <t>silk_genes, dup_50_nonorb, loss_50_nonorb</t>
+          <t>relaxed, busted_ph, dup_50_nonorb</t>
         </is>
       </c>
       <c r="C842" t="inlineStr">
         <is>
-          <t>129225276</t>
+          <t>129218554</t>
         </is>
       </c>
       <c r="D842" t="inlineStr">
         <is>
-          <t>GO:0005789 [Name: endoplasmic reticulum membrane]; GO:0015031 [Name: protein transport]</t>
+          <t>GO:0031982 [Name: vesicle]; GO:0005794 [Name: Golgi apparatus]; GO:0005802 [Name: trans-Golgi network]; GO:0003924 [Name: GTPase activity]; GO:0005525 [Name: GTP binding]; GO:0016192 [Name: vesicle-mediated transport]</t>
         </is>
       </c>
       <c r="E842" t="inlineStr">
         <is>
-          <t>dual oxidase maturation factor 2-like</t>
+          <t>ras-related protein Rab-7L1-like</t>
         </is>
       </c>
     </row>
     <row r="843">
       <c r="A843" t="inlineStr">
         <is>
-          <t>N5.HOG0067416</t>
+          <t>N5.HOG0063361</t>
         </is>
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>relaxed, busted_ph, dup_50_nonorb</t>
-        </is>
-      </c>
-      <c r="C843" t="inlineStr">
-        <is>
-          <t>129218554</t>
-        </is>
-      </c>
-      <c r="D843" t="inlineStr">
-        <is>
-          <t>GO:0031982 [Name: vesicle]; GO:0005794 [Name: Golgi apparatus]; GO:0005802 [Name: trans-Golgi network]; GO:0003924 [Name: GTPase activity]; GO:0005525 [Name: GTP binding]; GO:0016192 [Name: vesicle-mediated transport]</t>
-        </is>
-      </c>
-      <c r="E843" t="inlineStr">
-        <is>
-          <t>ras-related protein Rab-7L1-like</t>
-        </is>
-      </c>
+          <t>relaxed, busted_ph, loss_50_nonorb</t>
+        </is>
+      </c>
+      <c r="C843" t="inlineStr"/>
+      <c r="D843" t="inlineStr"/>
+      <c r="E843" t="inlineStr"/>
     </row>
     <row r="844">
       <c r="A844" t="inlineStr">
         <is>
-          <t>N5.HOG0063361</t>
+          <t>N5.HOG0066569</t>
         </is>
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>relaxed, busted_ph, loss_50_nonorb</t>
-        </is>
-      </c>
-      <c r="C844" t="inlineStr"/>
-      <c r="D844" t="inlineStr"/>
-      <c r="E844" t="inlineStr"/>
+          <t>relaxed, busted_ph_rev, dup_50_nonorb</t>
+        </is>
+      </c>
+      <c r="C844" t="inlineStr">
+        <is>
+          <t>129230806</t>
+        </is>
+      </c>
+      <c r="D844" t="inlineStr">
+        <is>
+          <t>GO:0003924 [Name: GTPase activity]; GO:0010506 [Name: regulation of autophagy]; GO:0071230 [Name: cellular response to amino acid stimulus]; GO:0009267 [Name: cellular response to starvation]; GO:1990131 [Name: Gtr1-Gtr2 GTPase complex]; GO:0032008 [Name: positive regulation of TOR signaling]; GO:0005525 [Name: GTP binding]; GO:0005634 [Name: nucleus]; GO:0005764 [Name: lysosome]</t>
+        </is>
+      </c>
+      <c r="E844" t="inlineStr">
+        <is>
+          <t>Ras-related GTP binding A/B</t>
+        </is>
+      </c>
     </row>
     <row r="845">
       <c r="A845" t="inlineStr">
         <is>
-          <t>N5.HOG0066569</t>
+          <t>N5.HOG0049214</t>
         </is>
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>relaxed, busted_ph_rev, dup_50_nonorb</t>
+          <t>intensified, busted_ph_rev, dup_50_nonorb</t>
         </is>
       </c>
       <c r="C845" t="inlineStr">
         <is>
-          <t>129230806</t>
+          <t>129227566</t>
         </is>
       </c>
       <c r="D845" t="inlineStr">
         <is>
-          <t>GO:0003924 [Name: GTPase activity]; GO:0010506 [Name: regulation of autophagy]; GO:0071230 [Name: cellular response to amino acid stimulus]; GO:0009267 [Name: cellular response to starvation]; GO:1990131 [Name: Gtr1-Gtr2 GTPase complex]; GO:0032008 [Name: positive regulation of TOR signaling]; GO:0005525 [Name: GTP binding]; GO:0005634 [Name: nucleus]; GO:0005764 [Name: lysosome]</t>
+          <t>GO:0003684 [Name: damaged DNA binding]; GO:0005634 [Name: nucleus]; GO:0000012 [Name: single strand break repair]; GO:0006303 [Name: double-strand break repair via nonhomologous end joining]; GO:0006284 [Name: base-excision repair]</t>
         </is>
       </c>
       <c r="E845" t="inlineStr">
         <is>
-          <t>Ras-related GTP binding A/B</t>
+          <t>DNA repair protein XRCC1</t>
         </is>
       </c>
     </row>
